--- a/原作搬运进度.xlsx
+++ b/原作搬运进度.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BBB-Bots-0525\WHATtheSpirebasedonQQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC5C381-0A4C-4E74-8EB9-664CE0BCA42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9613F7BE-CBDA-4B75-AC32-7F3744672A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="356">
   <si>
     <t>名称</t>
   </si>
@@ -2365,6 +2365,59 @@
   </si>
   <si>
     <t>create_warcry,</t>
+  </si>
+  <si>
+    <t>create_uppercut,</t>
+  </si>
+  <si>
+    <t>create_uppercut,</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_pummel,</t>
+  </si>
+  <si>
+    <t>create_carnage,</t>
+  </si>
+  <si>
+    <t>create_reckless_charge,</t>
+  </si>
+  <si>
+    <t>create_blood_for_blood,</t>
+  </si>
+  <si>
+    <t>create_dropkick,</t>
+  </si>
+  <si>
+    <t>create_hemokinesis,</t>
+  </si>
+  <si>
+    <t>create_rampage,</t>
+  </si>
+  <si>
+    <t>create_searing_blow,</t>
+  </si>
+  <si>
+    <t>create_sever_soul,</t>
+  </si>
+  <si>
+    <t>create_bludgeon,</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_immolate_history,</t>
+  </si>
+  <si>
+    <t>create_death_reaper,</t>
+  </si>
+  <si>
+    <t>create_immolate,</t>
+  </si>
+  <si>
+    <t>create_fiend_fire,</t>
+  </si>
+  <si>
+    <t>create_feed,</t>
   </si>
 </sst>
 </file>
@@ -2477,19 +2530,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2498,10 +2551,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2510,11 +2563,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2525,66 +2575,6 @@
     <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFA2A9B1"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFA2A9B1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2826,6 +2816,66 @@
         </left>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFA2A9B1"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFA2A9B1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2840,18 +2890,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}" name="表1" displayName="表1" ref="A1:I132" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}" name="表1" displayName="表1" ref="A1:I132" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="A1:I132" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{B6135FF2-C395-418D-8485-BC72711025F4}" name="名称" dataDxfId="10" dataCellStyle="超链接"/>
-    <tableColumn id="2" xr3:uid="{1B074D24-1599-4FC5-A236-BF6B4242EFE7}" name="英文名称" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{D865C2BE-A956-42B5-BB5A-7AE351AE07B6}" name="稀有度" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{3C3D501F-CAE0-4744-BAB5-1D7A745601E9}" name="类型" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{ABA971A8-6C44-4C6E-8C23-33561D5A983E}" name="耗能" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{9E82D8B0-ABBA-41BA-B169-92A89727DFAA}" name="描述" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{18D4BFF4-3B10-42F7-9F65-B8C97E7E712B}" name="升级耗能" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{E3C19DBB-A684-4385-8660-C5C4F8346A07}" name="升级描述" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{63182BFF-0D89-46A8-A878-6A9CEBB8D964}" name="ok？" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{B6135FF2-C395-418D-8485-BC72711025F4}" name="名称" dataDxfId="8" dataCellStyle="超链接"/>
+    <tableColumn id="2" xr3:uid="{1B074D24-1599-4FC5-A236-BF6B4242EFE7}" name="英文名称" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{D865C2BE-A956-42B5-BB5A-7AE351AE07B6}" name="稀有度" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{3C3D501F-CAE0-4744-BAB5-1D7A745601E9}" name="类型" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{ABA971A8-6C44-4C6E-8C23-33561D5A983E}" name="耗能" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{9E82D8B0-ABBA-41BA-B169-92A89727DFAA}" name="描述" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{18D4BFF4-3B10-42F7-9F65-B8C97E7E712B}" name="升级耗能" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E3C19DBB-A684-4385-8660-C5C4F8346A07}" name="升级描述" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{63182BFF-0D89-46A8-A878-6A9CEBB8D964}" name="ok？" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3120,14 +3170,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD8BFBA-4ECB-4D9C-9CFF-711EB681BC89}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="50.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>319</v>
       </c>
@@ -3135,17 +3185,20 @@
         <f>"""card."&amp;MID(LEFT(A1,LEN(A1)-1),8,LEN(LEFT(A1,LEN(A1)-1))-7)&amp;""": "&amp;LEFT(A1,LEN(A1)-1)&amp;","</f>
         <v>"card.clothesline": create_clothesline,</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>320</v>
       </c>
       <c r="B2" t="str">
-        <f t="shared" ref="B2:B20" si="0">"""card."&amp;MID(LEFT(A2,LEN(A2)-1),8,LEN(LEFT(A2,LEN(A2)-1))-7)&amp;""": "&amp;LEFT(A2,LEN(A2)-1)&amp;","</f>
+        <f t="shared" ref="B2:B37" si="0">"""card."&amp;MID(LEFT(A2,LEN(A2)-1),8,LEN(LEFT(A2,LEN(A2)-1))-7)&amp;""": "&amp;LEFT(A2,LEN(A2)-1)&amp;","</f>
         <v>"card.heavy_blade": create_heavy_blade,</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>321</v>
       </c>
@@ -3154,7 +3207,7 @@
         <v>"card.anger": create_anger,</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>322</v>
       </c>
@@ -3163,7 +3216,7 @@
         <v>"card.double_strike": create_double_strike,</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>323</v>
       </c>
@@ -3172,7 +3225,7 @@
         <v>"card.sword_boomerang": create_sword_boomerang,</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>324</v>
       </c>
@@ -3181,7 +3234,7 @@
         <v>"card.thunderclap": create_thunderclap,</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>325</v>
       </c>
@@ -3190,7 +3243,7 @@
         <v>"card.cleave": create_cleave,</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>326</v>
       </c>
@@ -3199,7 +3252,7 @@
         <v>"card.iron_wave": create_iron_wave,</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>327</v>
       </c>
@@ -3208,7 +3261,7 @@
         <v>"card.wild_strike": create_wild_strike,</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>328</v>
       </c>
@@ -3217,7 +3270,7 @@
         <v>"card.pommel_strike": create_pommel_strike,</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>329</v>
       </c>
@@ -3226,7 +3279,7 @@
         <v>"card.perfected_strike": create_perfected_strike,</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>331</v>
       </c>
@@ -3235,7 +3288,7 @@
         <v>"card.headbutt": create_headbutt,</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>332</v>
       </c>
@@ -3244,7 +3297,7 @@
         <v>"card.body_slam": create_body_slam,</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>333</v>
       </c>
@@ -3253,7 +3306,7 @@
         <v>"card.clash": create_clash,</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>335</v>
       </c>
@@ -3262,7 +3315,7 @@
         <v>"card.havoc": create_havoc,</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>336</v>
       </c>
@@ -3310,6 +3363,154 @@
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>334</v>
+      </c>
+      <c r="B21" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>339</v>
+      </c>
+      <c r="B22" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.uppercut": create_uppercut,</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>341</v>
+      </c>
+      <c r="B23" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.pummel": create_pummel,</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>342</v>
+      </c>
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.carnage": create_carnage,</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>343</v>
+      </c>
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.reckless_charge": create_reckless_charge,</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>350</v>
+      </c>
+      <c r="B26" t="str">
+        <f>"""card."&amp;MID(LEFT(A26,LEN(A26)-1),8,LEN(LEFT(A26,LEN(A26)-1))-7)&amp;""": "&amp;LEFT(A26,LEN(A26)-1)&amp;","</f>
+        <v>"card.bludgeon": create_bludgeon,</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>344</v>
+      </c>
+      <c r="B27" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.blood_for_blood": create_blood_for_blood,</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>345</v>
+      </c>
+      <c r="B28" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.dropkick": create_dropkick,</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>346</v>
+      </c>
+      <c r="B29" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.hemokinesis": create_hemokinesis,</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>347</v>
+      </c>
+      <c r="B30" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.rampage": create_rampage,</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>348</v>
+      </c>
+      <c r="B31" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.searing_blow": create_searing_blow,</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>349</v>
+      </c>
+      <c r="B32" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.sever_soul": create_sever_soul,</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>351</v>
+      </c>
+      <c r="B33" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.immolate_history": create_immolate_history,</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>352</v>
+      </c>
+      <c r="B34" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.death_reaper": create_death_reaper,</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>353</v>
+      </c>
+      <c r="B35" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.immolate": create_immolate,</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>354</v>
+      </c>
+      <c r="B36" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.fiend_fire": create_fiend_fire,</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>355</v>
+      </c>
+      <c r="B37" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.feed": create_feed,</v>
       </c>
     </row>
   </sheetData>
@@ -3335,7 +3536,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -3364,7 +3565,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -3393,7 +3594,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
+      <c r="A3" s="13"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -3407,7 +3608,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -3431,9 +3632,12 @@
       <c r="H4" s="7" t="s">
         <v>230</v>
       </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3447,7 +3651,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -3473,7 +3677,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -3502,7 +3706,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -3516,7 +3720,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -3542,7 +3746,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -3556,7 +3760,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -3582,7 +3786,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -3596,7 +3800,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -3620,9 +3824,12 @@
       <c r="H13" s="5" t="s">
         <v>37</v>
       </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
+      <c r="A14" s="13"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -3636,7 +3843,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -3662,7 +3869,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -3676,7 +3883,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -3700,9 +3907,12 @@
       <c r="H17" s="5" t="s">
         <v>48</v>
       </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>49</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -3731,7 +3941,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>51</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -3757,7 +3967,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+      <c r="A20" s="13"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -3771,7 +3981,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -3797,7 +4007,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
+      <c r="A22" s="13"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -3809,7 +4019,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="13" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -3833,9 +4043,12 @@
       <c r="H23" s="7" t="s">
         <v>241</v>
       </c>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
+      <c r="A24" s="13"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -3849,7 +4062,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="13" t="s">
         <v>61</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -3878,7 +4091,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="14"/>
+      <c r="A26" s="13"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -3892,7 +4105,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -3921,7 +4134,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -3950,7 +4163,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="14"/>
+      <c r="A29" s="13"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -3964,7 +4177,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="13" t="s">
         <v>72</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -3990,7 +4203,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="13" t="s">
         <v>76</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -4016,7 +4229,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A32" s="14"/>
+      <c r="A32" s="13"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -4030,7 +4243,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="13" t="s">
         <v>79</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -4056,7 +4269,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="13" t="s">
         <v>81</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -4085,7 +4298,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="13" t="s">
         <v>83</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -4111,7 +4324,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="13" t="s">
         <v>85</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -4137,7 +4350,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="14"/>
+      <c r="A37" s="13"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -4151,7 +4364,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="13" t="s">
         <v>87</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -4177,7 +4390,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="13" t="s">
         <v>91</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -4201,9 +4414,12 @@
       <c r="H39" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="I39" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A40" s="14"/>
+      <c r="A40" s="13"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -4217,7 +4433,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="13" t="s">
         <v>94</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -4243,7 +4459,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="13" t="s">
         <v>98</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -4269,7 +4485,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="13" t="s">
         <v>100</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -4295,7 +4511,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="14"/>
+      <c r="A44" s="13"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -4309,7 +4525,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="13" t="s">
         <v>102</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -4335,7 +4551,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="13" t="s">
         <v>104</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -4359,9 +4575,12 @@
       <c r="H46" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="I46" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A47" s="14"/>
+      <c r="A47" s="13"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -4375,7 +4594,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="14"/>
+      <c r="A48" s="13"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -4389,7 +4608,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="13" t="s">
         <v>106</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -4415,7 +4634,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="13" t="s">
         <v>108</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -4439,9 +4658,12 @@
       <c r="H50" s="7" t="s">
         <v>262</v>
       </c>
+      <c r="I50" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A51" s="14"/>
+      <c r="A51" s="13"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -4455,7 +4677,7 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="14"/>
+      <c r="A52" s="13"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -4469,7 +4691,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="13" t="s">
         <v>112</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -4495,7 +4717,7 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="13" t="s">
         <v>114</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -4521,7 +4743,7 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A55" s="14"/>
+      <c r="A55" s="13"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
@@ -4535,7 +4757,7 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="13" t="s">
         <v>118</v>
       </c>
       <c r="B56" s="4" t="s">
@@ -4564,7 +4786,7 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A57" s="14"/>
+      <c r="A57" s="13"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
@@ -4578,7 +4800,7 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="13" t="s">
         <v>120</v>
       </c>
       <c r="B58" s="4" t="s">
@@ -4604,7 +4826,7 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="14"/>
+      <c r="A59" s="13"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -4618,7 +4840,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="13" t="s">
         <v>122</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -4647,7 +4869,7 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="13" t="s">
         <v>124</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -4676,7 +4898,7 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A62" s="14"/>
+      <c r="A62" s="13"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
@@ -4690,7 +4912,7 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="13" t="s">
         <v>128</v>
       </c>
       <c r="B63" s="4" t="s">
@@ -4719,7 +4941,7 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A64" s="14"/>
+      <c r="A64" s="13"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
@@ -4733,7 +4955,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="13" t="s">
         <v>130</v>
       </c>
       <c r="B65" s="4" t="s">
@@ -4757,9 +4979,12 @@
       <c r="H65" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="I65" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="14"/>
+      <c r="A66" s="13"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
@@ -4773,7 +4998,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="13" t="s">
         <v>134</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -4797,9 +5022,12 @@
       <c r="H67" s="5" t="s">
         <v>137</v>
       </c>
+      <c r="I67" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A68" s="14"/>
+      <c r="A68" s="13"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -4813,7 +5041,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="13" t="s">
         <v>138</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -4839,7 +5067,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="14"/>
+      <c r="A70" s="13"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -4853,7 +5081,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="13" t="s">
         <v>140</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -4879,7 +5107,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A72" s="14"/>
+      <c r="A72" s="13"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -4893,7 +5121,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="14"/>
+      <c r="A73" s="13"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -4907,7 +5135,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="13" t="s">
         <v>144</v>
       </c>
       <c r="B74" s="4" t="s">
@@ -4933,7 +5161,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="13" t="s">
         <v>146</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -4959,7 +5187,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="14"/>
+      <c r="A76" s="13"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -4973,7 +5201,7 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="13" t="s">
         <v>148</v>
       </c>
       <c r="B77" s="4" t="s">
@@ -5002,7 +5230,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="14"/>
+      <c r="A78" s="13"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -5016,7 +5244,7 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="13" t="s">
         <v>151</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -5042,7 +5270,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="13" t="s">
         <v>153</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -5068,7 +5296,7 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="14"/>
+      <c r="A81" s="13"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -5080,7 +5308,7 @@
       <c r="H81" s="7"/>
     </row>
     <row r="82" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A82" s="14" t="s">
+      <c r="A82" s="13" t="s">
         <v>155</v>
       </c>
       <c r="B82" s="4" t="s">
@@ -5106,7 +5334,7 @@
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="14" t="s">
+      <c r="A83" s="13" t="s">
         <v>157</v>
       </c>
       <c r="B83" s="4" t="s">
@@ -5132,7 +5360,7 @@
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="14"/>
+      <c r="A84" s="13"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -5146,7 +5374,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="14"/>
+      <c r="A85" s="13"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -5160,7 +5388,7 @@
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="14"/>
+      <c r="A86" s="13"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -5174,7 +5402,7 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="13" t="s">
         <v>161</v>
       </c>
       <c r="B87" s="4" t="s">
@@ -5203,7 +5431,7 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A88" s="14"/>
+      <c r="A88" s="13"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -5217,7 +5445,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="13" t="s">
         <v>163</v>
       </c>
       <c r="B89" s="4" t="s">
@@ -5246,7 +5474,7 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="14"/>
+      <c r="A90" s="13"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -5260,7 +5488,7 @@
       </c>
     </row>
     <row r="91" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A91" s="14" t="s">
+      <c r="A91" s="13" t="s">
         <v>166</v>
       </c>
       <c r="B91" s="4" t="s">
@@ -5286,7 +5514,7 @@
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="14"/>
+      <c r="A92" s="13"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -5300,7 +5528,7 @@
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="14" t="s">
+      <c r="A93" s="13" t="s">
         <v>168</v>
       </c>
       <c r="B93" s="4" t="s">
@@ -5324,9 +5552,12 @@
       <c r="H93" s="5" t="s">
         <v>171</v>
       </c>
+      <c r="I93" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="14"/>
+      <c r="A94" s="13"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
@@ -5340,7 +5571,7 @@
       </c>
     </row>
     <row r="95" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="13" t="s">
         <v>172</v>
       </c>
       <c r="B95" s="4" t="s">
@@ -5366,7 +5597,7 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="14" t="s">
+      <c r="A96" s="13" t="s">
         <v>174</v>
       </c>
       <c r="B96" s="4" t="s">
@@ -5390,9 +5621,12 @@
       <c r="H96" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A97" s="14"/>
+      <c r="I96" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A97" s="13"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
@@ -5405,8 +5639,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A98" s="14" t="s">
+    <row r="98" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A98" s="13" t="s">
         <v>178</v>
       </c>
       <c r="B98" s="4" t="s">
@@ -5430,9 +5664,12 @@
       <c r="H98" s="5" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A99" s="14"/>
+      <c r="I98" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A99" s="13"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -5445,8 +5682,8 @@
         <v>295</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="14"/>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="13"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -5459,8 +5696,8 @@
         <v>251</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A101" s="14" t="s">
+    <row r="101" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A101" s="13" t="s">
         <v>182</v>
       </c>
       <c r="B101" s="4" t="s">
@@ -5484,9 +5721,12 @@
       <c r="H101" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A102" s="14"/>
+      <c r="I101" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A102" s="13"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -5499,8 +5739,8 @@
         <v>296</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A103" s="14" t="s">
+    <row r="103" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A103" s="13" t="s">
         <v>184</v>
       </c>
       <c r="B103" s="4" t="s">
@@ -5525,8 +5765,8 @@
         <v>298</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="14" t="s">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="13" t="s">
         <v>186</v>
       </c>
       <c r="B104" s="4" t="s">
@@ -5550,9 +5790,12 @@
       <c r="H104" s="5" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="14"/>
+      <c r="I104" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="13"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
@@ -5565,8 +5808,8 @@
         <v>299</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A106" s="14" t="s">
+    <row r="106" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A106" s="13" t="s">
         <v>189</v>
       </c>
       <c r="B106" s="4" t="s">
@@ -5591,8 +5834,8 @@
         <v>301</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="14" t="s">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="13" t="s">
         <v>191</v>
       </c>
       <c r="B107" s="4" t="s">
@@ -5617,8 +5860,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="14"/>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="13"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
@@ -5631,8 +5874,8 @@
         <v>251</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="14" t="s">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="13" t="s">
         <v>193</v>
       </c>
       <c r="B109" s="4" t="s">
@@ -5657,8 +5900,8 @@
         <v>246</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A110" s="14"/>
+    <row r="110" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A110" s="13"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
@@ -5671,8 +5914,8 @@
         <v>303</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A111" s="14" t="s">
+    <row r="111" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A111" s="13" t="s">
         <v>195</v>
       </c>
       <c r="B111" s="4" t="s">
@@ -5696,9 +5939,12 @@
       <c r="H111" s="7" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="14"/>
+      <c r="I111" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="13"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
@@ -5712,7 +5958,7 @@
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="14" t="s">
+      <c r="A113" s="13" t="s">
         <v>197</v>
       </c>
       <c r="B113" s="4" t="s">
@@ -5741,7 +5987,7 @@
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="14"/>
+      <c r="A114" s="13"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
@@ -5755,7 +6001,7 @@
       </c>
     </row>
     <row r="115" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A115" s="14" t="s">
+      <c r="A115" s="13" t="s">
         <v>199</v>
       </c>
       <c r="B115" s="4" t="s">
@@ -5781,7 +6027,7 @@
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="14"/>
+      <c r="A116" s="13"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
@@ -5795,7 +6041,7 @@
       </c>
     </row>
     <row r="117" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A117" s="14" t="s">
+      <c r="A117" s="13" t="s">
         <v>201</v>
       </c>
       <c r="B117" s="4" t="s">
@@ -5821,7 +6067,7 @@
       </c>
     </row>
     <row r="118" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A118" s="14" t="s">
+      <c r="A118" s="13" t="s">
         <v>203</v>
       </c>
       <c r="B118" s="4" t="s">
@@ -5850,7 +6096,7 @@
       </c>
     </row>
     <row r="119" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A119" s="14" t="s">
+      <c r="A119" s="13" t="s">
         <v>205</v>
       </c>
       <c r="B119" s="4" t="s">
@@ -5879,7 +6125,7 @@
       </c>
     </row>
     <row r="120" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A120" s="14" t="s">
+      <c r="A120" s="13" t="s">
         <v>209</v>
       </c>
       <c r="B120" s="4" t="s">
@@ -5908,7 +6154,7 @@
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="14" t="s">
+      <c r="A121" s="13" t="s">
         <v>211</v>
       </c>
       <c r="B121" s="4" t="s">
@@ -5937,7 +6183,7 @@
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="14"/>
+      <c r="A122" s="13"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
@@ -5951,7 +6197,7 @@
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="14" t="s">
+      <c r="A123" s="13" t="s">
         <v>213</v>
       </c>
       <c r="B123" s="4" t="s">
@@ -5980,7 +6226,7 @@
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="14" t="s">
+      <c r="A124" s="13" t="s">
         <v>217</v>
       </c>
       <c r="B124" s="4" t="s">
@@ -6004,9 +6250,12 @@
       <c r="H124" s="5" t="s">
         <v>219</v>
       </c>
+      <c r="I124" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="14"/>
+      <c r="A125" s="13"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
@@ -6020,7 +6269,7 @@
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="14"/>
+      <c r="A126" s="13"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
@@ -6034,7 +6283,7 @@
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="14" t="s">
+      <c r="A127" s="13" t="s">
         <v>220</v>
       </c>
       <c r="B127" s="4" t="s">
@@ -6063,7 +6312,7 @@
       </c>
     </row>
     <row r="128" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A128" s="14"/>
+      <c r="A128" s="13"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
@@ -6077,7 +6326,7 @@
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="14"/>
+      <c r="A129" s="13"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
@@ -6091,7 +6340,7 @@
       </c>
     </row>
     <row r="130" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A130" s="14" t="s">
+      <c r="A130" s="13" t="s">
         <v>223</v>
       </c>
       <c r="B130" s="4" t="s">
@@ -6115,9 +6364,12 @@
       <c r="H130" s="5" t="s">
         <v>226</v>
       </c>
+      <c r="I130" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="14" t="s">
+      <c r="A131" s="13" t="s">
         <v>227</v>
       </c>
       <c r="B131" s="4" t="s">

--- a/原作搬运进度.xlsx
+++ b/原作搬运进度.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BBB-Bots-0525\WHATtheSpirebasedonQQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9613F7BE-CBDA-4B75-AC32-7F3744672A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016D95ED-A67A-4ACF-BB12-1ADA56CCF945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="373">
   <si>
     <t>名称</t>
   </si>
@@ -2418,6 +2418,57 @@
   </si>
   <si>
     <t>create_feed,</t>
+  </si>
+  <si>
+    <t>create_shockwave,</t>
+  </si>
+  <si>
+    <t>create_intimidate,</t>
+  </si>
+  <si>
+    <t>create_battle_trance,</t>
+  </si>
+  <si>
+    <t>create_bloodletting,</t>
+  </si>
+  <si>
+    <t>create_burning_pact,</t>
+  </si>
+  <si>
+    <t>create_disarm,</t>
+  </si>
+  <si>
+    <t>create_dual_wield,</t>
+  </si>
+  <si>
+    <t>create_entrench,</t>
+  </si>
+  <si>
+    <t>create_flame_barrier,</t>
+  </si>
+  <si>
+    <t>create_ghostly_armor,</t>
+  </si>
+  <si>
+    <t>create_infernal_blade,</t>
+  </si>
+  <si>
+    <t>create_power_through,</t>
+  </si>
+  <si>
+    <t>create_rage,</t>
+  </si>
+  <si>
+    <t>create_second_wind,</t>
+  </si>
+  <si>
+    <t>create_seeing_red,</t>
+  </si>
+  <si>
+    <t>create_sentinel,</t>
+  </si>
+  <si>
+    <t>create_spot_weakness,</t>
   </si>
 </sst>
 </file>
@@ -2891,7 +2942,16 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}" name="表1" displayName="表1" ref="A1:I132" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
-  <autoFilter ref="A1:I132" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}"/>
+  <autoFilter ref="A1:I132" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="8">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{B6135FF2-C395-418D-8485-BC72711025F4}" name="名称" dataDxfId="8" dataCellStyle="超链接"/>
     <tableColumn id="2" xr3:uid="{1B074D24-1599-4FC5-A236-BF6B4242EFE7}" name="英文名称" dataDxfId="7"/>
@@ -3170,7 +3230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD8BFBA-4ECB-4D9C-9CFF-711EB681BC89}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3194,7 +3254,7 @@
         <v>320</v>
       </c>
       <c r="B2" t="str">
-        <f t="shared" ref="B2:B37" si="0">"""card."&amp;MID(LEFT(A2,LEN(A2)-1),8,LEN(LEFT(A2,LEN(A2)-1))-7)&amp;""": "&amp;LEFT(A2,LEN(A2)-1)&amp;","</f>
+        <f t="shared" ref="B2:C57" si="0">"""card."&amp;MID(LEFT(A2,LEN(A2)-1),8,LEN(LEFT(A2,LEN(A2)-1))-7)&amp;""": "&amp;LEFT(A2,LEN(A2)-1)&amp;","</f>
         <v>"card.heavy_blade": create_heavy_blade,</v>
       </c>
     </row>
@@ -3468,7 +3528,7 @@
         <v>"card.sever_soul": create_sever_soul,</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>351</v>
       </c>
@@ -3477,7 +3537,7 @@
         <v>"card.immolate_history": create_immolate_history,</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>352</v>
       </c>
@@ -3486,7 +3546,7 @@
         <v>"card.death_reaper": create_death_reaper,</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>353</v>
       </c>
@@ -3495,7 +3555,7 @@
         <v>"card.immolate": create_immolate,</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>354</v>
       </c>
@@ -3504,13 +3564,257 @@
         <v>"card.fiend_fire": create_fiend_fire,</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>355</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="0"/>
         <v>"card.feed": create_feed,</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B38" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B39" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B40" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>356</v>
+      </c>
+      <c r="B41" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.shockwave": create_shockwave,</v>
+      </c>
+      <c r="C41" t="str">
+        <f>"""card."&amp;MID(LEFT(A41,LEN(A41)-1),8,LEN(LEFT(A41,LEN(A41)-1))-7)&amp;""""&amp;","</f>
+        <v>"card.shockwave",</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>357</v>
+      </c>
+      <c r="B42" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.intimidate": create_intimidate,</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" ref="C42:C58" si="1">"""card."&amp;MID(LEFT(A42,LEN(A42)-1),8,LEN(LEFT(A42,LEN(A42)-1))-7)&amp;""""&amp;","</f>
+        <v>"card.intimidate",</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>358</v>
+      </c>
+      <c r="B43" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.battle_trance": create_battle_trance,</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.battle_trance",</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>359</v>
+      </c>
+      <c r="B44" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.bloodletting": create_bloodletting,</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.bloodletting",</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>360</v>
+      </c>
+      <c r="B45" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.burning_pact": create_burning_pact,</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.burning_pact",</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>361</v>
+      </c>
+      <c r="B46" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.disarm": create_disarm,</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.disarm",</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>362</v>
+      </c>
+      <c r="B47" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.dual_wield": create_dual_wield,</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.dual_wield",</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>363</v>
+      </c>
+      <c r="B48" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.entrench": create_entrench,</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.entrench",</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>364</v>
+      </c>
+      <c r="B49" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.flame_barrier": create_flame_barrier,</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.flame_barrier",</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>365</v>
+      </c>
+      <c r="B50" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.ghostly_armor": create_ghostly_armor,</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.ghostly_armor",</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>366</v>
+      </c>
+      <c r="B51" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.infernal_blade": create_infernal_blade,</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.infernal_blade",</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>367</v>
+      </c>
+      <c r="B52" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.power_through": create_power_through,</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.power_through",</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>368</v>
+      </c>
+      <c r="B53" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.rage": create_rage,</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.rage",</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>369</v>
+      </c>
+      <c r="B54" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.second_wind": create_second_wind,</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.second_wind",</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>370</v>
+      </c>
+      <c r="B55" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.seeing_red": create_seeing_red,</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.seeing_red",</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>371</v>
+      </c>
+      <c r="B56" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.sentinel": create_sentinel,</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.sentinel",</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>372</v>
+      </c>
+      <c r="B57" t="str">
+        <f t="shared" si="0"/>
+        <v>"card.spot_weakness": create_spot_weakness,</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="1"/>
+        <v>"card.spot_weakness",</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -3564,7 +3868,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
@@ -3593,7 +3897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3607,7 +3911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>15</v>
       </c>
@@ -3636,7 +3940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -3676,7 +3980,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
@@ -3705,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -3745,7 +4049,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -3759,7 +4063,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>29</v>
       </c>
@@ -3784,8 +4088,11 @@
       <c r="H11" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3799,7 +4106,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>35</v>
       </c>
@@ -3828,7 +4135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -3842,7 +4149,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>40</v>
       </c>
@@ -3867,8 +4174,11 @@
       <c r="H15" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -3882,7 +4192,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>45</v>
       </c>
@@ -3911,7 +4221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>49</v>
       </c>
@@ -3940,7 +4250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>51</v>
       </c>
@@ -3965,8 +4275,11 @@
       <c r="H19" s="7" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -4006,7 +4319,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -4018,7 +4331,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>57</v>
       </c>
@@ -4047,7 +4360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -4061,7 +4374,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>61</v>
       </c>
@@ -4090,7 +4403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -4104,7 +4417,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>65</v>
       </c>
@@ -4133,7 +4446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>69</v>
       </c>
@@ -4162,7 +4475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -4228,7 +4541,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -4268,7 +4581,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>81</v>
       </c>
@@ -4323,7 +4636,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>85</v>
       </c>
@@ -4348,8 +4661,11 @@
       <c r="H36" s="7" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -4389,7 +4705,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>91</v>
       </c>
@@ -4418,7 +4734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -4432,7 +4748,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>94</v>
       </c>
@@ -4457,8 +4773,11 @@
       <c r="H41" s="5" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="I41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>98</v>
       </c>
@@ -4482,6 +4801,9 @@
       </c>
       <c r="H42" s="7" t="s">
         <v>254</v>
+      </c>
+      <c r="I42" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
@@ -4510,7 +4832,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -4550,7 +4872,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>104</v>
       </c>
@@ -4579,7 +4901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -4593,7 +4915,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -4633,7 +4955,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>108</v>
       </c>
@@ -4662,7 +4984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -4676,7 +4998,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -4716,7 +5038,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>114</v>
       </c>
@@ -4741,8 +5063,11 @@
       <c r="H54" s="7" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="I54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -4756,7 +5081,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>118</v>
       </c>
@@ -4785,7 +5110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -4799,7 +5124,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>120</v>
       </c>
@@ -4824,8 +5149,11 @@
       <c r="H58" s="7" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -4839,7 +5167,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>122</v>
       </c>
@@ -4868,7 +5196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>124</v>
       </c>
@@ -4897,7 +5225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -4911,7 +5239,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
         <v>128</v>
       </c>
@@ -4940,7 +5268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="13"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -4954,7 +5282,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
         <v>130</v>
       </c>
@@ -4983,7 +5311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -4997,7 +5325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
         <v>134</v>
       </c>
@@ -5026,7 +5354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="13"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -5066,7 +5394,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="13"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -5080,7 +5408,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
         <v>140</v>
       </c>
@@ -5105,8 +5433,11 @@
       <c r="H71" s="5" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="I71" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="13"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -5120,7 +5451,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="13"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -5160,7 +5491,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
         <v>146</v>
       </c>
@@ -5185,8 +5516,11 @@
       <c r="H75" s="7" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="13"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -5200,7 +5534,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
         <v>148</v>
       </c>
@@ -5229,7 +5563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="13"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -5295,7 +5629,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -5359,7 +5693,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="13"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -5373,7 +5707,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="13"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -5387,7 +5721,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="13"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -5401,7 +5735,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
         <v>161</v>
       </c>
@@ -5430,7 +5764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="13"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -5444,7 +5778,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
         <v>163</v>
       </c>
@@ -5473,7 +5807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="13"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -5487,7 +5821,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
         <v>166</v>
       </c>
@@ -5512,8 +5846,11 @@
       <c r="H91" s="7" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I91" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="13"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -5527,7 +5864,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
         <v>168</v>
       </c>
@@ -5556,7 +5893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="13"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -5570,7 +5907,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
         <v>172</v>
       </c>
@@ -5595,8 +5932,11 @@
       <c r="H95" s="7" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I95" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
         <v>174</v>
       </c>
@@ -5625,7 +5965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="13"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -5639,7 +5979,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>178</v>
       </c>
@@ -5668,7 +6008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="13"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -5682,7 +6022,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -5696,7 +6036,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
         <v>182</v>
       </c>
@@ -5725,7 +6065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="13"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -5765,7 +6105,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
         <v>186</v>
       </c>
@@ -5794,7 +6134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="13"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -5808,7 +6148,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="13" t="s">
         <v>189</v>
       </c>
@@ -5833,8 +6173,11 @@
       <c r="H106" s="9" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I106" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
         <v>191</v>
       </c>
@@ -5859,8 +6202,11 @@
       <c r="H107" s="5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I107" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="13"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -5874,7 +6220,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
         <v>193</v>
       </c>
@@ -5899,8 +6245,11 @@
       <c r="H109" s="7" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="I109" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="13"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -5914,7 +6263,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
         <v>195</v>
       </c>
@@ -5943,7 +6292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="13"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -5957,7 +6306,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
         <v>197</v>
       </c>
@@ -5986,7 +6335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="13"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -6000,7 +6349,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="13" t="s">
         <v>199</v>
       </c>
@@ -6025,8 +6374,11 @@
       <c r="H115" s="5" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I115" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="13"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -6040,7 +6392,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
         <v>201</v>
       </c>
@@ -6065,8 +6417,11 @@
       <c r="H117" s="7" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="I117" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="13" t="s">
         <v>203</v>
       </c>
@@ -6095,7 +6450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="13" t="s">
         <v>205</v>
       </c>
@@ -6124,7 +6479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13" t="s">
         <v>209</v>
       </c>
@@ -6153,7 +6508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="13" t="s">
         <v>211</v>
       </c>
@@ -6182,7 +6537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="13"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -6196,7 +6551,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
         <v>213</v>
       </c>
@@ -6225,7 +6580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
         <v>217</v>
       </c>
@@ -6254,7 +6609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="13"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -6268,7 +6623,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="13"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -6282,7 +6637,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
         <v>220</v>
       </c>
@@ -6311,7 +6666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="13"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -6325,7 +6680,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="13"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -6339,7 +6694,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="13" t="s">
         <v>223</v>
       </c>
@@ -6368,7 +6723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="13" t="s">
         <v>227</v>
       </c>
@@ -6397,7 +6752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" ht="28.2" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="10"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>

--- a/原作搬运进度.xlsx
+++ b/原作搬运进度.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BBB-Bots-0525\WHATtheSpirebasedonQQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016D95ED-A67A-4ACF-BB12-1ADA56CCF945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D156214-1061-409A-9D48-C55FC7D2E016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作台" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="394">
   <si>
     <t>名称</t>
   </si>
@@ -2469,6 +2469,69 @@
   </si>
   <si>
     <t>create_spot_weakness,</t>
+  </si>
+  <si>
+    <t>create_combust,</t>
+  </si>
+  <si>
+    <t>create_dark_embrace,</t>
+  </si>
+  <si>
+    <t>create_feel_no_pain,</t>
+  </si>
+  <si>
+    <t>create_fire_breathing,</t>
+  </si>
+  <si>
+    <t>create_fire_breathing_history,</t>
+  </si>
+  <si>
+    <t>create_inflame,</t>
+  </si>
+  <si>
+    <t>create_metallicize,</t>
+  </si>
+  <si>
+    <t>create_rupture,</t>
+  </si>
+  <si>
+    <t>create_evolve,</t>
+  </si>
+  <si>
+    <t>create_barricade,</t>
+  </si>
+  <si>
+    <t>create_berserk,</t>
+  </si>
+  <si>
+    <t>create_brutality,</t>
+  </si>
+  <si>
+    <t>create_corruption,</t>
+  </si>
+  <si>
+    <t>create_juggernaut,</t>
+  </si>
+  <si>
+    <t>create_impervious,</t>
+  </si>
+  <si>
+    <t>create_double_tap,</t>
+  </si>
+  <si>
+    <t>create_burst,</t>
+  </si>
+  <si>
+    <t>create_limit_break,</t>
+  </si>
+  <si>
+    <t>create_offering,</t>
+  </si>
+  <si>
+    <t>create_amplify,</t>
+  </si>
+  <si>
+    <t>create_exhume,</t>
   </si>
 </sst>
 </file>
@@ -2943,13 +3006,15 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}" name="表1" displayName="表1" ref="A1:I132" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="A1:I132" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="稀有"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="3">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="8">
-      <filters blank="1"/>
+      <filters>
+        <filter val="技能"/>
+      </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="9">
@@ -3230,7 +3295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD8BFBA-4ECB-4D9C-9CFF-711EB681BC89}">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3254,7 +3319,7 @@
         <v>320</v>
       </c>
       <c r="B2" t="str">
-        <f t="shared" ref="B2:C57" si="0">"""card."&amp;MID(LEFT(A2,LEN(A2)-1),8,LEN(LEFT(A2,LEN(A2)-1))-7)&amp;""": "&amp;LEFT(A2,LEN(A2)-1)&amp;","</f>
+        <f t="shared" ref="B2:B57" si="0">"""card."&amp;MID(LEFT(A2,LEN(A2)-1),8,LEN(LEFT(A2,LEN(A2)-1))-7)&amp;""": "&amp;LEFT(A2,LEN(A2)-1)&amp;","</f>
         <v>"card.heavy_blade": create_heavy_blade,</v>
       </c>
     </row>
@@ -3613,7 +3678,7 @@
         <v>"card.intimidate": create_intimidate,</v>
       </c>
       <c r="C42" t="str">
-        <f t="shared" ref="C42:C58" si="1">"""card."&amp;MID(LEFT(A42,LEN(A42)-1),8,LEN(LEFT(A42,LEN(A42)-1))-7)&amp;""""&amp;","</f>
+        <f t="shared" ref="C42:C57" si="1">"""card."&amp;MID(LEFT(A42,LEN(A42)-1),8,LEN(LEFT(A42,LEN(A42)-1))-7)&amp;""""&amp;","</f>
         <v>"card.intimidate",</v>
       </c>
     </row>
@@ -3815,6 +3880,287 @@
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>334</v>
+      </c>
+      <c r="B58" t="e">
+        <f t="shared" ref="B58:B79" si="2">"""card."&amp;MID(LEFT(A58,LEN(A58)-1),8,LEN(LEFT(A58,LEN(A58)-1))-7)&amp;""": "&amp;LEFT(A58,LEN(A58)-1)&amp;","</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C58" t="e">
+        <f t="shared" ref="C58:C79" si="3">"""card."&amp;MID(LEFT(A58,LEN(A58)-1),8,LEN(LEFT(A58,LEN(A58)-1))-7)&amp;""""&amp;","</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>373</v>
+      </c>
+      <c r="B59" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.combust": create_combust,</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.combust",</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>374</v>
+      </c>
+      <c r="B60" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.dark_embrace": create_dark_embrace,</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.dark_embrace",</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>375</v>
+      </c>
+      <c r="B61" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.feel_no_pain": create_feel_no_pain,</v>
+      </c>
+      <c r="C61" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.feel_no_pain",</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>376</v>
+      </c>
+      <c r="B62" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.fire_breathing": create_fire_breathing,</v>
+      </c>
+      <c r="C62" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.fire_breathing",</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>377</v>
+      </c>
+      <c r="B63" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.fire_breathing_history": create_fire_breathing_history,</v>
+      </c>
+      <c r="C63" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.fire_breathing_history",</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>378</v>
+      </c>
+      <c r="B64" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.inflame": create_inflame,</v>
+      </c>
+      <c r="C64" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.inflame",</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>379</v>
+      </c>
+      <c r="B65" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.metallicize": create_metallicize,</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.metallicize",</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>380</v>
+      </c>
+      <c r="B66" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.rupture": create_rupture,</v>
+      </c>
+      <c r="C66" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.rupture",</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>381</v>
+      </c>
+      <c r="B67" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.evolve": create_evolve,</v>
+      </c>
+      <c r="C67" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.evolve",</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>382</v>
+      </c>
+      <c r="B68" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.barricade": create_barricade,</v>
+      </c>
+      <c r="C68" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.barricade",</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>383</v>
+      </c>
+      <c r="B69" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.berserk": create_berserk,</v>
+      </c>
+      <c r="C69" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.berserk",</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>384</v>
+      </c>
+      <c r="B70" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.brutality": create_brutality,</v>
+      </c>
+      <c r="C70" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.brutality",</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>385</v>
+      </c>
+      <c r="B71" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.corruption": create_corruption,</v>
+      </c>
+      <c r="C71" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.corruption",</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>386</v>
+      </c>
+      <c r="B72" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.juggernaut": create_juggernaut,</v>
+      </c>
+      <c r="C72" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.juggernaut",</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>387</v>
+      </c>
+      <c r="B73" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.impervious": create_impervious,</v>
+      </c>
+      <c r="C73" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.impervious",</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>388</v>
+      </c>
+      <c r="B74" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.double_tap": create_double_tap,</v>
+      </c>
+      <c r="C74" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.double_tap",</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>389</v>
+      </c>
+      <c r="B75" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.burst": create_burst,</v>
+      </c>
+      <c r="C75" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.burst",</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>390</v>
+      </c>
+      <c r="B76" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.limit_break": create_limit_break,</v>
+      </c>
+      <c r="C76" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.limit_break",</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>391</v>
+      </c>
+      <c r="B77" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.offering": create_offering,</v>
+      </c>
+      <c r="C77" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.offering",</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>392</v>
+      </c>
+      <c r="B78" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.amplify": create_amplify,</v>
+      </c>
+      <c r="C78" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.amplify",</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>393</v>
+      </c>
+      <c r="B79" t="str">
+        <f t="shared" si="2"/>
+        <v>"card.exhume": create_exhume,</v>
+      </c>
+      <c r="C79" t="str">
+        <f t="shared" si="3"/>
+        <v>"card.exhume",</v>
       </c>
     </row>
   </sheetData>
@@ -3954,7 +4300,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
@@ -3978,6 +4324,9 @@
       </c>
       <c r="H6" s="7" t="s">
         <v>233</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -4023,7 +4372,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
@@ -4047,6 +4396,9 @@
       </c>
       <c r="H9" s="7" t="s">
         <v>237</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
@@ -4293,7 +4645,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>54</v>
       </c>
@@ -4317,6 +4669,9 @@
       </c>
       <c r="H21" s="7" t="s">
         <v>240</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
@@ -4489,7 +4844,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>72</v>
       </c>
@@ -4514,8 +4869,11 @@
       <c r="H30" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>76</v>
       </c>
@@ -4539,6 +4897,9 @@
       </c>
       <c r="H31" s="5" t="s">
         <v>78</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
@@ -4555,7 +4916,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>79</v>
       </c>
@@ -4579,6 +4940,9 @@
       </c>
       <c r="H33" s="7" t="s">
         <v>245</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
@@ -4610,7 +4974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>83</v>
       </c>
@@ -4634,6 +4998,9 @@
       </c>
       <c r="H35" s="7" t="s">
         <v>248</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -4704,6 +5071,9 @@
       <c r="H38" s="5" t="s">
         <v>90</v>
       </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
@@ -4831,6 +5201,9 @@
       <c r="H43" s="7" t="s">
         <v>255</v>
       </c>
+      <c r="I43" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
@@ -4846,7 +5219,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>102</v>
       </c>
@@ -4870,6 +5243,9 @@
       </c>
       <c r="H45" s="7" t="s">
         <v>257</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -4929,7 +5305,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>106</v>
       </c>
@@ -4953,6 +5329,9 @@
       </c>
       <c r="H49" s="5" t="s">
         <v>261</v>
+      </c>
+      <c r="I49" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -5012,7 +5391,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>112</v>
       </c>
@@ -5036,6 +5415,9 @@
       </c>
       <c r="H53" s="5" t="s">
         <v>264</v>
+      </c>
+      <c r="I53" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -5393,6 +5775,9 @@
       <c r="H69" s="7" t="s">
         <v>278</v>
       </c>
+      <c r="I69" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="13"/>
@@ -5465,7 +5850,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
         <v>144</v>
       </c>
@@ -5489,6 +5874,9 @@
       </c>
       <c r="H74" s="7" t="s">
         <v>279</v>
+      </c>
+      <c r="I74" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
@@ -5577,7 +5965,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>151</v>
       </c>
@@ -5601,6 +5989,9 @@
       </c>
       <c r="H79" s="7" t="s">
         <v>284</v>
+      </c>
+      <c r="I79" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -5627,6 +6018,9 @@
       </c>
       <c r="H80" s="7" t="s">
         <v>285</v>
+      </c>
+      <c r="I80" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -5641,7 +6035,7 @@
       <c r="G81" s="4"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
         <v>155</v>
       </c>
@@ -5665,6 +6059,9 @@
       </c>
       <c r="H82" s="7" t="s">
         <v>287</v>
+      </c>
+      <c r="I82" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -5691,6 +6088,9 @@
       </c>
       <c r="H83" s="5" t="s">
         <v>159</v>
+      </c>
+      <c r="I83" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -6079,7 +6479,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
         <v>184</v>
       </c>
@@ -6103,6 +6503,9 @@
       </c>
       <c r="H103" s="7" t="s">
         <v>298</v>
+      </c>
+      <c r="I103" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">

--- a/原作搬运进度.xlsx
+++ b/原作搬运进度.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BBB-Bots-0525\WHATtheSpirebasedonQQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D156214-1061-409A-9D48-C55FC7D2E016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7071F1AB-0428-4A47-A6D8-0A6386B9F7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作台" sheetId="2" r:id="rId1"/>
-    <sheet name="战士.塔1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="战士.塔1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="580">
   <si>
     <t>名称</t>
   </si>
@@ -2533,12 +2534,843 @@
   <si>
     <t>create_exhume,</t>
   </si>
+  <si>
+    <t>颜色</t>
+  </si>
+  <si>
+    <t>神化</t>
+  </si>
+  <si>
+    <t>Apotheosis</t>
+  </si>
+  <si>
+    <t>无色</t>
+  </si>
+  <si>
+    <t>包扎</t>
+  </si>
+  <si>
+    <t>Bandage Up</t>
+  </si>
+  <si>
+    <t>回复4生命。</t>
+  </si>
+  <si>
+    <t>恢复6生命。</t>
+  </si>
+  <si>
+    <t>噬咬</t>
+  </si>
+  <si>
+    <t>Bite</t>
+  </si>
+  <si>
+    <t>特殊</t>
+  </si>
+  <si>
+    <t>回复2点生命。</t>
+  </si>
+  <si>
+    <t>回复3点生命。</t>
+  </si>
+  <si>
+    <t>贝塔</t>
+  </si>
+  <si>
+    <t>Beta</t>
+  </si>
+  <si>
+    <t>致盲</t>
+  </si>
+  <si>
+    <t>Blind</t>
+  </si>
+  <si>
+    <t>灼伤</t>
+  </si>
+  <si>
+    <t>Burn</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>在你的回合结束时，你受到2点伤害。</t>
+  </si>
+  <si>
+    <t>在你的回合结束时，你受到4点伤害。</t>
+  </si>
+  <si>
+    <t>结茧</t>
+  </si>
+  <si>
+    <t>Chrysalis</t>
+  </si>
+  <si>
+    <t>在你的抽牌堆中加入3张随机技能牌。</t>
+  </si>
+  <si>
+    <t>它们在本场战斗中耗能为0。</t>
+  </si>
+  <si>
+    <t>在你的抽牌堆中加入5张随机技能牌。</t>
+  </si>
+  <si>
+    <t>黑暗镣铐</t>
+  </si>
+  <si>
+    <t>Dark Shackles</t>
+  </si>
+  <si>
+    <t>晕眩</t>
+  </si>
+  <si>
+    <t>Dazed</t>
+  </si>
+  <si>
+    <t>nil</t>
+  </si>
+  <si>
+    <t>深呼吸</t>
+  </si>
+  <si>
+    <t>Deep Breath</t>
+  </si>
+  <si>
+    <t>将你的弃牌堆洗牌后放入你的抽牌堆。</t>
+  </si>
+  <si>
+    <t>发现</t>
+  </si>
+  <si>
+    <t>Discovery</t>
+  </si>
+  <si>
+    <t>从3张随机牌中选择1张加入你的手牌。</t>
+  </si>
+  <si>
+    <t>闪亮登场</t>
+  </si>
+  <si>
+    <t>Dramatic Entrance</t>
+  </si>
+  <si>
+    <t>对所有敌人造成12点伤害。</t>
+  </si>
+  <si>
+    <t>开悟</t>
+  </si>
+  <si>
+    <t>Enlightenment</t>
+  </si>
+  <si>
+    <t>在这个回合，你当前手牌中所有牌的耗能降低到1。</t>
+  </si>
+  <si>
+    <t>在本场战斗，你当前手牌中所有牌的耗能降低到1.</t>
+  </si>
+  <si>
+    <t>灭除之刃</t>
+  </si>
+  <si>
+    <t>Expunger</t>
+  </si>
+  <si>
+    <t>造成9点伤害X次。</t>
+  </si>
+  <si>
+    <t>造成15点伤害X次。</t>
+  </si>
+  <si>
+    <t>妙计</t>
+  </si>
+  <si>
+    <t>Finesse</t>
+  </si>
+  <si>
+    <t>亮剑</t>
+  </si>
+  <si>
+    <t>Flash of Steel</t>
+  </si>
+  <si>
+    <t>造成3点伤害。</t>
+  </si>
+  <si>
+    <t>预谋</t>
+  </si>
+  <si>
+    <t>Forethought</t>
+  </si>
+  <si>
+    <t>将手牌中的一张牌放到抽牌堆的底部。</t>
+  </si>
+  <si>
+    <t>并且这张牌在被打出之前，耗能变为0。</t>
+  </si>
+  <si>
+    <t>将手牌中的任意张牌放到抽牌堆的底部。</t>
+  </si>
+  <si>
+    <t>并且它们被打出之前，耗能变为0。</t>
+  </si>
+  <si>
+    <t>灵体</t>
+  </si>
+  <si>
+    <t>Ghostly</t>
+  </si>
+  <si>
+    <t>获得1层无实体。</t>
+  </si>
+  <si>
+    <t>优秀直觉</t>
+  </si>
+  <si>
+    <t>Good Instincts</t>
+  </si>
+  <si>
+    <t>贪婪之手</t>
+  </si>
+  <si>
+    <t>Hand Of Greed</t>
+  </si>
+  <si>
+    <t>造成25点伤害。</t>
+  </si>
+  <si>
+    <t>急躁</t>
+  </si>
+  <si>
+    <t>Impatience</t>
+  </si>
+  <si>
+    <t>如果你的手牌中没有攻击牌，抽2张牌。</t>
+  </si>
+  <si>
+    <t>如果你的手牌中没有攻击牌，抽3张牌。</t>
+  </si>
+  <si>
+    <t>洞见</t>
+  </si>
+  <si>
+    <t>Insight</t>
+  </si>
+  <si>
+    <t>J.A.X.</t>
+  </si>
+  <si>
+    <t>花样百出</t>
+  </si>
+  <si>
+    <t>Jack Of All Trades</t>
+  </si>
+  <si>
+    <t>增加1张随机无色牌到你的手牌。</t>
+  </si>
+  <si>
+    <t>增加2张随机无色牌到你的手牌。</t>
+  </si>
+  <si>
+    <t>疯狂</t>
+  </si>
+  <si>
+    <t>Madness</t>
+  </si>
+  <si>
+    <t>你手牌中一张随机牌在本场战斗中耗能变为0。</t>
+  </si>
+  <si>
+    <t>磁力</t>
+  </si>
+  <si>
+    <t>Magnetism</t>
+  </si>
+  <si>
+    <t>在每回合开始时，增加一张随机无色牌到你的手牌。</t>
+  </si>
+  <si>
+    <t>战略大师</t>
+  </si>
+  <si>
+    <t>Master of Strategy</t>
+  </si>
+  <si>
+    <t>乱战</t>
+  </si>
+  <si>
+    <t>Mayhem</t>
+  </si>
+  <si>
+    <t>在你的回合开始时，打出你抽牌堆顶部的牌。</t>
+  </si>
+  <si>
+    <t>羽化</t>
+  </si>
+  <si>
+    <t>Metamorphosis</t>
+  </si>
+  <si>
+    <t>在你的抽牌堆中加入3张随机攻击牌。</t>
+  </si>
+  <si>
+    <t>在你的抽牌堆中加入5张随机攻击牌。</t>
+  </si>
+  <si>
+    <t>奇迹</t>
+  </si>
+  <si>
+    <t>Miracle</t>
+  </si>
+  <si>
+    <t>获得[P]。</t>
+  </si>
+  <si>
+    <t>获得[P][P]。</t>
+  </si>
+  <si>
+    <t>心灵震慑</t>
+  </si>
+  <si>
+    <t>Mind Blast</t>
+  </si>
+  <si>
+    <t>造成你抽牌堆中剩余牌数的伤害。</t>
+  </si>
+  <si>
+    <t>欧米伽</t>
+  </si>
+  <si>
+    <t>Omega</t>
+  </si>
+  <si>
+    <t>在你的回合结束时，对所有敌人造成50点伤害。</t>
+  </si>
+  <si>
+    <t>在你的回合结束时，对所有敌人造成60点伤害。</t>
+  </si>
+  <si>
+    <t>万能药</t>
+  </si>
+  <si>
+    <t>Panacea</t>
+  </si>
+  <si>
+    <t>神气制胜</t>
+  </si>
+  <si>
+    <t>Panache</t>
+  </si>
+  <si>
+    <t>你每在同个回合内打出5张牌，就对所有敌人造成10点伤害。</t>
+  </si>
+  <si>
+    <t>你每在同个回合内打出5张牌，就对所有敌人造成14点伤害。</t>
+  </si>
+  <si>
+    <t>应急按钮</t>
+  </si>
+  <si>
+    <t>Panic Button</t>
+  </si>
+  <si>
+    <t>你在接下来2回合内无法再从卡牌中获得格挡。</t>
+  </si>
+  <si>
+    <t>净化</t>
+  </si>
+  <si>
+    <t>Purity</t>
+  </si>
+  <si>
+    <t>仪式匕首</t>
+  </si>
+  <si>
+    <t>Ritual Dagger</t>
+  </si>
+  <si>
+    <t>残虐天性</t>
+  </si>
+  <si>
+    <t>Sadistic Nature</t>
+  </si>
+  <si>
+    <t>每当你对一名敌人造成负面状态，使对方受到5点伤害。</t>
+  </si>
+  <si>
+    <t>每当你对一名敌人造成负面状态，使对方受到7点伤害。</t>
+  </si>
+  <si>
+    <t>平安</t>
+  </si>
+  <si>
+    <t>Safety</t>
+  </si>
+  <si>
+    <t>秘密技法</t>
+  </si>
+  <si>
+    <t>Secret Technique</t>
+  </si>
+  <si>
+    <t>从抽牌堆中选择一张技能牌放入你的手牌。</t>
+  </si>
+  <si>
+    <t>秘密武器</t>
+  </si>
+  <si>
+    <t>Secret Weapon</t>
+  </si>
+  <si>
+    <t>从抽牌堆中选择一张攻击牌放入你的手牌。</t>
+  </si>
+  <si>
+    <t>小刀</t>
+  </si>
+  <si>
+    <t>Shiv</t>
+  </si>
+  <si>
+    <t>造成4点伤害。</t>
+  </si>
+  <si>
+    <t>消耗</t>
+  </si>
+  <si>
+    <t>黏液</t>
+  </si>
+  <si>
+    <t>Slimed</t>
+  </si>
+  <si>
+    <t>惩恶</t>
+  </si>
+  <si>
+    <t>Smite</t>
+  </si>
+  <si>
+    <t>迅捷打击</t>
+  </si>
+  <si>
+    <t>Swift Strike</t>
+  </si>
+  <si>
+    <t>炸弹</t>
+  </si>
+  <si>
+    <t>The Bomb</t>
+  </si>
+  <si>
+    <t>在3回合结束后，对所有敌人造成40点伤害。</t>
+  </si>
+  <si>
+    <t>在3回合结束后，对所有敌人造成50点伤害。</t>
+  </si>
+  <si>
+    <t>深谋远虑</t>
+  </si>
+  <si>
+    <t>Thinking Ahead</t>
+  </si>
+  <si>
+    <t>抽2张牌，然后将手牌中的一张牌放到你抽牌堆的顶端。</t>
+  </si>
+  <si>
+    <t>以暴易暴</t>
+  </si>
+  <si>
+    <t>Through Violence</t>
+  </si>
+  <si>
+    <t>造成30点伤害。</t>
+  </si>
+  <si>
+    <t>转化</t>
+  </si>
+  <si>
+    <t>Transmutation</t>
+  </si>
+  <si>
+    <t>在你的手牌中加入X张随机无色牌。</t>
+  </si>
+  <si>
+    <t>它们在本回合的耗能变为0。</t>
+  </si>
+  <si>
+    <t>绊倒</t>
+  </si>
+  <si>
+    <t>Trip</t>
+  </si>
+  <si>
+    <t>暴力</t>
+  </si>
+  <si>
+    <t>Violence</t>
+  </si>
+  <si>
+    <t>随机将你抽牌堆中3张攻击牌加入你的手牌。</t>
+  </si>
+  <si>
+    <t>随机将你抽牌堆中4张攻击牌加入你的手牌。</t>
+  </si>
+  <si>
+    <t>虚空</t>
+  </si>
+  <si>
+    <t>Void</t>
+  </si>
+  <si>
+    <t>抽到这张牌时失去1点能量。</t>
+  </si>
+  <si>
+    <t>伤口</t>
+  </si>
+  <si>
+    <t>Wound</t>
+  </si>
+  <si>
+    <r>
+      <t>在本场战斗中</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>升级你的所有牌。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>将一张</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>欧米伽放入你的抽牌堆中。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>不能被打出</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>让一名敌人在本回合内失去9点</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>力量。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>让一名敌人在本回合内失去15点</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>力量。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>获得2点</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>格挡。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>获得4点</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>格挡。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>获得6点</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>格挡。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>斩杀</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>时，获得20金币。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>斩杀</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>时，获得25金币。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>保留</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>获得1层</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>人工制品。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>获得2层</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>人工制品。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>从手牌中选择最多3张牌</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>消耗。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>从手牌中选择最多5张牌</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>消耗。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>斩杀</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>时，它在本局游戏中的伤害永久性增加3。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>斩杀</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>时，它在本局游戏中的伤害永久性增加5。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>在你的手牌中放入X张</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>升级过的随机无色牌。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>给予2层</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>易伤 。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>给予所有敌人2层</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>易伤。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ok</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2593,6 +3425,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2644,7 +3483,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2683,12 +3522,344 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFA2A9B1"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFA2A9B1"/>
+        </right>
+        <bottom style="medium">
+          <color rgb="FFA2A9B1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3004,7 +4175,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}" name="表1" displayName="表1" ref="A1:I132" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A605A88E-2CA9-4C62-96A8-159FB74257BD}" name="表4" displayName="表4" ref="A1:J106" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2" tableBorderDxfId="12">
+  <autoFilter ref="A1:J106" xr:uid="{A605A88E-2CA9-4C62-96A8-159FB74257BD}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{537C478B-F25C-48D2-A47A-FE83482A04CB}" name="名称" dataDxfId="11" dataCellStyle="超链接"/>
+    <tableColumn id="2" xr3:uid="{C6096DE0-266A-4413-A945-F560C0C783E9}" name="英文名称" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{52504C75-8D32-4CC6-9823-5FBE16459E75}" name="颜色" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C9572819-8A36-472F-B242-1262100B4C3F}" name="稀有度" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{3FC8295B-0E7C-4F08-A755-2EC63F777A6A}" name="类型" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{364007B5-556C-4D91-A3A2-A84B37BE65B2}" name="耗能" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{E27D4591-194B-410C-81D9-6C7B7D6C561A}" name="描述" dataDxfId="5" dataCellStyle="超链接"/>
+    <tableColumn id="8" xr3:uid="{6AD0342B-DAD3-4AB2-8895-5729DE28AD00}" name="升级耗能" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{8A689ADC-343C-4E73-AA80-C16E9C1CFCB9}" name="升级描述" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{A584E3BD-E0B0-40E1-8B43-841C2DB2A160}" name="ok？" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}" name="表1" displayName="表1" ref="A1:I132" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" tableBorderDxfId="22">
   <autoFilter ref="A1:I132" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}">
     <filterColumn colId="2">
       <filters>
@@ -3018,15 +4208,15 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{B6135FF2-C395-418D-8485-BC72711025F4}" name="名称" dataDxfId="8" dataCellStyle="超链接"/>
-    <tableColumn id="2" xr3:uid="{1B074D24-1599-4FC5-A236-BF6B4242EFE7}" name="英文名称" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{D865C2BE-A956-42B5-BB5A-7AE351AE07B6}" name="稀有度" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{3C3D501F-CAE0-4744-BAB5-1D7A745601E9}" name="类型" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{ABA971A8-6C44-4C6E-8C23-33561D5A983E}" name="耗能" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{9E82D8B0-ABBA-41BA-B169-92A89727DFAA}" name="描述" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{18D4BFF4-3B10-42F7-9F65-B8C97E7E712B}" name="升级耗能" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{E3C19DBB-A684-4385-8660-C5C4F8346A07}" name="升级描述" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{63182BFF-0D89-46A8-A878-6A9CEBB8D964}" name="ok？" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B6135FF2-C395-418D-8485-BC72711025F4}" name="名称" dataDxfId="21" dataCellStyle="超链接"/>
+    <tableColumn id="2" xr3:uid="{1B074D24-1599-4FC5-A236-BF6B4242EFE7}" name="英文名称" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{D865C2BE-A956-42B5-BB5A-7AE351AE07B6}" name="稀有度" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{3C3D501F-CAE0-4744-BAB5-1D7A745601E9}" name="类型" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{ABA971A8-6C44-4C6E-8C23-33561D5A983E}" name="耗能" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{9E82D8B0-ABBA-41BA-B169-92A89727DFAA}" name="描述" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{18D4BFF4-3B10-42F7-9F65-B8C97E7E712B}" name="升级耗能" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{E3C19DBB-A684-4385-8660-C5C4F8346A07}" name="升级描述" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{63182BFF-0D89-46A8-A878-6A9CEBB8D964}" name="ok？" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4171,6 +5361,2634 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF66D3D-5735-4513-99A1-DFDBFEA9E050}">
+  <dimension ref="A1:J106"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="16">
+        <v>2</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="H2" s="16">
+        <v>1</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="J2" s="20"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="16">
+        <v>0</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="H4" s="16">
+        <v>0</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="J4" s="18"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H5" s="16"/>
+      <c r="I5" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="16">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" s="16">
+        <v>1</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="H7" s="16"/>
+      <c r="I7" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="16">
+        <v>2</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="H8" s="16">
+        <v>1</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="J8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H10" s="16">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="J10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="F11" s="16">
+        <v>-2</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="H11" s="16">
+        <v>-2</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="J11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="J12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="16">
+        <v>2</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="H13" s="16">
+        <v>2</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="H16" s="16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="I17" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="F18" s="16">
+        <v>-2</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="H18" s="16">
+        <v>-2</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H19" s="16"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="16">
+        <v>0</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="H20" s="16">
+        <v>0</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="H21" s="16"/>
+      <c r="I21" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="16">
+        <v>1</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="H22" s="16">
+        <v>1</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A23" s="13"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="H23" s="16"/>
+      <c r="I23" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H24" s="16"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="16">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H25" s="16">
+        <v>0</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="J25" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A26" s="13"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H26" s="16"/>
+      <c r="I26" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="13"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H27" s="16"/>
+      <c r="I27" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="H28" s="16">
+        <v>0</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="16">
+        <v>1</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="H29" s="16">
+        <v>1</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>442</v>
+      </c>
+      <c r="J29" s="18"/>
+    </row>
+    <row r="30" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H30" s="16">
+        <v>0</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>565</v>
+      </c>
+      <c r="J30" s="20"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="13"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="H31" s="16"/>
+      <c r="I31" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="16">
+        <v>0</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="H32" s="16">
+        <v>0</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="13"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="H33" s="16"/>
+      <c r="I33" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="J33" s="18"/>
+    </row>
+    <row r="34" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="16">
+        <v>0</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="H34" s="16">
+        <v>0</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>452</v>
+      </c>
+      <c r="J34" s="18"/>
+    </row>
+    <row r="35" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A35" s="13"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="H35" s="16"/>
+      <c r="I35" s="18" t="s">
+        <v>453</v>
+      </c>
+      <c r="J35" s="18"/>
+    </row>
+    <row r="36" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="16">
+        <v>1</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="H36" s="16">
+        <v>1</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="J36" s="18"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="13"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H37" s="16"/>
+      <c r="I37" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J37" s="20"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="13"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H38" s="16"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="18"/>
+    </row>
+    <row r="39" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="16">
+        <v>0</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="H39" s="16">
+        <v>0</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="J39" s="20"/>
+    </row>
+    <row r="40" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="16">
+        <v>2</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H40" s="16">
+        <v>2</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="J40" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A41" s="13"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="H41" s="16"/>
+      <c r="I41" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="J41" s="20"/>
+    </row>
+    <row r="42" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="16">
+        <v>0</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="H42" s="16">
+        <v>0</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="J42" s="18"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="16">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="H43" s="16">
+        <v>0</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="J43" s="20"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="13"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H44" s="16"/>
+      <c r="I44" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J44" s="18"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="13"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H45" s="16"/>
+      <c r="I45" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J45" s="20"/>
+    </row>
+    <row r="46" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="16">
+        <v>0</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H46" s="16">
+        <v>0</v>
+      </c>
+      <c r="I46" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="J46" s="18"/>
+    </row>
+    <row r="47" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A47" s="13"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H47" s="16"/>
+      <c r="I47" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="J47" s="20"/>
+    </row>
+    <row r="48" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="16">
+        <v>0</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="H48" s="16">
+        <v>0</v>
+      </c>
+      <c r="I48" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="J48" s="18"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="13"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H49" s="16"/>
+      <c r="I49" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J49" s="20"/>
+    </row>
+    <row r="50" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="16">
+        <v>1</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="H50" s="16">
+        <v>0</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="J50" s="18"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="13"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H51" s="16"/>
+      <c r="I51" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J51" s="20"/>
+    </row>
+    <row r="52" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" s="16">
+        <v>2</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="H52" s="16">
+        <v>1</v>
+      </c>
+      <c r="I52" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="J52" s="18"/>
+    </row>
+    <row r="53" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="16">
+        <v>0</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H53" s="16">
+        <v>0</v>
+      </c>
+      <c r="I53" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J53" s="18"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="13"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H54" s="16"/>
+      <c r="I54" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J54" s="20"/>
+    </row>
+    <row r="55" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" s="16">
+        <v>2</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="H55" s="16">
+        <v>1</v>
+      </c>
+      <c r="I55" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="J55" s="18"/>
+    </row>
+    <row r="56" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="16">
+        <v>2</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="H56" s="16">
+        <v>2</v>
+      </c>
+      <c r="I56" s="18" t="s">
+        <v>487</v>
+      </c>
+      <c r="J56" s="18"/>
+    </row>
+    <row r="57" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A57" s="13"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="H57" s="16"/>
+      <c r="I57" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="J57" s="18"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="13"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H58" s="16"/>
+      <c r="I58" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J58" s="20"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="16">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="H59" s="16">
+        <v>0</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="J59" s="20"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="13"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="H60" s="16"/>
+      <c r="I60" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="J60" s="18"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="13"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H61" s="16"/>
+      <c r="I61" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J61" s="20"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="16">
+        <v>2</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H62" s="16">
+        <v>1</v>
+      </c>
+      <c r="I62" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="J62" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A63" s="13"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="H63" s="16"/>
+      <c r="I63" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="J63" s="18"/>
+    </row>
+    <row r="64" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" s="16">
+        <v>3</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="H64" s="16">
+        <v>3</v>
+      </c>
+      <c r="I64" s="18" t="s">
+        <v>498</v>
+      </c>
+      <c r="J64" s="18"/>
+    </row>
+    <row r="65" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="16">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="H65" s="16">
+        <v>0</v>
+      </c>
+      <c r="I65" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="J65" s="20"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="13"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H66" s="16"/>
+      <c r="I66" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J66" s="20"/>
+    </row>
+    <row r="67" spans="1:10" ht="92.4" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" s="16">
+        <v>0</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="H67" s="16">
+        <v>0</v>
+      </c>
+      <c r="I67" s="18" t="s">
+        <v>504</v>
+      </c>
+      <c r="J67" s="18"/>
+    </row>
+    <row r="68" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="16">
+        <v>0</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="H68" s="16">
+        <v>0</v>
+      </c>
+      <c r="I68" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="J68" s="20"/>
+    </row>
+    <row r="69" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A69" s="13"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="H69" s="16"/>
+      <c r="I69" s="18" t="s">
+        <v>507</v>
+      </c>
+      <c r="J69" s="18"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="13"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H70" s="16"/>
+      <c r="I70" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J70" s="20"/>
+    </row>
+    <row r="71" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="16">
+        <v>0</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="H71" s="16">
+        <v>0</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>573</v>
+      </c>
+      <c r="J71" s="20"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="13"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H72" s="16"/>
+      <c r="I72" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J72" s="20"/>
+    </row>
+    <row r="73" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A73" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="16">
+        <v>1</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="H73" s="16">
+        <v>1</v>
+      </c>
+      <c r="I73" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="J73" s="18"/>
+    </row>
+    <row r="74" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="A74" s="13"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="H74" s="16"/>
+      <c r="I74" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="J74" s="20"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="13"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H75" s="16"/>
+      <c r="I75" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J75" s="20"/>
+    </row>
+    <row r="76" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A76" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F76" s="16">
+        <v>0</v>
+      </c>
+      <c r="G76" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="H76" s="16">
+        <v>0</v>
+      </c>
+      <c r="I76" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="J76" s="18"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D77" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="16">
+        <v>1</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="H77" s="16">
+        <v>1</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="J77" s="20"/>
+    </row>
+    <row r="78" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A78" s="13"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H78" s="16"/>
+      <c r="I78" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="J78" s="20"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="13"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H79" s="16"/>
+      <c r="I79" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J79" s="20"/>
+    </row>
+    <row r="80" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A80" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="B80" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" s="16">
+        <v>0</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="H80" s="16">
+        <v>0</v>
+      </c>
+      <c r="I80" s="18" t="s">
+        <v>520</v>
+      </c>
+      <c r="J80" s="18"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="13"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H81" s="16"/>
+      <c r="I81" s="18"/>
+      <c r="J81" s="18"/>
+    </row>
+    <row r="82" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A82" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="B82" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="16">
+        <v>0</v>
+      </c>
+      <c r="G82" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="H82" s="16">
+        <v>0</v>
+      </c>
+      <c r="I82" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="J82" s="18"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="13"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H83" s="16"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+    </row>
+    <row r="84" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A84" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="B84" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="16">
+        <v>0</v>
+      </c>
+      <c r="G84" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="H84" s="16">
+        <v>0</v>
+      </c>
+      <c r="I84" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="J84" s="18"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="13"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="16"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H85" s="16"/>
+      <c r="I85" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="J85" s="20"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="13" t="s">
+        <v>528</v>
+      </c>
+      <c r="B86" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E86" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="F86" s="16">
+        <v>1</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H86" s="16">
+        <v>0</v>
+      </c>
+      <c r="I86" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="J86" s="18"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E87" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="16">
+        <v>1</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="H87" s="16">
+        <v>1</v>
+      </c>
+      <c r="I87" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="J87" s="20"/>
+    </row>
+    <row r="88" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A88" s="13"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H88" s="16"/>
+      <c r="I88" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="J88" s="18"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="13"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H89" s="16"/>
+      <c r="I89" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J89" s="20"/>
+    </row>
+    <row r="90" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A90" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="B90" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="16">
+        <v>0</v>
+      </c>
+      <c r="G90" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="H90" s="16">
+        <v>0</v>
+      </c>
+      <c r="I90" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="J90" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A91" s="13" t="s">
+        <v>534</v>
+      </c>
+      <c r="B91" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E91" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" s="16">
+        <v>2</v>
+      </c>
+      <c r="G91" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="H91" s="16">
+        <v>2</v>
+      </c>
+      <c r="I91" s="18" t="s">
+        <v>537</v>
+      </c>
+      <c r="J91" s="18"/>
+    </row>
+    <row r="92" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A92" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D92" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E92" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="16">
+        <v>0</v>
+      </c>
+      <c r="G92" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="H92" s="16">
+        <v>0</v>
+      </c>
+      <c r="I92" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="J92" s="18"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="13"/>
+      <c r="B93" s="16"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="16"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H93" s="16"/>
+      <c r="I93" s="18"/>
+      <c r="J93" s="18"/>
+    </row>
+    <row r="94" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A94" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D94" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E94" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="16">
+        <v>0</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="H94" s="16">
+        <v>0</v>
+      </c>
+      <c r="I94" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="J94" s="20"/>
+    </row>
+    <row r="95" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A95" s="13"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="16"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H95" s="16"/>
+      <c r="I95" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="J95" s="18"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="13"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="16"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H96" s="16"/>
+      <c r="I96" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J96" s="20"/>
+    </row>
+    <row r="97" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A97" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="B97" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="C97" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D97" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" s="16">
+        <v>-1</v>
+      </c>
+      <c r="G97" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="H97" s="16">
+        <v>-1</v>
+      </c>
+      <c r="I97" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="J97" s="20"/>
+    </row>
+    <row r="98" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A98" s="13"/>
+      <c r="B98" s="16"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="16"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="H98" s="16"/>
+      <c r="I98" s="18" t="s">
+        <v>547</v>
+      </c>
+      <c r="J98" s="18"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="13"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H99" s="16"/>
+      <c r="I99" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J99" s="20"/>
+    </row>
+    <row r="100" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A100" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F100" s="16">
+        <v>0</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="H100" s="16">
+        <v>0</v>
+      </c>
+      <c r="I100" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="J100" s="20"/>
+    </row>
+    <row r="101" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A101" s="13" t="s">
+        <v>550</v>
+      </c>
+      <c r="B101" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="16">
+        <v>0</v>
+      </c>
+      <c r="G101" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="H101" s="16">
+        <v>0</v>
+      </c>
+      <c r="I101" s="18" t="s">
+        <v>553</v>
+      </c>
+      <c r="J101" s="18"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="13"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H102" s="16"/>
+      <c r="I102" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J102" s="20"/>
+    </row>
+    <row r="103" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A103" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="B103" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E103" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="F103" s="16">
+        <v>-2</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="H103" s="16">
+        <v>-2</v>
+      </c>
+      <c r="I103" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="J103" s="18"/>
+    </row>
+    <row r="104" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A104" s="13"/>
+      <c r="B104" s="16"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="H104" s="16"/>
+      <c r="I104" s="18"/>
+      <c r="J104" s="18"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="13"/>
+      <c r="B105" s="16"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="16"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H105" s="16"/>
+      <c r="I105" s="18"/>
+      <c r="J105" s="18"/>
+    </row>
+    <row r="106" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A106" s="13" t="s">
+        <v>557</v>
+      </c>
+      <c r="B106" s="18" t="s">
+        <v>558</v>
+      </c>
+      <c r="C106" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="D106" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="E106" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="F106" s="18">
+        <v>-2</v>
+      </c>
+      <c r="G106" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="H106" s="18">
+        <v>-2</v>
+      </c>
+      <c r="I106" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="J106" s="18"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" tooltip="神化" display="https://sts.huijiwiki.com/wiki/%E7%A5%9E%E5%8C%96" xr:uid="{0B9A7FBA-BDFC-43AE-9CC8-AE9DF7D5B105}"/>
+    <hyperlink ref="G2" r:id="rId2" tooltip="升级" display="https://sts.huijiwiki.com/wiki/%E5%8D%87%E7%BA%A7" xr:uid="{FA0EDDD8-E5B4-4251-829D-525B4C3F202D}"/>
+    <hyperlink ref="G3" r:id="rId3" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{8A4CDD1A-E7DC-4EC6-A116-5D7B68BC5F31}"/>
+    <hyperlink ref="I2" r:id="rId4" tooltip="升级" display="https://sts.huijiwiki.com/wiki/%E5%8D%87%E7%BA%A7" xr:uid="{A755DFD2-D459-4F32-965E-499F70EC6EBF}"/>
+    <hyperlink ref="I3" r:id="rId5" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{213ECABA-3FB7-4756-B995-5E674D5D3C9A}"/>
+    <hyperlink ref="A4" r:id="rId6" tooltip="包扎" display="https://sts.huijiwiki.com/wiki/%E5%8C%85%E6%89%8E" xr:uid="{39AB81D3-3056-4EA5-A0C6-FDDF852D275C}"/>
+    <hyperlink ref="G5" r:id="rId7" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{A7C18BDD-8553-4F9C-80C4-891DD4954AEC}"/>
+    <hyperlink ref="I5" r:id="rId8" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{0AC79CB4-D58B-4C07-B704-26AAC57EE707}"/>
+    <hyperlink ref="A6" r:id="rId9" tooltip="噬咬" display="https://sts.huijiwiki.com/wiki/%E5%99%AC%E5%92%AC" xr:uid="{FE344B0B-A9E8-4454-99E2-576004DE426A}"/>
+    <hyperlink ref="A8" r:id="rId10" tooltip="贝塔" display="https://sts.huijiwiki.com/wiki/%E8%B4%9D%E5%A1%94" xr:uid="{8ACD8C3A-E045-4175-A063-F49C30F3277D}"/>
+    <hyperlink ref="G8" r:id="rId11" tooltip="欧米伽" display="https://sts.huijiwiki.com/wiki/%E6%AC%A7%E7%B1%B3%E4%BC%BD" xr:uid="{02347664-109E-44FA-BE60-1E2235441F09}"/>
+    <hyperlink ref="G9" r:id="rId12" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{5237A280-1E8F-473A-9FF3-13C8F356A898}"/>
+    <hyperlink ref="I8" r:id="rId13" tooltip="欧米伽" display="https://sts.huijiwiki.com/wiki/%E6%AC%A7%E7%B1%B3%E4%BC%BD" xr:uid="{BDCDC3F1-54B8-409E-BB7F-D129848E973F}"/>
+    <hyperlink ref="I9" r:id="rId14" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{A0EC0ABB-7E08-43BE-96C6-F96B6105B17B}"/>
+    <hyperlink ref="A10" r:id="rId15" tooltip="致盲" display="https://sts.huijiwiki.com/wiki/%E8%87%B4%E7%9B%B2" xr:uid="{B32B2127-3FAC-42E0-A8E7-5062622198E6}"/>
+    <hyperlink ref="G10" r:id="rId16" tooltip="虚弱" display="https://sts.huijiwiki.com/wiki/%E8%99%9A%E5%BC%B1" xr:uid="{F2597362-944B-4665-A6D0-82D4CCBD4A5C}"/>
+    <hyperlink ref="I10" r:id="rId17" tooltip="虚弱" display="https://sts.huijiwiki.com/wiki/%E8%99%9A%E5%BC%B1" xr:uid="{42834626-7D6B-40E5-8520-A27575691BA0}"/>
+    <hyperlink ref="A11" r:id="rId18" tooltip="灼伤" display="https://sts.huijiwiki.com/wiki/%E7%81%BC%E4%BC%A4" xr:uid="{181B7C61-0BA6-4DB3-8725-B0BEC97124C1}"/>
+    <hyperlink ref="G11" r:id="rId19" tooltip="不能被打出" display="https://sts.huijiwiki.com/wiki/%E4%B8%8D%E8%83%BD%E8%A2%AB%E6%89%93%E5%87%BA" xr:uid="{5234D9AC-E326-4228-9B5E-F0E2B322AFB4}"/>
+    <hyperlink ref="I11" r:id="rId20" tooltip="不能被打出" display="https://sts.huijiwiki.com/wiki/%E4%B8%8D%E8%83%BD%E8%A2%AB%E6%89%93%E5%87%BA" xr:uid="{CB82BF15-BF84-4E04-AA53-A20AEDAC60C6}"/>
+    <hyperlink ref="A13" r:id="rId21" tooltip="结茧" display="https://sts.huijiwiki.com/wiki/%E7%BB%93%E8%8C%A7" xr:uid="{338AD127-C3A4-41ED-88BB-2231F681BE5A}"/>
+    <hyperlink ref="G15" r:id="rId22" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{61AFAE6A-F885-4EF4-B8F0-CE96CE1171C7}"/>
+    <hyperlink ref="I15" r:id="rId23" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{786EDCF8-040F-4C79-906A-45A58DA0651E}"/>
+    <hyperlink ref="A16" r:id="rId24" tooltip="黑暗镣铐" display="https://sts.huijiwiki.com/wiki/%E9%BB%91%E6%9A%97%E9%95%A3%E9%93%90" xr:uid="{D2A0387D-B544-48D5-A73F-6373CAD0F735}"/>
+    <hyperlink ref="G16" r:id="rId25" tooltip="力量" display="https://sts.huijiwiki.com/wiki/%E5%8A%9B%E9%87%8F" xr:uid="{76F9B356-67CF-403B-A7BD-E050FA91166E}"/>
+    <hyperlink ref="G17" r:id="rId26" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{2E8E4CDD-B4E0-48CC-9DE4-C37998B9D22D}"/>
+    <hyperlink ref="I16" r:id="rId27" tooltip="力量" display="https://sts.huijiwiki.com/wiki/%E5%8A%9B%E9%87%8F" xr:uid="{9927EA1E-92CC-4A0D-9349-4FCC4B7FE7EB}"/>
+    <hyperlink ref="I17" r:id="rId28" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{21F86416-597D-42A8-B002-F2D181EA77BA}"/>
+    <hyperlink ref="A18" r:id="rId29" tooltip="晕眩" display="https://sts.huijiwiki.com/wiki/%E6%99%95%E7%9C%A9" xr:uid="{FAED629C-E06F-417F-916F-ED6A57B03B54}"/>
+    <hyperlink ref="G18" r:id="rId30" tooltip="不能被打出" display="https://sts.huijiwiki.com/wiki/%E4%B8%8D%E8%83%BD%E8%A2%AB%E6%89%93%E5%87%BA" xr:uid="{3E3499EF-622B-42EE-BA0D-199ECDA942BC}"/>
+    <hyperlink ref="G19" r:id="rId31" tooltip="虚无" display="https://sts.huijiwiki.com/wiki/%E8%99%9A%E6%97%A0" xr:uid="{014FF59A-91C5-4F77-BA3B-AAEC8C0282B3}"/>
+    <hyperlink ref="A20" r:id="rId32" tooltip="深呼吸" display="https://sts.huijiwiki.com/wiki/%E6%B7%B1%E5%91%BC%E5%90%B8" xr:uid="{C7258EE5-29E4-4367-8711-E1B25562FD9B}"/>
+    <hyperlink ref="A22" r:id="rId33" tooltip="发现" display="https://sts.huijiwiki.com/wiki/%E5%8F%91%E7%8E%B0" xr:uid="{688B4F13-A2B8-4CF5-BC8F-5363D36957C2}"/>
+    <hyperlink ref="G24" r:id="rId34" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{B7CDEF71-7E29-4144-B2B9-3FA806962444}"/>
+    <hyperlink ref="A25" r:id="rId35" tooltip="闪亮登场" display="https://sts.huijiwiki.com/wiki/%E9%97%AA%E4%BA%AE%E7%99%BB%E5%9C%BA" xr:uid="{92E8BB9A-1C01-4C88-A648-C2B7AECCA752}"/>
+    <hyperlink ref="G25" r:id="rId36" tooltip="固有" display="https://sts.huijiwiki.com/wiki/%E5%9B%BA%E6%9C%89" xr:uid="{97665EA2-5EAB-4DE7-A3FA-B44E5456BE57}"/>
+    <hyperlink ref="G27" r:id="rId37" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{EC41922F-D19B-4330-9091-DE29B45F9F55}"/>
+    <hyperlink ref="I25" r:id="rId38" tooltip="固有" display="https://sts.huijiwiki.com/wiki/%E5%9B%BA%E6%9C%89" xr:uid="{53BB63C3-443B-46BB-978C-D783527BDD92}"/>
+    <hyperlink ref="I27" r:id="rId39" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{F2315A98-FD86-4E2B-A767-DA125E7EEA2A}"/>
+    <hyperlink ref="A28" r:id="rId40" tooltip="开悟" display="https://sts.huijiwiki.com/wiki/%E5%BC%80%E6%82%9F" xr:uid="{86689BE8-F4E1-4978-B02C-0E019CA0C1D4}"/>
+    <hyperlink ref="A29" r:id="rId41" tooltip="灭除之刃" display="https://sts.huijiwiki.com/wiki/%E7%81%AD%E9%99%A4%E4%B9%8B%E5%88%83" xr:uid="{631F828E-7A53-43ED-8296-4CB7ABB64DF3}"/>
+    <hyperlink ref="A30" r:id="rId42" tooltip="妙计" display="https://sts.huijiwiki.com/wiki/%E5%A6%99%E8%AE%A1" xr:uid="{801968DC-85FE-453F-833A-29659A789297}"/>
+    <hyperlink ref="G30" r:id="rId43" tooltip="格挡" display="https://sts.huijiwiki.com/wiki/%E6%A0%BC%E6%8C%A1" xr:uid="{15198A5C-24BB-4EC7-8A3E-866E4FAC2C1F}"/>
+    <hyperlink ref="I30" r:id="rId44" tooltip="格挡" display="https://sts.huijiwiki.com/wiki/%E6%A0%BC%E6%8C%A1" xr:uid="{824F4A35-563B-466F-BEE5-FCF8A1D99F75}"/>
+    <hyperlink ref="A32" r:id="rId45" tooltip="亮剑" display="https://sts.huijiwiki.com/wiki/%E4%BA%AE%E5%89%91" xr:uid="{FFC1034F-7C1A-4239-B3EE-B4B5FFB2C1BA}"/>
+    <hyperlink ref="A34" r:id="rId46" tooltip="预谋" display="https://sts.huijiwiki.com/wiki/%E9%A2%84%E8%B0%8B" xr:uid="{945F0E23-68D1-4998-B6E0-1352D91E970D}"/>
+    <hyperlink ref="A36" r:id="rId47" tooltip="灵体" display="https://sts.huijiwiki.com/wiki/%E7%81%B5%E4%BD%93" xr:uid="{2C4CED5D-AA93-4C2F-BCB2-0AED28E44C42}"/>
+    <hyperlink ref="G37" r:id="rId48" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{6F114989-5CC7-416C-B93A-4ECC55E4B672}"/>
+    <hyperlink ref="G38" r:id="rId49" tooltip="虚无" display="https://sts.huijiwiki.com/wiki/%E8%99%9A%E6%97%A0" xr:uid="{4CC3E31E-C82D-47BE-B8EF-BD6B882DD27E}"/>
+    <hyperlink ref="I37" r:id="rId50" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{2BFBE317-7FAC-4706-8804-4B3F1E455AA3}"/>
+    <hyperlink ref="A39" r:id="rId51" tooltip="优秀直觉" display="https://sts.huijiwiki.com/wiki/%E4%BC%98%E7%A7%80%E7%9B%B4%E8%A7%89" xr:uid="{6BEA2447-A8A5-4A69-A6C8-F12DFD554A79}"/>
+    <hyperlink ref="G39" r:id="rId52" tooltip="格挡" display="https://sts.huijiwiki.com/wiki/%E6%A0%BC%E6%8C%A1" xr:uid="{200C7122-8780-4F49-8A55-87F73F04345C}"/>
+    <hyperlink ref="I39" r:id="rId53" tooltip="格挡" display="https://sts.huijiwiki.com/wiki/%E6%A0%BC%E6%8C%A1" xr:uid="{37A8B2A1-DC04-479D-9663-87F9796C627B}"/>
+    <hyperlink ref="A40" r:id="rId54" tooltip="贪婪之手" display="https://sts.huijiwiki.com/wiki/%E8%B4%AA%E5%A9%AA%E4%B9%8B%E6%89%8B" xr:uid="{24764DC3-2B1E-40CD-94D4-60D76DD14AEE}"/>
+    <hyperlink ref="G41" r:id="rId55" tooltip="斩杀" display="https://sts.huijiwiki.com/wiki/%E6%96%A9%E6%9D%80" xr:uid="{5173BF50-EE78-4B5F-865E-B3FA92CE2B38}"/>
+    <hyperlink ref="I41" r:id="rId56" tooltip="斩杀" display="https://sts.huijiwiki.com/wiki/%E6%96%A9%E6%9D%80" xr:uid="{6B67DF02-EC52-484F-8140-EF4A1F132370}"/>
+    <hyperlink ref="A42" r:id="rId57" tooltip="急躁" display="https://sts.huijiwiki.com/wiki/%E6%80%A5%E8%BA%81" xr:uid="{E21759F1-0ED6-446F-ACFB-8E487C45D47D}"/>
+    <hyperlink ref="A43" r:id="rId58" tooltip="洞见" display="https://sts.huijiwiki.com/wiki/%E6%B4%9E%E8%A7%81" xr:uid="{3387BF03-4541-410B-B29A-29010A6AE9A6}"/>
+    <hyperlink ref="G43" r:id="rId59" tooltip="保留" display="https://sts.huijiwiki.com/wiki/%E4%BF%9D%E7%95%99" xr:uid="{7D172EE0-83BD-42D0-8774-C649B1A395BB}"/>
+    <hyperlink ref="G45" r:id="rId60" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{BA32FCBB-3F0C-4073-A8B3-21BBDDC8BC85}"/>
+    <hyperlink ref="I43" r:id="rId61" tooltip="保留" display="https://sts.huijiwiki.com/wiki/%E4%BF%9D%E7%95%99" xr:uid="{580F6F89-DDFF-43B9-B343-F0440ACD7231}"/>
+    <hyperlink ref="I45" r:id="rId62" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{738310A8-1EAE-46CD-9146-C94F7767A2AB}"/>
+    <hyperlink ref="A46" r:id="rId63" tooltip="J.A.X." display="https://sts.huijiwiki.com/wiki/J.A.X." xr:uid="{AB4A6696-4158-4061-9F87-1C949D87F4B6}"/>
+    <hyperlink ref="G47" r:id="rId64" tooltip="力量" display="https://sts.huijiwiki.com/wiki/%E5%8A%9B%E9%87%8F" xr:uid="{2FE98082-344B-4586-BC24-48974623ACCD}"/>
+    <hyperlink ref="I47" r:id="rId65" tooltip="力量" display="https://sts.huijiwiki.com/wiki/%E5%8A%9B%E9%87%8F" xr:uid="{D0A20199-71F2-4F17-A4A9-E764B23DA8E9}"/>
+    <hyperlink ref="A48" r:id="rId66" tooltip="花样百出" display="https://sts.huijiwiki.com/wiki/%E8%8A%B1%E6%A0%B7%E7%99%BE%E5%87%BA" xr:uid="{1CDF6BB4-7AFC-4169-BFDB-A668EFA9D221}"/>
+    <hyperlink ref="G49" r:id="rId67" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{E50C9036-6B1C-4012-BEE1-ADC552D284FB}"/>
+    <hyperlink ref="I49" r:id="rId68" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{FDD7E56A-55C6-48D4-AC1C-8DCA13E02D67}"/>
+    <hyperlink ref="A50" r:id="rId69" tooltip="疯狂" display="https://sts.huijiwiki.com/wiki/%E7%96%AF%E7%8B%82" xr:uid="{530F8D34-5998-4C43-A559-E85338F00E20}"/>
+    <hyperlink ref="G51" r:id="rId70" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{9D3405D3-F314-4795-88E6-C7C37D340393}"/>
+    <hyperlink ref="I51" r:id="rId71" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{62F41C3C-F42A-46FC-9E37-FE6289497604}"/>
+    <hyperlink ref="A52" r:id="rId72" tooltip="磁力" display="https://sts.huijiwiki.com/wiki/%E7%A3%81%E5%8A%9B" xr:uid="{9D8DB3D6-6A30-4D77-B6C2-4F61E03EAB85}"/>
+    <hyperlink ref="A53" r:id="rId73" tooltip="战略大师" display="https://sts.huijiwiki.com/wiki/%E6%88%98%E7%95%A5%E5%A4%A7%E5%B8%88" xr:uid="{2728FC3B-733F-4EDF-8B9A-A4C083EDE05D}"/>
+    <hyperlink ref="G54" r:id="rId74" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{AA215E9D-FBB8-43CD-BD58-101A3C91D341}"/>
+    <hyperlink ref="I54" r:id="rId75" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{24B61CC7-2A07-47FB-A516-6889604058B6}"/>
+    <hyperlink ref="A55" r:id="rId76" tooltip="乱战" display="https://sts.huijiwiki.com/wiki/%E4%B9%B1%E6%88%98" xr:uid="{8E50445D-3CAC-4C1D-B788-A5AAAF3A5A30}"/>
+    <hyperlink ref="A56" r:id="rId77" tooltip="羽化" display="https://sts.huijiwiki.com/wiki/%E7%BE%BD%E5%8C%96" xr:uid="{18DC6763-78BA-4AD7-8816-AA1BB1C02335}"/>
+    <hyperlink ref="G58" r:id="rId78" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{AC29F28B-FB03-4BDE-84EA-7546D79A41AD}"/>
+    <hyperlink ref="I58" r:id="rId79" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{6B007BE1-4744-44A5-BA19-51A161A11D6A}"/>
+    <hyperlink ref="A59" r:id="rId80" tooltip="奇迹" display="https://sts.huijiwiki.com/wiki/%E5%A5%87%E8%BF%B9" xr:uid="{422F4053-D5FB-4414-9AE3-C1D8E42FD143}"/>
+    <hyperlink ref="G59" r:id="rId81" tooltip="保留" display="https://sts.huijiwiki.com/wiki/%E4%BF%9D%E7%95%99" xr:uid="{96D9A763-E317-4632-921F-10F30190D121}"/>
+    <hyperlink ref="G61" r:id="rId82" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{2E9D5C6E-AA83-459E-A87B-55A8D1AC32E6}"/>
+    <hyperlink ref="I59" r:id="rId83" tooltip="保留" display="https://sts.huijiwiki.com/wiki/%E4%BF%9D%E7%95%99" xr:uid="{FF5E0A80-CB20-4ADE-8515-A491A0A25980}"/>
+    <hyperlink ref="I61" r:id="rId84" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{BD94EBCA-7FBF-4548-BEFF-6E8376F0309D}"/>
+    <hyperlink ref="A62" r:id="rId85" tooltip="心灵震慑" display="https://sts.huijiwiki.com/wiki/%E5%BF%83%E7%81%B5%E9%9C%87%E6%85%91" xr:uid="{92411D5C-2415-4ECB-BF61-F65B844814CF}"/>
+    <hyperlink ref="G62" r:id="rId86" tooltip="固有" display="https://sts.huijiwiki.com/wiki/%E5%9B%BA%E6%9C%89" xr:uid="{37B9FAAA-21B7-4C6F-A7DE-AD91E67608CF}"/>
+    <hyperlink ref="I62" r:id="rId87" tooltip="固有" display="https://sts.huijiwiki.com/wiki/%E5%9B%BA%E6%9C%89" xr:uid="{6CCB1E41-FE87-44CA-9C82-B851A5CB1F6F}"/>
+    <hyperlink ref="A64" r:id="rId88" tooltip="欧米伽" display="https://sts.huijiwiki.com/wiki/%E6%AC%A7%E7%B1%B3%E4%BC%BD" xr:uid="{A69739DE-567D-400F-A3E6-0631CBC5E281}"/>
+    <hyperlink ref="A65" r:id="rId89" tooltip="万能药" display="https://sts.huijiwiki.com/wiki/%E4%B8%87%E8%83%BD%E8%8D%AF" xr:uid="{77254162-708A-40D1-975A-232B12757202}"/>
+    <hyperlink ref="G65" r:id="rId90" tooltip="人工制品" display="https://sts.huijiwiki.com/wiki/%E4%BA%BA%E5%B7%A5%E5%88%B6%E5%93%81" xr:uid="{ACDE924C-60B7-448A-AD33-6797A9C91A3E}"/>
+    <hyperlink ref="G66" r:id="rId91" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{46038126-07CA-4C27-A432-0FB98C050E2E}"/>
+    <hyperlink ref="I65" r:id="rId92" tooltip="人工制品" display="https://sts.huijiwiki.com/wiki/%E4%BA%BA%E5%B7%A5%E5%88%B6%E5%93%81" xr:uid="{4FAA9608-554A-4811-966F-44A68EB79D01}"/>
+    <hyperlink ref="I66" r:id="rId93" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{C5B93E51-F919-41E8-8F3C-879C4CD97792}"/>
+    <hyperlink ref="A67" r:id="rId94" tooltip="神气制胜" display="https://sts.huijiwiki.com/wiki/%E7%A5%9E%E6%B0%94%E5%88%B6%E8%83%9C" xr:uid="{1008A5C2-44B0-4859-827B-2022EBABA174}"/>
+    <hyperlink ref="A68" r:id="rId95" tooltip="应急按钮" display="https://sts.huijiwiki.com/wiki/%E5%BA%94%E6%80%A5%E6%8C%89%E9%92%AE" xr:uid="{8FB1A610-727D-4C45-8783-0121498DA6F4}"/>
+    <hyperlink ref="G68" r:id="rId96" tooltip="格挡" display="https://sts.huijiwiki.com/wiki/%E6%A0%BC%E6%8C%A1" xr:uid="{5794C2D7-2A76-41C9-91EB-723E991101AF}"/>
+    <hyperlink ref="G70" r:id="rId97" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{17E7121B-F1D3-48FE-8EBC-08C56567E30D}"/>
+    <hyperlink ref="I68" r:id="rId98" tooltip="格挡" display="https://sts.huijiwiki.com/wiki/%E6%A0%BC%E6%8C%A1" xr:uid="{C2EE9DC4-7025-46AB-9F0D-EF6ECCF3355A}"/>
+    <hyperlink ref="I70" r:id="rId99" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{FC8F3A34-3AFB-403B-B32C-0494D19AAEE2}"/>
+    <hyperlink ref="A71" r:id="rId100" tooltip="净化" display="https://sts.huijiwiki.com/wiki/%E5%87%80%E5%8C%96" xr:uid="{FF00E121-BE54-4B7B-BD75-25ADB7945BD3}"/>
+    <hyperlink ref="G71" r:id="rId101" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{02924FA6-C08F-4889-B1D9-644179529F65}"/>
+    <hyperlink ref="G72" r:id="rId102" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{7712804D-233B-4E09-804B-7685DD0EFE5B}"/>
+    <hyperlink ref="I71" r:id="rId103" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{C55A65A5-4B4C-4A57-BA2E-F436B960CD87}"/>
+    <hyperlink ref="I72" r:id="rId104" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{CB716F2F-B917-4EDA-BFB9-9871CADD6970}"/>
+    <hyperlink ref="A73" r:id="rId105" tooltip="仪式匕首" display="https://sts.huijiwiki.com/wiki/%E4%BB%AA%E5%BC%8F%E5%8C%95%E9%A6%96" xr:uid="{65E34006-D554-47D7-8C9A-97168ECBD3C2}"/>
+    <hyperlink ref="G74" r:id="rId106" tooltip="斩杀" display="https://sts.huijiwiki.com/wiki/%E6%96%A9%E6%9D%80" xr:uid="{42A370E3-FF3A-4AE9-9000-F6D17C961007}"/>
+    <hyperlink ref="G75" r:id="rId107" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{88EB79B0-8208-4F67-A09B-C62D4E067AB0}"/>
+    <hyperlink ref="I74" r:id="rId108" tooltip="斩杀" display="https://sts.huijiwiki.com/wiki/%E6%96%A9%E6%9D%80" xr:uid="{D436F4B0-67FD-4719-A982-B8C1394C0F51}"/>
+    <hyperlink ref="I75" r:id="rId109" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{0F5E7F32-2172-4F3D-82A3-E498C78DE94B}"/>
+    <hyperlink ref="A76" r:id="rId110" tooltip="残虐天性" display="https://sts.huijiwiki.com/wiki/%E6%AE%8B%E8%99%90%E5%A4%A9%E6%80%A7" xr:uid="{9B89103A-B8DD-46F6-B02C-4BD243B6C355}"/>
+    <hyperlink ref="A77" r:id="rId111" tooltip="平安" display="https://sts.huijiwiki.com/wiki/%E5%B9%B3%E5%AE%89" xr:uid="{5FF70956-A9BB-4846-9DEB-67A4553212B2}"/>
+    <hyperlink ref="G77" r:id="rId112" tooltip="保留" display="https://sts.huijiwiki.com/wiki/%E4%BF%9D%E7%95%99" xr:uid="{3DA1E25E-BB01-4970-AC37-283B2637BA93}"/>
+    <hyperlink ref="G78" r:id="rId113" tooltip="格挡" display="https://sts.huijiwiki.com/wiki/%E6%A0%BC%E6%8C%A1" xr:uid="{843A6D0A-2A0C-49D9-8758-06A7EC425316}"/>
+    <hyperlink ref="G79" r:id="rId114" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{EB7ECB04-C1C5-448E-985C-46CA88C03374}"/>
+    <hyperlink ref="I77" r:id="rId115" tooltip="保留" display="https://sts.huijiwiki.com/wiki/%E4%BF%9D%E7%95%99" xr:uid="{7870D8F1-34C3-4FC6-8FA9-4667B3A453CC}"/>
+    <hyperlink ref="I78" r:id="rId116" tooltip="格挡" display="https://sts.huijiwiki.com/wiki/%E6%A0%BC%E6%8C%A1" xr:uid="{C38CC730-D10C-4CB0-A711-463BC1497331}"/>
+    <hyperlink ref="I79" r:id="rId117" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{6DB17E8E-89F8-4E06-AF35-30601D2037CE}"/>
+    <hyperlink ref="A80" r:id="rId118" tooltip="秘密技法" display="https://sts.huijiwiki.com/wiki/%E7%A7%98%E5%AF%86%E6%8A%80%E6%B3%95" xr:uid="{F6F37867-8C01-4D35-AFF9-804515BFF8D8}"/>
+    <hyperlink ref="G81" r:id="rId119" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{78EFD540-16B4-455A-AF64-779F1D21FEFB}"/>
+    <hyperlink ref="A82" r:id="rId120" tooltip="秘密武器" display="https://sts.huijiwiki.com/wiki/%E7%A7%98%E5%AF%86%E6%AD%A6%E5%99%A8" xr:uid="{0E97151E-B180-4837-8DBA-96BE3A1B5729}"/>
+    <hyperlink ref="G83" r:id="rId121" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{49D7576F-777A-4B4C-9DB2-8D4C1669126D}"/>
+    <hyperlink ref="A84" r:id="rId122" tooltip="小刀" display="https://sts.huijiwiki.com/wiki/%E5%B0%8F%E5%88%80" xr:uid="{ACDE972D-5EA3-4677-A815-43A8D0551BC8}"/>
+    <hyperlink ref="G85" r:id="rId123" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{FCE890A8-88B2-4B83-A7D5-C0AE12DA2C5A}"/>
+    <hyperlink ref="I85" r:id="rId124" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{0BD056A6-D05A-4EAE-949F-0EFBA2DEE411}"/>
+    <hyperlink ref="A86" r:id="rId125" tooltip="黏液" display="https://sts.huijiwiki.com/wiki/%E9%BB%8F%E6%B6%B2" xr:uid="{9FD9B852-24ED-42B2-A2D2-877217EFF648}"/>
+    <hyperlink ref="G86" r:id="rId126" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{8FF3477D-168D-45F7-B8E4-34FFFCA24406}"/>
+    <hyperlink ref="A87" r:id="rId127" tooltip="惩恶" display="https://sts.huijiwiki.com/wiki/%E6%83%A9%E6%81%B6" xr:uid="{7C948821-AC0E-4393-BCE2-D46A44EB18CF}"/>
+    <hyperlink ref="G87" r:id="rId128" tooltip="保留" display="https://sts.huijiwiki.com/wiki/%E4%BF%9D%E7%95%99" xr:uid="{3C5EE7C0-2150-4345-820A-735AB2F99E0D}"/>
+    <hyperlink ref="G89" r:id="rId129" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{A72D8829-6B7A-4AF3-B80D-2EAFA4321BE6}"/>
+    <hyperlink ref="I87" r:id="rId130" tooltip="保留" display="https://sts.huijiwiki.com/wiki/%E4%BF%9D%E7%95%99" xr:uid="{8271E526-AE68-451D-9FB9-4EAE65A64482}"/>
+    <hyperlink ref="I89" r:id="rId131" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{4A277D9E-B977-497B-B01F-5B297A5DD07D}"/>
+    <hyperlink ref="A90" r:id="rId132" tooltip="迅捷打击" display="https://sts.huijiwiki.com/wiki/%E8%BF%85%E6%8D%B7%E6%89%93%E5%87%BB" xr:uid="{C5172B66-CCD0-44D4-8F7F-1ACDD2FFB4C1}"/>
+    <hyperlink ref="A91" r:id="rId133" tooltip="炸弹" display="https://sts.huijiwiki.com/wiki/%E7%82%B8%E5%BC%B9" xr:uid="{FD155114-4141-44CE-93DC-41E5743D8366}"/>
+    <hyperlink ref="A92" r:id="rId134" tooltip="深谋远虑" display="https://sts.huijiwiki.com/wiki/%E6%B7%B1%E8%B0%8B%E8%BF%9C%E8%99%91" xr:uid="{0860464C-A87F-460F-9F9F-5DFECFB79976}"/>
+    <hyperlink ref="G93" r:id="rId135" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{2C2217D4-49FF-4BA5-A6AF-F6D76FB84FFC}"/>
+    <hyperlink ref="A94" r:id="rId136" tooltip="以暴易暴" display="https://sts.huijiwiki.com/wiki/%E4%BB%A5%E6%9A%B4%E6%98%93%E6%9A%B4" xr:uid="{BD8AD09E-3318-43FD-A353-61DFC27BFB3C}"/>
+    <hyperlink ref="G94" r:id="rId137" display="https://sts.huijiwiki.com/wiki/%E4%BF%9D%E7%95%99" xr:uid="{3CE75AAD-8AE3-4183-B50D-DCE12A1B2143}"/>
+    <hyperlink ref="G96" r:id="rId138" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{38BA039F-1683-4D40-A4D8-414E3D775F97}"/>
+    <hyperlink ref="I94" r:id="rId139" tooltip="保留" display="https://sts.huijiwiki.com/wiki/%E4%BF%9D%E7%95%99" xr:uid="{657056B8-BFA9-4783-8ADD-23D88879C40A}"/>
+    <hyperlink ref="I96" r:id="rId140" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{B8117B88-D6D8-498B-A78F-56337E1F0011}"/>
+    <hyperlink ref="A97" r:id="rId141" tooltip="转化" display="https://sts.huijiwiki.com/wiki/%E8%BD%AC%E5%8C%96" xr:uid="{3B067CD5-F00B-407C-8DE4-E290B862E704}"/>
+    <hyperlink ref="G99" r:id="rId142" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{68915867-9DEF-4681-83C4-F0B17C257DAF}"/>
+    <hyperlink ref="I97" r:id="rId143" tooltip="升级" display="https://sts.huijiwiki.com/wiki/%E5%8D%87%E7%BA%A7" xr:uid="{A0C12582-D125-494A-B570-055A86B7180C}"/>
+    <hyperlink ref="I99" r:id="rId144" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{AFA19B1B-0D3E-4D88-9FA9-6A073F43F37C}"/>
+    <hyperlink ref="A100" r:id="rId145" tooltip="绊倒" display="https://sts.huijiwiki.com/wiki/%E7%BB%8A%E5%80%92" xr:uid="{5781A1AB-7026-4A73-A35D-24A281474CE9}"/>
+    <hyperlink ref="G100" r:id="rId146" tooltip="易伤" display="https://sts.huijiwiki.com/wiki/%E6%98%93%E4%BC%A4" xr:uid="{EDF0E96E-3355-45C1-A548-2669C212DF89}"/>
+    <hyperlink ref="I100" r:id="rId147" tooltip="易伤" display="https://sts.huijiwiki.com/wiki/%E6%98%93%E4%BC%A4" xr:uid="{3F34195E-FE41-4E0A-B00B-AAF692D88CC5}"/>
+    <hyperlink ref="A101" r:id="rId148" tooltip="暴力" display="https://sts.huijiwiki.com/wiki/%E6%9A%B4%E5%8A%9B" xr:uid="{E82ECE4D-E52F-445E-A8AB-C0ECA946F021}"/>
+    <hyperlink ref="G102" r:id="rId149" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{FAA36007-47B9-4EE1-99C0-03AFEC3F85D6}"/>
+    <hyperlink ref="I102" r:id="rId150" tooltip="消耗" display="https://sts.huijiwiki.com/wiki/%E6%B6%88%E8%80%97" xr:uid="{62CFBC85-2F1E-4DEC-A076-F278BA368EB7}"/>
+    <hyperlink ref="A103" r:id="rId151" tooltip="虚空" display="https://sts.huijiwiki.com/wiki/%E8%99%9A%E7%A9%BA" xr:uid="{05127E33-75A1-4DB0-9822-47408AEEE2ED}"/>
+    <hyperlink ref="G103" r:id="rId152" tooltip="不能被打出" display="https://sts.huijiwiki.com/wiki/%E4%B8%8D%E8%83%BD%E8%A2%AB%E6%89%93%E5%87%BA" xr:uid="{8003613F-2415-4BED-947A-DD8EB4CACD82}"/>
+    <hyperlink ref="G105" r:id="rId153" tooltip="虚无" display="https://sts.huijiwiki.com/wiki/%E8%99%9A%E6%97%A0" xr:uid="{BF43AB58-40BD-4D68-B517-60007F87EF67}"/>
+    <hyperlink ref="A106" r:id="rId154" tooltip="伤口" display="https://sts.huijiwiki.com/wiki/%E4%BC%A4%E5%8F%A3" xr:uid="{57CD29FB-1FDF-4FA8-B00E-0AFF1FC8F812}"/>
+    <hyperlink ref="G106" r:id="rId155" tooltip="不能被打出" display="https://sts.huijiwiki.com/wiki/%E4%B8%8D%E8%83%BD%E8%A2%AB%E6%89%93%E5%87%BA" xr:uid="{67663AC5-BBA2-4AAA-A846-0DF4EC1265A2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId156"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>

--- a/原作搬运进度.xlsx
+++ b/原作搬运进度.xlsx
@@ -1,37 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BBB-Bots-0525\WHATtheSpirebasedonQQ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BBB-Bots\SlaytheSpirebasedonQQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7071F1AB-0428-4A47-A6D8-0A6386B9F7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A829CBA-F981-4BF6-8F8E-AD001206DD4D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作台" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
-    <sheet name="战士.塔1" sheetId="1" r:id="rId3"/>
+    <sheet name="无所属" sheetId="4" r:id="rId2"/>
+    <sheet name="塔2.无所属" sheetId="5" r:id="rId3"/>
+    <sheet name="战士.塔1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2604,9 +2594,6 @@
     <t>结茧</t>
   </si>
   <si>
-    <t>Chrysalis</t>
-  </si>
-  <si>
     <t>在你的抽牌堆中加入3张随机技能牌。</t>
   </si>
   <si>
@@ -3365,12 +3352,16 @@
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>Chrysalis</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3547,319 +3538,6 @@
     <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="25">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFA2A9B1"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFA2A9B1"/>
-        </right>
-        <bottom style="medium">
-          <color rgb="FFA2A9B1"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4161,6 +3839,319 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFA2A9B1"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFA2A9B1"/>
+        </right>
+        <bottom style="medium">
+          <color rgb="FFA2A9B1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4175,26 +4166,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A605A88E-2CA9-4C62-96A8-159FB74257BD}" name="表4" displayName="表4" ref="A1:J106" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A605A88E-2CA9-4C62-96A8-159FB74257BD}" name="表4" displayName="表4" ref="A1:J106" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" tableBorderDxfId="22">
   <autoFilter ref="A1:J106" xr:uid="{A605A88E-2CA9-4C62-96A8-159FB74257BD}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{537C478B-F25C-48D2-A47A-FE83482A04CB}" name="名称" dataDxfId="11" dataCellStyle="超链接"/>
-    <tableColumn id="2" xr3:uid="{C6096DE0-266A-4413-A945-F560C0C783E9}" name="英文名称" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{52504C75-8D32-4CC6-9823-5FBE16459E75}" name="颜色" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{C9572819-8A36-472F-B242-1262100B4C3F}" name="稀有度" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{3FC8295B-0E7C-4F08-A755-2EC63F777A6A}" name="类型" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{364007B5-556C-4D91-A3A2-A84B37BE65B2}" name="耗能" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{E27D4591-194B-410C-81D9-6C7B7D6C561A}" name="描述" dataDxfId="5" dataCellStyle="超链接"/>
-    <tableColumn id="8" xr3:uid="{6AD0342B-DAD3-4AB2-8895-5729DE28AD00}" name="升级耗能" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{8A689ADC-343C-4E73-AA80-C16E9C1CFCB9}" name="升级描述" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{A584E3BD-E0B0-40E1-8B43-841C2DB2A160}" name="ok？" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{537C478B-F25C-48D2-A47A-FE83482A04CB}" name="名称" dataDxfId="21" dataCellStyle="超链接"/>
+    <tableColumn id="2" xr3:uid="{C6096DE0-266A-4413-A945-F560C0C783E9}" name="英文名称" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{52504C75-8D32-4CC6-9823-5FBE16459E75}" name="颜色" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{C9572819-8A36-472F-B242-1262100B4C3F}" name="稀有度" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{3FC8295B-0E7C-4F08-A755-2EC63F777A6A}" name="类型" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{364007B5-556C-4D91-A3A2-A84B37BE65B2}" name="耗能" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{E27D4591-194B-410C-81D9-6C7B7D6C561A}" name="描述" dataDxfId="15" dataCellStyle="超链接"/>
+    <tableColumn id="8" xr3:uid="{6AD0342B-DAD3-4AB2-8895-5729DE28AD00}" name="升级耗能" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{8A689ADC-343C-4E73-AA80-C16E9C1CFCB9}" name="升级描述" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{A584E3BD-E0B0-40E1-8B43-841C2DB2A160}" name="ok？" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}" name="表1" displayName="表1" ref="A1:I132" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" tableBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}" name="表1" displayName="表1" ref="A1:I132" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="A1:I132" xr:uid="{0E235B15-7185-4016-A37B-884A21F7F44E}">
     <filterColumn colId="2">
       <filters>
@@ -4208,15 +4199,15 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{B6135FF2-C395-418D-8485-BC72711025F4}" name="名称" dataDxfId="21" dataCellStyle="超链接"/>
-    <tableColumn id="2" xr3:uid="{1B074D24-1599-4FC5-A236-BF6B4242EFE7}" name="英文名称" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{D865C2BE-A956-42B5-BB5A-7AE351AE07B6}" name="稀有度" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{3C3D501F-CAE0-4744-BAB5-1D7A745601E9}" name="类型" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{ABA971A8-6C44-4C6E-8C23-33561D5A983E}" name="耗能" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{9E82D8B0-ABBA-41BA-B169-92A89727DFAA}" name="描述" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{18D4BFF4-3B10-42F7-9F65-B8C97E7E712B}" name="升级耗能" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{E3C19DBB-A684-4385-8660-C5C4F8346A07}" name="升级描述" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{63182BFF-0D89-46A8-A878-6A9CEBB8D964}" name="ok？" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{B6135FF2-C395-418D-8485-BC72711025F4}" name="名称" dataDxfId="8" dataCellStyle="超链接"/>
+    <tableColumn id="2" xr3:uid="{1B074D24-1599-4FC5-A236-BF6B4242EFE7}" name="英文名称" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{D865C2BE-A956-42B5-BB5A-7AE351AE07B6}" name="稀有度" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{3C3D501F-CAE0-4744-BAB5-1D7A745601E9}" name="类型" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{ABA971A8-6C44-4C6E-8C23-33561D5A983E}" name="耗能" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{9E82D8B0-ABBA-41BA-B169-92A89727DFAA}" name="描述" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{18D4BFF4-3B10-42F7-9F65-B8C97E7E712B}" name="升级耗能" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E3C19DBB-A684-4385-8660-C5C4F8346A07}" name="升级描述" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{63182BFF-0D89-46A8-A878-6A9CEBB8D964}" name="ok？" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4486,13 +4477,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD8BFBA-4ECB-4D9C-9CFF-711EB681BC89}">
   <dimension ref="A1:D79"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="50.109375" customWidth="1"/>
+    <col min="2" max="2" width="50.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>319</v>
       </c>
@@ -4504,7 +4495,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>320</v>
       </c>
@@ -4513,7 +4504,7 @@
         <v>"card.heavy_blade": create_heavy_blade,</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>321</v>
       </c>
@@ -4522,7 +4513,7 @@
         <v>"card.anger": create_anger,</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>322</v>
       </c>
@@ -4531,7 +4522,7 @@
         <v>"card.double_strike": create_double_strike,</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>323</v>
       </c>
@@ -4540,7 +4531,7 @@
         <v>"card.sword_boomerang": create_sword_boomerang,</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>324</v>
       </c>
@@ -4549,7 +4540,7 @@
         <v>"card.thunderclap": create_thunderclap,</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>325</v>
       </c>
@@ -4558,7 +4549,7 @@
         <v>"card.cleave": create_cleave,</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>326</v>
       </c>
@@ -4567,7 +4558,7 @@
         <v>"card.iron_wave": create_iron_wave,</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>327</v>
       </c>
@@ -4576,7 +4567,7 @@
         <v>"card.wild_strike": create_wild_strike,</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>328</v>
       </c>
@@ -4585,7 +4576,7 @@
         <v>"card.pommel_strike": create_pommel_strike,</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>329</v>
       </c>
@@ -4594,7 +4585,7 @@
         <v>"card.perfected_strike": create_perfected_strike,</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>331</v>
       </c>
@@ -4603,7 +4594,7 @@
         <v>"card.headbutt": create_headbutt,</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>332</v>
       </c>
@@ -4612,7 +4603,7 @@
         <v>"card.body_slam": create_body_slam,</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>333</v>
       </c>
@@ -4621,7 +4612,7 @@
         <v>"card.clash": create_clash,</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>335</v>
       </c>
@@ -4630,7 +4621,7 @@
         <v>"card.havoc": create_havoc,</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>336</v>
       </c>
@@ -4639,7 +4630,7 @@
         <v>"card.shrug_it_off": create_shrug_it_off,</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>337</v>
       </c>
@@ -4648,7 +4639,7 @@
         <v>"card.true_grit": create_true_grit,</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>338</v>
       </c>
@@ -4657,7 +4648,7 @@
         <v>"card.warcry": create_warcry,</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>330</v>
       </c>
@@ -4666,7 +4657,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>330</v>
       </c>
@@ -4675,7 +4666,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>334</v>
       </c>
@@ -4684,7 +4675,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>339</v>
       </c>
@@ -4693,7 +4684,7 @@
         <v>"card.uppercut": create_uppercut,</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>341</v>
       </c>
@@ -4702,7 +4693,7 @@
         <v>"card.pummel": create_pummel,</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>342</v>
       </c>
@@ -4711,7 +4702,7 @@
         <v>"card.carnage": create_carnage,</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>343</v>
       </c>
@@ -4720,7 +4711,7 @@
         <v>"card.reckless_charge": create_reckless_charge,</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>350</v>
       </c>
@@ -4729,7 +4720,7 @@
         <v>"card.bludgeon": create_bludgeon,</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>344</v>
       </c>
@@ -4738,7 +4729,7 @@
         <v>"card.blood_for_blood": create_blood_for_blood,</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>345</v>
       </c>
@@ -4747,7 +4738,7 @@
         <v>"card.dropkick": create_dropkick,</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>346</v>
       </c>
@@ -4756,7 +4747,7 @@
         <v>"card.hemokinesis": create_hemokinesis,</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>347</v>
       </c>
@@ -4765,7 +4756,7 @@
         <v>"card.rampage": create_rampage,</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>348</v>
       </c>
@@ -4774,7 +4765,7 @@
         <v>"card.searing_blow": create_searing_blow,</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>349</v>
       </c>
@@ -4783,7 +4774,7 @@
         <v>"card.sever_soul": create_sever_soul,</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>351</v>
       </c>
@@ -4792,7 +4783,7 @@
         <v>"card.immolate_history": create_immolate_history,</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>352</v>
       </c>
@@ -4801,7 +4792,7 @@
         <v>"card.death_reaper": create_death_reaper,</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>353</v>
       </c>
@@ -4810,7 +4801,7 @@
         <v>"card.immolate": create_immolate,</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>354</v>
       </c>
@@ -4819,7 +4810,7 @@
         <v>"card.fiend_fire": create_fiend_fire,</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>355</v>
       </c>
@@ -4828,25 +4819,25 @@
         <v>"card.feed": create_feed,</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="B38" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="B39" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="B40" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>356</v>
       </c>
@@ -4859,7 +4850,7 @@
         <v>"card.shockwave",</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>357</v>
       </c>
@@ -4872,7 +4863,7 @@
         <v>"card.intimidate",</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>358</v>
       </c>
@@ -4885,7 +4876,7 @@
         <v>"card.battle_trance",</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>359</v>
       </c>
@@ -4898,7 +4889,7 @@
         <v>"card.bloodletting",</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>360</v>
       </c>
@@ -4911,7 +4902,7 @@
         <v>"card.burning_pact",</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>361</v>
       </c>
@@ -4924,7 +4915,7 @@
         <v>"card.disarm",</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>362</v>
       </c>
@@ -4937,7 +4928,7 @@
         <v>"card.dual_wield",</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>363</v>
       </c>
@@ -4950,7 +4941,7 @@
         <v>"card.entrench",</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>364</v>
       </c>
@@ -4963,7 +4954,7 @@
         <v>"card.flame_barrier",</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>365</v>
       </c>
@@ -4976,7 +4967,7 @@
         <v>"card.ghostly_armor",</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>366</v>
       </c>
@@ -4989,7 +4980,7 @@
         <v>"card.infernal_blade",</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>367</v>
       </c>
@@ -5002,7 +4993,7 @@
         <v>"card.power_through",</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>368</v>
       </c>
@@ -5015,7 +5006,7 @@
         <v>"card.rage",</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>369</v>
       </c>
@@ -5028,7 +5019,7 @@
         <v>"card.second_wind",</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>370</v>
       </c>
@@ -5041,7 +5032,7 @@
         <v>"card.seeing_red",</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>371</v>
       </c>
@@ -5054,7 +5045,7 @@
         <v>"card.sentinel",</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>372</v>
       </c>
@@ -5067,7 +5058,7 @@
         <v>"card.spot_weakness",</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>334</v>
       </c>
@@ -5080,7 +5071,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>373</v>
       </c>
@@ -5093,7 +5084,7 @@
         <v>"card.combust",</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>374</v>
       </c>
@@ -5106,7 +5097,7 @@
         <v>"card.dark_embrace",</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>375</v>
       </c>
@@ -5119,7 +5110,7 @@
         <v>"card.feel_no_pain",</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>376</v>
       </c>
@@ -5132,7 +5123,7 @@
         <v>"card.fire_breathing",</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>377</v>
       </c>
@@ -5145,7 +5136,7 @@
         <v>"card.fire_breathing_history",</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>378</v>
       </c>
@@ -5158,7 +5149,7 @@
         <v>"card.inflame",</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>379</v>
       </c>
@@ -5171,7 +5162,7 @@
         <v>"card.metallicize",</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>380</v>
       </c>
@@ -5184,7 +5175,7 @@
         <v>"card.rupture",</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>381</v>
       </c>
@@ -5197,7 +5188,7 @@
         <v>"card.evolve",</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>382</v>
       </c>
@@ -5210,7 +5201,7 @@
         <v>"card.barricade",</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>383</v>
       </c>
@@ -5223,7 +5214,7 @@
         <v>"card.berserk",</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>384</v>
       </c>
@@ -5236,7 +5227,7 @@
         <v>"card.brutality",</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>385</v>
       </c>
@@ -5249,7 +5240,7 @@
         <v>"card.corruption",</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>386</v>
       </c>
@@ -5262,7 +5253,7 @@
         <v>"card.juggernaut",</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>387</v>
       </c>
@@ -5275,7 +5266,7 @@
         <v>"card.impervious",</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>388</v>
       </c>
@@ -5288,7 +5279,7 @@
         <v>"card.double_tap",</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>389</v>
       </c>
@@ -5301,7 +5292,7 @@
         <v>"card.burst",</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>390</v>
       </c>
@@ -5314,7 +5305,7 @@
         <v>"card.limit_break",</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>391</v>
       </c>
@@ -5327,7 +5318,7 @@
         <v>"card.offering",</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>392</v>
       </c>
@@ -5340,7 +5331,7 @@
         <v>"card.amplify",</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>393</v>
       </c>
@@ -5363,18 +5354,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF66D3D-5735-4513-99A1-DFDBFEA9E050}">
   <dimension ref="A1:J106"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.58203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9.77734375" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.5546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="15"/>
+    <col min="5" max="7" width="9.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.58203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.9140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -5403,10 +5394,10 @@
         <v>7</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="42">
       <c r="A2" s="13" t="s">
         <v>395</v>
       </c>
@@ -5426,17 +5417,17 @@
         <v>2</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2" s="16">
         <v>1</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J2" s="20"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="13"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -5452,7 +5443,7 @@
       </c>
       <c r="J3" s="20"/>
     </row>
-    <row r="4" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="25">
       <c r="A4" s="13" t="s">
         <v>398</v>
       </c>
@@ -5482,7 +5473,7 @@
       </c>
       <c r="J4" s="18"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="13"/>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -5498,7 +5489,7 @@
       </c>
       <c r="J5" s="20"/>
     </row>
-    <row r="6" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="25">
       <c r="A6" s="13" t="s">
         <v>402</v>
       </c>
@@ -5528,7 +5519,7 @@
       </c>
       <c r="J6" s="18"/>
     </row>
-    <row r="7" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="25">
       <c r="A7" s="13"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -5544,7 +5535,7 @@
       </c>
       <c r="J7" s="18"/>
     </row>
-    <row r="8" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="42">
       <c r="A8" s="13" t="s">
         <v>407</v>
       </c>
@@ -5564,17 +5555,17 @@
         <v>2</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H8" s="16">
         <v>1</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J8" s="20"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="13"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -5590,7 +5581,7 @@
       </c>
       <c r="J9" s="20"/>
     </row>
-    <row r="10" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="28">
       <c r="A10" s="13" t="s">
         <v>409</v>
       </c>
@@ -5620,7 +5611,7 @@
       </c>
       <c r="J10" s="20"/>
     </row>
-    <row r="11" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="28">
       <c r="A11" s="13" t="s">
         <v>411</v>
       </c>
@@ -5640,17 +5631,19 @@
         <v>-2</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H11" s="16">
         <v>-2</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>561</v>
-      </c>
-      <c r="J11" s="20"/>
-    </row>
-    <row r="12" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+      <c r="J11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="50">
       <c r="A12" s="13"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -5666,12 +5659,12 @@
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="50">
       <c r="A13" s="13" t="s">
         <v>416</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>417</v>
+        <v>579</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>397</v>
@@ -5686,17 +5679,17 @@
         <v>2</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H13" s="16">
         <v>2</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J13" s="18"/>
     </row>
-    <row r="14" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="37.5">
       <c r="A14" s="13"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -5704,15 +5697,15 @@
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="18" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J14" s="18"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="13"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -5728,12 +5721,12 @@
       </c>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="56">
       <c r="A16" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>421</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>422</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>397</v>
@@ -5748,17 +5741,17 @@
         <v>0</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H16" s="16">
         <v>0</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="13"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -5774,12 +5767,12 @@
       </c>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="28">
       <c r="A18" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>423</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>424</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>397</v>
@@ -5794,17 +5787,19 @@
         <v>-2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H18" s="16">
         <v>-2</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="J18" s="18"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+      <c r="J18" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="13"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -5818,12 +5813,12 @@
       <c r="I19" s="18"/>
       <c r="J19" s="18"/>
     </row>
-    <row r="20" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="50">
       <c r="A20" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>426</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>427</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>397</v>
@@ -5838,17 +5833,17 @@
         <v>0</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H20" s="16">
         <v>0</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J20" s="18"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="13"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -5864,12 +5859,12 @@
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="50">
       <c r="A22" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>429</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>430</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>397</v>
@@ -5884,17 +5879,17 @@
         <v>1</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H22" s="16">
         <v>1</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J22" s="18"/>
     </row>
-    <row r="23" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="37.5">
       <c r="A23" s="13"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -5910,7 +5905,7 @@
       </c>
       <c r="J23" s="18"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="13"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -5924,12 +5919,12 @@
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
     </row>
-    <row r="25" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="25">
       <c r="A25" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="B25" s="16" t="s">
         <v>432</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>433</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>397</v>
@@ -5956,7 +5951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="37.5">
       <c r="A26" s="13"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -5968,11 +5963,11 @@
       </c>
       <c r="H26" s="16"/>
       <c r="I26" s="18" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="13"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -5988,12 +5983,12 @@
       </c>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="62.5">
       <c r="A28" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>435</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>436</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>397</v>
@@ -6008,22 +6003,22 @@
         <v>0</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H28" s="16">
         <v>0</v>
       </c>
       <c r="I28" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" ht="25">
+      <c r="A29" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="B29" s="16" t="s">
         <v>439</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>440</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>397</v>
@@ -6038,22 +6033,22 @@
         <v>1</v>
       </c>
       <c r="G29" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="H29" s="16">
+        <v>1</v>
+      </c>
+      <c r="I29" s="18" t="s">
         <v>441</v>
       </c>
-      <c r="H29" s="16">
-        <v>1</v>
-      </c>
-      <c r="I29" s="18" t="s">
+      <c r="J29" s="18"/>
+    </row>
+    <row r="30" spans="1:10" ht="28">
+      <c r="A30" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="J29" s="18"/>
-    </row>
-    <row r="30" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+      <c r="B30" s="16" t="s">
         <v>443</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>444</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>397</v>
@@ -6068,17 +6063,17 @@
         <v>0</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H30" s="16">
         <v>0</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="13"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -6094,12 +6089,12 @@
       </c>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="25">
       <c r="A32" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="B32" s="16" t="s">
         <v>445</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>446</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>397</v>
@@ -6114,7 +6109,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H32" s="16">
         <v>0</v>
@@ -6126,7 +6121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="13"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -6142,12 +6137,12 @@
       </c>
       <c r="J33" s="18"/>
     </row>
-    <row r="34" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="50">
       <c r="A34" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="B34" s="16" t="s">
         <v>448</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>449</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>397</v>
@@ -6162,17 +6157,17 @@
         <v>0</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H34" s="16">
         <v>0</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J34" s="18"/>
     </row>
-    <row r="35" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="50">
       <c r="A35" s="13"/>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -6180,20 +6175,20 @@
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
       <c r="G35" s="16" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H35" s="16"/>
       <c r="I35" s="18" t="s">
+        <v>452</v>
+      </c>
+      <c r="J35" s="18"/>
+    </row>
+    <row r="36" spans="1:10" ht="25">
+      <c r="A36" s="13" t="s">
         <v>453</v>
       </c>
-      <c r="J35" s="18"/>
-    </row>
-    <row r="36" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
+      <c r="B36" s="16" t="s">
         <v>454</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>455</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>397</v>
@@ -6208,17 +6203,17 @@
         <v>1</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H36" s="16">
         <v>1</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J36" s="18"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" s="13"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -6234,7 +6229,7 @@
       </c>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" s="13"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -6248,12 +6243,12 @@
       <c r="I38" s="19"/>
       <c r="J38" s="18"/>
     </row>
-    <row r="39" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="28">
       <c r="A39" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="B39" s="16" t="s">
         <v>457</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>458</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>397</v>
@@ -6268,7 +6263,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H39" s="16">
         <v>0</v>
@@ -6278,12 +6273,12 @@
       </c>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="25">
       <c r="A40" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="B40" s="16" t="s">
         <v>459</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>460</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>397</v>
@@ -6304,13 +6299,13 @@
         <v>2</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J40" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="42">
       <c r="A41" s="13"/>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -6318,20 +6313,20 @@
       <c r="E41" s="16"/>
       <c r="F41" s="16"/>
       <c r="G41" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H41" s="16"/>
       <c r="I41" s="13" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="50">
       <c r="A42" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="B42" s="16" t="s">
         <v>462</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>463</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>397</v>
@@ -6346,22 +6341,22 @@
         <v>0</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H42" s="16">
         <v>0</v>
       </c>
       <c r="I42" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="J42" s="18"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="13" t="s">
         <v>465</v>
       </c>
-      <c r="J42" s="18"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
+      <c r="B43" s="16" t="s">
         <v>466</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>467</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>397</v>
@@ -6376,17 +6371,17 @@
         <v>0</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H43" s="16">
         <v>0</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10">
       <c r="A44" s="13"/>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -6402,7 +6397,7 @@
       </c>
       <c r="J44" s="18"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10">
       <c r="A45" s="13"/>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -6418,12 +6413,12 @@
       </c>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="25">
       <c r="A46" s="13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>397</v>
@@ -6446,9 +6441,11 @@
       <c r="I46" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="J46" s="18"/>
-    </row>
-    <row r="47" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="J46" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="28">
       <c r="A47" s="13"/>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -6464,12 +6461,12 @@
       </c>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="37.5">
       <c r="A48" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="B48" s="16" t="s">
         <v>469</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>470</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>397</v>
@@ -6484,17 +6481,17 @@
         <v>0</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H48" s="16">
         <v>0</v>
       </c>
       <c r="I48" s="18" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J48" s="18"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10">
       <c r="A49" s="13"/>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -6510,12 +6507,12 @@
       </c>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="62.5">
       <c r="A50" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="B50" s="16" t="s">
         <v>473</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>474</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>397</v>
@@ -6530,17 +6527,17 @@
         <v>1</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H50" s="16">
         <v>0</v>
       </c>
       <c r="I50" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J50" s="18"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10">
       <c r="A51" s="13"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -6556,12 +6553,12 @@
       </c>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="62.5">
       <c r="A52" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="B52" s="16" t="s">
         <v>476</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>477</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>397</v>
@@ -6576,22 +6573,22 @@
         <v>2</v>
       </c>
       <c r="G52" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="H52" s="16">
+        <v>1</v>
+      </c>
+      <c r="I52" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="J52" s="18"/>
+    </row>
+    <row r="53" spans="1:10" ht="25">
+      <c r="A53" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="H52" s="16">
-        <v>1</v>
-      </c>
-      <c r="I52" s="18" t="s">
-        <v>478</v>
-      </c>
-      <c r="J52" s="18"/>
-    </row>
-    <row r="53" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
+      <c r="B53" s="16" t="s">
         <v>479</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>480</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>397</v>
@@ -6616,7 +6613,7 @@
       </c>
       <c r="J53" s="18"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10">
       <c r="A54" s="13"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -6632,12 +6629,12 @@
       </c>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="50">
       <c r="A55" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="B55" s="16" t="s">
         <v>481</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>482</v>
       </c>
       <c r="C55" s="16" t="s">
         <v>397</v>
@@ -6652,22 +6649,22 @@
         <v>2</v>
       </c>
       <c r="G55" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="H55" s="16">
+        <v>1</v>
+      </c>
+      <c r="I55" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="J55" s="18"/>
+    </row>
+    <row r="56" spans="1:10" ht="50">
+      <c r="A56" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="H55" s="16">
-        <v>1</v>
-      </c>
-      <c r="I55" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="J55" s="18"/>
-    </row>
-    <row r="56" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A56" s="13" t="s">
+      <c r="B56" s="16" t="s">
         <v>484</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>485</v>
       </c>
       <c r="C56" s="16" t="s">
         <v>397</v>
@@ -6682,17 +6679,17 @@
         <v>2</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H56" s="16">
         <v>2</v>
       </c>
       <c r="I56" s="18" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J56" s="18"/>
     </row>
-    <row r="57" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="37.5">
       <c r="A57" s="13"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -6700,15 +6697,15 @@
       <c r="E57" s="16"/>
       <c r="F57" s="16"/>
       <c r="G57" s="16" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H57" s="16"/>
       <c r="I57" s="18" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J57" s="18"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10">
       <c r="A58" s="13"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -6724,12 +6721,12 @@
       </c>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10">
       <c r="A59" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="B59" s="16" t="s">
         <v>488</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>489</v>
       </c>
       <c r="C59" s="16" t="s">
         <v>397</v>
@@ -6744,17 +6741,17 @@
         <v>0</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H59" s="16">
         <v>0</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10">
       <c r="A60" s="13"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -6762,15 +6759,15 @@
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
       <c r="G60" s="16" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H60" s="16"/>
       <c r="I60" s="18" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J60" s="18"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10">
       <c r="A61" s="13"/>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -6786,12 +6783,12 @@
       </c>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10">
       <c r="A62" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="B62" s="16" t="s">
         <v>492</v>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>493</v>
       </c>
       <c r="C62" s="16" t="s">
         <v>397</v>
@@ -6818,7 +6815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="37.5">
       <c r="A63" s="13"/>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -6826,20 +6823,20 @@
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="16" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H63" s="16"/>
       <c r="I63" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="J63" s="18"/>
+    </row>
+    <row r="64" spans="1:10" ht="62.5">
+      <c r="A64" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="J63" s="18"/>
-    </row>
-    <row r="64" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
+      <c r="B64" s="16" t="s">
         <v>495</v>
-      </c>
-      <c r="B64" s="16" t="s">
-        <v>496</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>397</v>
@@ -6854,22 +6851,22 @@
         <v>3</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H64" s="16">
         <v>3</v>
       </c>
       <c r="I64" s="18" t="s">
+        <v>497</v>
+      </c>
+      <c r="J64" s="18"/>
+    </row>
+    <row r="65" spans="1:10" ht="28">
+      <c r="A65" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="J64" s="18"/>
-    </row>
-    <row r="65" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A65" s="13" t="s">
+      <c r="B65" s="16" t="s">
         <v>499</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>500</v>
       </c>
       <c r="C65" s="16" t="s">
         <v>397</v>
@@ -6884,17 +6881,17 @@
         <v>0</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H65" s="16">
         <v>0</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10">
       <c r="A66" s="13"/>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
@@ -6910,12 +6907,12 @@
       </c>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="1:10" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="75">
       <c r="A67" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="B67" s="16" t="s">
         <v>501</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>502</v>
       </c>
       <c r="C67" s="16" t="s">
         <v>397</v>
@@ -6930,22 +6927,22 @@
         <v>0</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H67" s="16">
         <v>0</v>
       </c>
       <c r="I67" s="18" t="s">
+        <v>503</v>
+      </c>
+      <c r="J67" s="18"/>
+    </row>
+    <row r="68" spans="1:10" ht="28">
+      <c r="A68" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="J67" s="18"/>
-    </row>
-    <row r="68" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
+      <c r="B68" s="16" t="s">
         <v>505</v>
-      </c>
-      <c r="B68" s="16" t="s">
-        <v>506</v>
       </c>
       <c r="C68" s="16" t="s">
         <v>397</v>
@@ -6970,7 +6967,7 @@
       </c>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="62.5">
       <c r="A69" s="13"/>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -6978,15 +6975,15 @@
       <c r="E69" s="16"/>
       <c r="F69" s="16"/>
       <c r="G69" s="16" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H69" s="16"/>
       <c r="I69" s="18" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J69" s="18"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10">
       <c r="A70" s="13"/>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -7002,12 +6999,12 @@
       </c>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="42">
       <c r="A71" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="B71" s="16" t="s">
         <v>508</v>
-      </c>
-      <c r="B71" s="16" t="s">
-        <v>509</v>
       </c>
       <c r="C71" s="16" t="s">
         <v>397</v>
@@ -7022,17 +7019,17 @@
         <v>0</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H71" s="16">
         <v>0</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10">
       <c r="A72" s="13"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -7048,12 +7045,12 @@
       </c>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="25">
       <c r="A73" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="B73" s="16" t="s">
         <v>510</v>
-      </c>
-      <c r="B73" s="16" t="s">
-        <v>511</v>
       </c>
       <c r="C73" s="16" t="s">
         <v>397</v>
@@ -7078,7 +7075,7 @@
       </c>
       <c r="J73" s="18"/>
     </row>
-    <row r="74" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="70">
       <c r="A74" s="13"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
@@ -7086,15 +7083,15 @@
       <c r="E74" s="16"/>
       <c r="F74" s="16"/>
       <c r="G74" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H74" s="16"/>
       <c r="I74" s="13" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10">
       <c r="A75" s="13"/>
       <c r="B75" s="16"/>
       <c r="C75" s="16"/>
@@ -7110,12 +7107,12 @@
       </c>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="62.5">
       <c r="A76" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="B76" s="16" t="s">
         <v>512</v>
-      </c>
-      <c r="B76" s="16" t="s">
-        <v>513</v>
       </c>
       <c r="C76" s="16" t="s">
         <v>397</v>
@@ -7130,22 +7127,22 @@
         <v>0</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H76" s="16">
         <v>0</v>
       </c>
       <c r="I76" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="J76" s="18"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="J76" s="18"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="13" t="s">
+      <c r="B77" s="16" t="s">
         <v>516</v>
-      </c>
-      <c r="B77" s="16" t="s">
-        <v>517</v>
       </c>
       <c r="C77" s="16" t="s">
         <v>397</v>
@@ -7160,17 +7157,17 @@
         <v>1</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H77" s="16">
         <v>1</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="28">
       <c r="A78" s="13"/>
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
@@ -7186,7 +7183,7 @@
       </c>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10">
       <c r="A79" s="13"/>
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
@@ -7202,12 +7199,12 @@
       </c>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="50">
       <c r="A80" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="B80" s="16" t="s">
         <v>518</v>
-      </c>
-      <c r="B80" s="16" t="s">
-        <v>519</v>
       </c>
       <c r="C80" s="16" t="s">
         <v>397</v>
@@ -7222,17 +7219,17 @@
         <v>0</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H80" s="16">
         <v>0</v>
       </c>
       <c r="I80" s="18" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J80" s="18"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10">
       <c r="A81" s="13"/>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
@@ -7246,12 +7243,12 @@
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
     </row>
-    <row r="82" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="50">
       <c r="A82" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="B82" s="16" t="s">
         <v>521</v>
-      </c>
-      <c r="B82" s="16" t="s">
-        <v>522</v>
       </c>
       <c r="C82" s="16" t="s">
         <v>397</v>
@@ -7266,17 +7263,17 @@
         <v>0</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H82" s="16">
         <v>0</v>
       </c>
       <c r="I82" s="18" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J82" s="18"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10">
       <c r="A83" s="13"/>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
@@ -7290,12 +7287,12 @@
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
     </row>
-    <row r="84" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="25">
       <c r="A84" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="B84" s="16" t="s">
         <v>524</v>
-      </c>
-      <c r="B84" s="16" t="s">
-        <v>525</v>
       </c>
       <c r="C84" s="16" t="s">
         <v>397</v>
@@ -7310,7 +7307,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H84" s="16">
         <v>0</v>
@@ -7318,9 +7315,11 @@
       <c r="I84" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="J84" s="18"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J84" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" s="13"/>
       <c r="B85" s="16"/>
       <c r="C85" s="16"/>
@@ -7332,16 +7331,16 @@
       </c>
       <c r="H85" s="16"/>
       <c r="I85" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="J85" s="20"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="J85" s="20"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="13" t="s">
+      <c r="B86" s="16" t="s">
         <v>528</v>
-      </c>
-      <c r="B86" s="16" t="s">
-        <v>529</v>
       </c>
       <c r="C86" s="16" t="s">
         <v>397</v>
@@ -7362,16 +7361,18 @@
         <v>0</v>
       </c>
       <c r="I86" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="J86" s="18"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+      <c r="J86" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="13" t="s">
+        <v>529</v>
+      </c>
+      <c r="B87" s="16" t="s">
         <v>530</v>
-      </c>
-      <c r="B87" s="16" t="s">
-        <v>531</v>
       </c>
       <c r="C87" s="16" t="s">
         <v>397</v>
@@ -7386,17 +7387,17 @@
         <v>1</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H87" s="16">
         <v>1</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="25">
       <c r="A88" s="13"/>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
@@ -7412,7 +7413,7 @@
       </c>
       <c r="J88" s="18"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10">
       <c r="A89" s="13"/>
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
@@ -7428,12 +7429,12 @@
       </c>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="25">
       <c r="A90" s="13" t="s">
+        <v>531</v>
+      </c>
+      <c r="B90" s="16" t="s">
         <v>532</v>
-      </c>
-      <c r="B90" s="16" t="s">
-        <v>533</v>
       </c>
       <c r="C90" s="16" t="s">
         <v>397</v>
@@ -7460,12 +7461,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="50">
       <c r="A91" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="B91" s="16" t="s">
         <v>534</v>
-      </c>
-      <c r="B91" s="16" t="s">
-        <v>535</v>
       </c>
       <c r="C91" s="16" t="s">
         <v>397</v>
@@ -7480,22 +7481,22 @@
         <v>2</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H91" s="16">
         <v>2</v>
       </c>
       <c r="I91" s="18" t="s">
+        <v>536</v>
+      </c>
+      <c r="J91" s="18"/>
+    </row>
+    <row r="92" spans="1:10" ht="62.5">
+      <c r="A92" s="13" t="s">
         <v>537</v>
       </c>
-      <c r="J91" s="18"/>
-    </row>
-    <row r="92" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A92" s="13" t="s">
+      <c r="B92" s="16" t="s">
         <v>538</v>
-      </c>
-      <c r="B92" s="16" t="s">
-        <v>539</v>
       </c>
       <c r="C92" s="16" t="s">
         <v>397</v>
@@ -7510,17 +7511,17 @@
         <v>0</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H92" s="16">
         <v>0</v>
       </c>
       <c r="I92" s="18" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="J92" s="18"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10">
       <c r="A93" s="13"/>
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
@@ -7534,12 +7535,12 @@
       <c r="I93" s="18"/>
       <c r="J93" s="18"/>
     </row>
-    <row r="94" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10">
       <c r="A94" s="13" t="s">
+        <v>540</v>
+      </c>
+      <c r="B94" s="16" t="s">
         <v>541</v>
-      </c>
-      <c r="B94" s="16" t="s">
-        <v>542</v>
       </c>
       <c r="C94" s="16" t="s">
         <v>397</v>
@@ -7554,17 +7555,17 @@
         <v>0</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H94" s="16">
         <v>0</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="25">
       <c r="A95" s="13"/>
       <c r="B95" s="16"/>
       <c r="C95" s="16"/>
@@ -7576,11 +7577,11 @@
       </c>
       <c r="H95" s="16"/>
       <c r="I95" s="18" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="J95" s="18"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10">
       <c r="A96" s="13"/>
       <c r="B96" s="16"/>
       <c r="C96" s="16"/>
@@ -7596,12 +7597,12 @@
       </c>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="50">
       <c r="A97" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="B97" s="16" t="s">
         <v>544</v>
-      </c>
-      <c r="B97" s="16" t="s">
-        <v>545</v>
       </c>
       <c r="C97" s="16" t="s">
         <v>397</v>
@@ -7616,17 +7617,17 @@
         <v>-1</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H97" s="16">
         <v>-1</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="37.5">
       <c r="A98" s="13"/>
       <c r="B98" s="16"/>
       <c r="C98" s="16"/>
@@ -7634,15 +7635,15 @@
       <c r="E98" s="16"/>
       <c r="F98" s="16"/>
       <c r="G98" s="16" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H98" s="16"/>
       <c r="I98" s="18" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J98" s="18"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10">
       <c r="A99" s="13"/>
       <c r="B99" s="16"/>
       <c r="C99" s="16"/>
@@ -7658,12 +7659,12 @@
       </c>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="28">
       <c r="A100" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="B100" s="16" t="s">
         <v>548</v>
-      </c>
-      <c r="B100" s="16" t="s">
-        <v>549</v>
       </c>
       <c r="C100" s="16" t="s">
         <v>397</v>
@@ -7678,22 +7679,22 @@
         <v>0</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H100" s="16">
         <v>0</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="50">
       <c r="A101" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="B101" s="16" t="s">
         <v>550</v>
-      </c>
-      <c r="B101" s="16" t="s">
-        <v>551</v>
       </c>
       <c r="C101" s="16" t="s">
         <v>397</v>
@@ -7708,17 +7709,17 @@
         <v>0</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H101" s="16">
         <v>0</v>
       </c>
       <c r="I101" s="18" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="J101" s="18"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10">
       <c r="A102" s="13"/>
       <c r="B102" s="16"/>
       <c r="C102" s="16"/>
@@ -7734,12 +7735,12 @@
       </c>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="28">
       <c r="A103" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="B103" s="16" t="s">
         <v>554</v>
-      </c>
-      <c r="B103" s="16" t="s">
-        <v>555</v>
       </c>
       <c r="C103" s="16" t="s">
         <v>397</v>
@@ -7754,17 +7755,17 @@
         <v>-2</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H103" s="16">
         <v>-2</v>
       </c>
       <c r="I103" s="18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J103" s="18"/>
     </row>
-    <row r="104" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="37.5">
       <c r="A104" s="13"/>
       <c r="B104" s="16"/>
       <c r="C104" s="16"/>
@@ -7772,13 +7773,13 @@
       <c r="E104" s="16"/>
       <c r="F104" s="16"/>
       <c r="G104" s="16" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H104" s="16"/>
       <c r="I104" s="18"/>
       <c r="J104" s="18"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10">
       <c r="A105" s="13"/>
       <c r="B105" s="16"/>
       <c r="C105" s="16"/>
@@ -7792,12 +7793,12 @@
       <c r="I105" s="18"/>
       <c r="J105" s="18"/>
     </row>
-    <row r="106" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="28">
       <c r="A106" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="B106" s="18" t="s">
         <v>557</v>
-      </c>
-      <c r="B106" s="18" t="s">
-        <v>558</v>
       </c>
       <c r="C106" s="18" t="s">
         <v>397</v>
@@ -7812,15 +7813,17 @@
         <v>-2</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H106" s="18">
         <v>-2</v>
       </c>
       <c r="I106" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="J106" s="18"/>
+        <v>424</v>
+      </c>
+      <c r="J106" s="18">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -7982,28 +7985,39 @@
     <hyperlink ref="G106" r:id="rId155" tooltip="不能被打出" display="https://sts.huijiwiki.com/wiki/%E4%B8%8D%E8%83%BD%E8%A2%AB%E6%89%93%E5%87%BA" xr:uid="{67663AC5-BBA2-4AAA-A846-0DF4EC1265A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId156"/>
   <tableParts count="1">
-    <tablePart r:id="rId156"/>
+    <tablePart r:id="rId157"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53A55E73-7352-4A59-9A14-0CC045D3CCAF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.4140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.75" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="44.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.4140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="9" max="16384" width="8.9140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8032,7 +8046,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1">
       <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
@@ -8061,7 +8075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="25" hidden="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -8075,7 +8089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1">
       <c r="A4" s="13" t="s">
         <v>15</v>
       </c>
@@ -8104,7 +8118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="28" hidden="1">
       <c r="A5" s="13"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -8118,7 +8132,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="28" hidden="1">
       <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
@@ -8147,7 +8161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1">
       <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
@@ -8176,7 +8190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1">
       <c r="A8" s="13"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -8190,7 +8204,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1">
       <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
@@ -8219,7 +8233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1">
       <c r="A10" s="13"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -8233,7 +8247,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1">
       <c r="A11" s="13" t="s">
         <v>29</v>
       </c>
@@ -8262,7 +8276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="25" hidden="1">
       <c r="A12" s="13"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -8276,7 +8290,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="37.5" hidden="1">
       <c r="A13" s="13" t="s">
         <v>35</v>
       </c>
@@ -8305,7 +8319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1">
       <c r="A14" s="13"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -8319,7 +8333,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1">
       <c r="A15" s="13" t="s">
         <v>40</v>
       </c>
@@ -8348,7 +8362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1">
       <c r="A16" s="13"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -8362,7 +8376,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1">
       <c r="A17" s="13" t="s">
         <v>45</v>
       </c>
@@ -8391,7 +8405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="28" hidden="1">
       <c r="A18" s="13" t="s">
         <v>49</v>
       </c>
@@ -8420,7 +8434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1">
       <c r="A19" s="13" t="s">
         <v>51</v>
       </c>
@@ -8449,7 +8463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="13"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -8463,7 +8477,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1">
       <c r="A21" s="13" t="s">
         <v>54</v>
       </c>
@@ -8492,7 +8506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="25" hidden="1">
       <c r="A22" s="13"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -8504,7 +8518,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1">
       <c r="A23" s="13" t="s">
         <v>57</v>
       </c>
@@ -8533,7 +8547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1">
       <c r="A24" s="13"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -8547,7 +8561,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="25" hidden="1">
       <c r="A25" s="13" t="s">
         <v>61</v>
       </c>
@@ -8576,7 +8590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1">
       <c r="A26" s="13"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -8590,7 +8604,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="25" hidden="1">
       <c r="A27" s="13" t="s">
         <v>65</v>
       </c>
@@ -8619,7 +8633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1">
       <c r="A28" s="13" t="s">
         <v>69</v>
       </c>
@@ -8648,7 +8662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1">
       <c r="A29" s="13"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -8662,7 +8676,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="37.5" hidden="1">
       <c r="A30" s="13" t="s">
         <v>72</v>
       </c>
@@ -8691,7 +8705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1">
       <c r="A31" s="13" t="s">
         <v>76</v>
       </c>
@@ -8720,7 +8734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="28" hidden="1">
       <c r="A32" s="13"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -8734,7 +8748,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="28" hidden="1">
       <c r="A33" s="13" t="s">
         <v>79</v>
       </c>
@@ -8763,7 +8777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="28" hidden="1">
       <c r="A34" s="13" t="s">
         <v>81</v>
       </c>
@@ -8792,7 +8806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="28" hidden="1">
       <c r="A35" s="13" t="s">
         <v>83</v>
       </c>
@@ -8821,7 +8835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1">
       <c r="A36" s="13" t="s">
         <v>85</v>
       </c>
@@ -8850,7 +8864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1">
       <c r="A37" s="13"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -8864,7 +8878,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="25">
       <c r="A38" s="13" t="s">
         <v>87</v>
       </c>
@@ -8893,7 +8907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1">
       <c r="A39" s="13" t="s">
         <v>91</v>
       </c>
@@ -8922,7 +8936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="28" hidden="1">
       <c r="A40" s="13"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -8936,7 +8950,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="25" hidden="1">
       <c r="A41" s="13" t="s">
         <v>94</v>
       </c>
@@ -8965,7 +8979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1">
       <c r="A42" s="13" t="s">
         <v>98</v>
       </c>
@@ -8994,7 +9008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="28">
       <c r="A43" s="13" t="s">
         <v>100</v>
       </c>
@@ -9023,7 +9037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1">
       <c r="A44" s="13"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -9037,7 +9051,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="28" hidden="1">
       <c r="A45" s="13" t="s">
         <v>102</v>
       </c>
@@ -9066,7 +9080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1">
       <c r="A46" s="13" t="s">
         <v>104</v>
       </c>
@@ -9095,7 +9109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="28" hidden="1">
       <c r="A47" s="13"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -9109,7 +9123,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1">
       <c r="A48" s="13"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -9123,7 +9137,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="26" hidden="1">
       <c r="A49" s="13" t="s">
         <v>106</v>
       </c>
@@ -9152,7 +9166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1">
       <c r="A50" s="13" t="s">
         <v>108</v>
       </c>
@@ -9181,7 +9195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="25" hidden="1">
       <c r="A51" s="13"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -9195,7 +9209,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1">
       <c r="A52" s="13"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -9209,7 +9223,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="38.5" hidden="1">
       <c r="A53" s="13" t="s">
         <v>112</v>
       </c>
@@ -9238,7 +9252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1">
       <c r="A54" s="13" t="s">
         <v>114</v>
       </c>
@@ -9267,7 +9281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="37.5" hidden="1">
       <c r="A55" s="13"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -9281,7 +9295,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1">
       <c r="A56" s="13" t="s">
         <v>118</v>
       </c>
@@ -9310,7 +9324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="28" hidden="1">
       <c r="A57" s="13"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -9324,7 +9338,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1">
       <c r="A58" s="13" t="s">
         <v>120</v>
       </c>
@@ -9353,7 +9367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1">
       <c r="A59" s="13"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -9367,7 +9381,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="28" hidden="1">
       <c r="A60" s="13" t="s">
         <v>122</v>
       </c>
@@ -9396,7 +9410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1">
       <c r="A61" s="13" t="s">
         <v>124</v>
       </c>
@@ -9425,7 +9439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="25" hidden="1">
       <c r="A62" s="13"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -9439,7 +9453,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1">
       <c r="A63" s="13" t="s">
         <v>128</v>
       </c>
@@ -9468,7 +9482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="28" hidden="1">
       <c r="A64" s="13"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -9482,7 +9496,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1">
       <c r="A65" s="13" t="s">
         <v>130</v>
       </c>
@@ -9511,7 +9525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1">
       <c r="A66" s="13"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -9525,7 +9539,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="25" hidden="1">
       <c r="A67" s="13" t="s">
         <v>134</v>
       </c>
@@ -9554,7 +9568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="28" hidden="1">
       <c r="A68" s="13"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -9568,7 +9582,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" s="13" t="s">
         <v>138</v>
       </c>
@@ -9597,7 +9611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1">
       <c r="A70" s="13"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -9611,7 +9625,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="25" hidden="1">
       <c r="A71" s="13" t="s">
         <v>140</v>
       </c>
@@ -9640,7 +9654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="25" hidden="1">
       <c r="A72" s="13"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -9654,7 +9668,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1">
       <c r="A73" s="13"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -9668,7 +9682,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1">
       <c r="A74" s="13" t="s">
         <v>144</v>
       </c>
@@ -9697,7 +9711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1">
       <c r="A75" s="13" t="s">
         <v>146</v>
       </c>
@@ -9726,7 +9740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1">
       <c r="A76" s="13"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -9740,7 +9754,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1">
       <c r="A77" s="13" t="s">
         <v>148</v>
       </c>
@@ -9769,7 +9783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1">
       <c r="A78" s="13"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -9783,7 +9797,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="42" hidden="1">
       <c r="A79" s="13" t="s">
         <v>151</v>
       </c>
@@ -9812,7 +9826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" s="13" t="s">
         <v>153</v>
       </c>
@@ -9841,7 +9855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1">
       <c r="A81" s="13"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -9853,7 +9867,7 @@
       <c r="G81" s="4"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="28" hidden="1">
       <c r="A82" s="13" t="s">
         <v>155</v>
       </c>
@@ -9882,7 +9896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9">
       <c r="A83" s="13" t="s">
         <v>157</v>
       </c>
@@ -9911,7 +9925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1">
       <c r="A84" s="13"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -9925,7 +9939,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1">
       <c r="A85" s="13"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -9939,7 +9953,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1">
       <c r="A86" s="13"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -9953,7 +9967,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1">
       <c r="A87" s="13" t="s">
         <v>161</v>
       </c>
@@ -9982,7 +9996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="28" hidden="1">
       <c r="A88" s="13"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -9996,7 +10010,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1">
       <c r="A89" s="13" t="s">
         <v>163</v>
       </c>
@@ -10025,7 +10039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1">
       <c r="A90" s="13"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -10039,7 +10053,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="28" hidden="1">
       <c r="A91" s="13" t="s">
         <v>166</v>
       </c>
@@ -10068,7 +10082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1">
       <c r="A92" s="13"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -10082,7 +10096,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1">
       <c r="A93" s="13" t="s">
         <v>168</v>
       </c>
@@ -10111,7 +10125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1">
       <c r="A94" s="13"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -10125,7 +10139,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="42" hidden="1">
       <c r="A95" s="13" t="s">
         <v>172</v>
       </c>
@@ -10154,7 +10168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1">
       <c r="A96" s="13" t="s">
         <v>174</v>
       </c>
@@ -10183,7 +10197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="25" hidden="1">
       <c r="A97" s="13"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -10197,7 +10211,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1">
       <c r="A98" s="13" t="s">
         <v>178</v>
       </c>
@@ -10226,7 +10240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="28" hidden="1">
       <c r="A99" s="13"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -10240,7 +10254,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1">
       <c r="A100" s="13"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -10254,7 +10268,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1">
       <c r="A101" s="13" t="s">
         <v>182</v>
       </c>
@@ -10283,7 +10297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="28" hidden="1">
       <c r="A102" s="13"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -10297,7 +10311,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="28" hidden="1">
       <c r="A103" s="13" t="s">
         <v>184</v>
       </c>
@@ -10326,7 +10340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1">
       <c r="A104" s="13" t="s">
         <v>186</v>
       </c>
@@ -10355,7 +10369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1">
       <c r="A105" s="13"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -10369,7 +10383,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="26" hidden="1">
       <c r="A106" s="13" t="s">
         <v>189</v>
       </c>
@@ -10398,7 +10412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1">
       <c r="A107" s="13" t="s">
         <v>191</v>
       </c>
@@ -10427,7 +10441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1">
       <c r="A108" s="13"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -10441,7 +10455,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1">
       <c r="A109" s="13" t="s">
         <v>193</v>
       </c>
@@ -10470,7 +10484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" ht="28" hidden="1">
       <c r="A110" s="13"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -10484,7 +10498,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="28" hidden="1">
       <c r="A111" s="13" t="s">
         <v>195</v>
       </c>
@@ -10513,7 +10527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1">
       <c r="A112" s="13"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -10527,7 +10541,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1">
       <c r="A113" s="13" t="s">
         <v>197</v>
       </c>
@@ -10556,7 +10570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1">
       <c r="A114" s="13"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -10570,7 +10584,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="26" hidden="1">
       <c r="A115" s="13" t="s">
         <v>199</v>
       </c>
@@ -10599,7 +10613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1">
       <c r="A116" s="13"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -10613,7 +10627,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="28" hidden="1">
       <c r="A117" s="13" t="s">
         <v>201</v>
       </c>
@@ -10642,7 +10656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="28" hidden="1">
       <c r="A118" s="13" t="s">
         <v>203</v>
       </c>
@@ -10671,7 +10685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="28" hidden="1">
       <c r="A119" s="13" t="s">
         <v>205</v>
       </c>
@@ -10700,7 +10714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="28" hidden="1">
       <c r="A120" s="13" t="s">
         <v>209</v>
       </c>
@@ -10729,7 +10743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1">
       <c r="A121" s="13" t="s">
         <v>211</v>
       </c>
@@ -10758,7 +10772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1">
       <c r="A122" s="13"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -10772,7 +10786,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1">
       <c r="A123" s="13" t="s">
         <v>213</v>
       </c>
@@ -10801,7 +10815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1">
       <c r="A124" s="13" t="s">
         <v>217</v>
       </c>
@@ -10830,7 +10844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1">
       <c r="A125" s="13"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -10844,7 +10858,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1">
       <c r="A126" s="13"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -10858,7 +10872,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1">
       <c r="A127" s="13" t="s">
         <v>220</v>
       </c>
@@ -10887,7 +10901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="25" hidden="1">
       <c r="A128" s="13"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -10901,7 +10915,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1">
       <c r="A129" s="13"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -10915,7 +10929,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="25" hidden="1">
       <c r="A130" s="13" t="s">
         <v>223</v>
       </c>
@@ -10944,7 +10958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1">
       <c r="A131" s="13" t="s">
         <v>227</v>
       </c>
@@ -10973,7 +10987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="28.2" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" ht="28.5" hidden="1" thickBot="1">
       <c r="A132" s="10"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>

--- a/原作搬运进度.xlsx
+++ b/原作搬运进度.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BBB-Bots-0525\WHATtheSpirebasedonQQ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BBB-Bots\SlaytheSpirebasedonQQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0E619A-709B-4FEF-867D-3DCD9B7068E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EA8C60-8C0B-49D9-9F70-E9EB21AC09CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="23260" windowHeight="12580" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作台" sheetId="2" r:id="rId1"/>
@@ -19,28 +19,17 @@
     <sheet name="战士.塔1" sheetId="1" r:id="rId4"/>
     <sheet name="猎人.塔1" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="847">
   <si>
     <t>名称</t>
   </si>
@@ -3399,9 +3388,6 @@
     <t>After Image</t>
   </si>
   <si>
-    <t>全力攻击</t>
-  </si>
-  <si>
     <t>All Out Attack</t>
   </si>
   <si>
@@ -3510,9 +3496,6 @@
     <t>铁蒺藜</t>
   </si>
   <si>
-    <t>Caltrops</t>
-  </si>
-  <si>
     <t>每当你被攻击时，对攻击者造成3点伤害。</t>
   </si>
   <si>
@@ -3738,12 +3721,6 @@
     <t>在下一回合获得[G]。</t>
   </si>
   <si>
-    <t>灵动步法</t>
-  </si>
-  <si>
-    <t>Footwork</t>
-  </si>
-  <si>
     <t>玻璃刀刃</t>
   </si>
   <si>
@@ -3783,9 +3760,6 @@
     <t>无限刀刃</t>
   </si>
   <si>
-    <t>Infinite Blades</t>
-  </si>
-  <si>
     <t>扫腿</t>
   </si>
   <si>
@@ -3831,9 +3805,6 @@
     <t>毒雾</t>
   </si>
   <si>
-    <t>Noxious Fumes</t>
-  </si>
-  <si>
     <t>抢占先机</t>
   </si>
   <si>
@@ -4024,9 +3995,6 @@
   </si>
   <si>
     <t>计划妥当</t>
-  </si>
-  <si>
-    <t>Well Laid Plans</t>
   </si>
   <si>
     <t>幽魂形态</t>
@@ -4640,7 +4608,7 @@
   </si>
   <si>
     <r>
-      <t>在你的回合开始时，给予所有敌人2层</t>
+      <t>在你的回合开始时，给予所有敌人3层</t>
     </r>
     <r>
       <rPr>
@@ -4656,7 +4624,7 @@
   </si>
   <si>
     <r>
-      <t>在你的回合开始时，给予所有敌人3层</t>
+      <t>给予3层</t>
     </r>
     <r>
       <rPr>
@@ -4672,7 +4640,7 @@
   </si>
   <si>
     <r>
-      <t>给予3层</t>
+      <t>给予4层</t>
     </r>
     <r>
       <rPr>
@@ -4688,7 +4656,7 @@
   </si>
   <si>
     <r>
-      <t>给予4层</t>
+      <t>每丢弃一张牌，在你的手牌中增加一张</t>
     </r>
     <r>
       <rPr>
@@ -4699,7 +4667,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>中毒。</t>
+      <t>小刀。</t>
     </r>
   </si>
   <si>
@@ -4715,12 +4683,12 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>小刀。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>每丢弃一张牌，在你的手牌中增加一张</t>
+      <t>小刀+。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>给予99层</t>
     </r>
     <r>
       <rPr>
@@ -4731,12 +4699,12 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>小刀+。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>给予99层</t>
+      <t>易伤。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>在你的回合结束时，</t>
     </r>
     <r>
       <rPr>
@@ -4747,12 +4715,12 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>易伤。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>在你的回合结束时，</t>
+      <t>保留最多2张牌。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>获得2层</t>
     </r>
     <r>
       <rPr>
@@ -4763,12 +4731,12 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>保留最多1张牌。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>在你的回合结束时，</t>
+      <t>无实体。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>获得3层</t>
     </r>
     <r>
       <rPr>
@@ -4779,12 +4747,12 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>保留最多2张牌。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>获得2层</t>
+      <t>无实体。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>在每回合结束时失去1点</t>
     </r>
     <r>
       <rPr>
@@ -4795,12 +4763,28 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>无实体。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>获得3层</t>
+      <t>敏捷。</t>
+    </r>
+  </si>
+  <si>
+    <t>Caltrops</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Footwork</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵动步法</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Infinite Blades</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在你的回合开始时，增加一张</t>
     </r>
     <r>
       <rPr>
@@ -4811,12 +4795,17 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>无实体。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>在每回合结束时失去1点</t>
+      <t>小刀到你的手牌。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Noxious Fumes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在你的回合开始时，给予所有敌人2层</t>
     </r>
     <r>
       <rPr>
@@ -4827,15 +4816,41 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>敏捷。</t>
-    </r>
+      <t>中毒。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Well Laid Plans</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在你的回合结束时，</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>保留最多1张牌。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>全力攻击</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5024,31 +5039,6 @@
     <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="36">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5290,6 +5280,31 @@
           <color rgb="FFA2A9B1"/>
         </left>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5967,24 +5982,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1218E1B0-95ED-42BB-96C9-6CE52BDB2EE5}" name="表3" displayName="表3" ref="A1:J134" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="10">
-  <autoFilter ref="A1:J134" xr:uid="{1218E1B0-95ED-42BB-96C9-6CE52BDB2EE5}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="罕见"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1218E1B0-95ED-42BB-96C9-6CE52BDB2EE5}" name="表3" displayName="表3" ref="A1:J134" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
+  <autoFilter ref="A1:J134" xr:uid="{1218E1B0-95ED-42BB-96C9-6CE52BDB2EE5}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{86153326-CBA8-4F8F-9EC2-14387C45F2DC}" name="名称" dataDxfId="9" dataCellStyle="超链接"/>
-    <tableColumn id="2" xr3:uid="{60F76BEB-A430-4260-A841-287FB2B859A0}" name="英文名称" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{35E6E336-EECD-41BB-B1D5-6D2067724FC0}" name="颜色" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{A1C9A528-07EE-49BC-ABD8-84993EA4CC60}" name="稀有度" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{EFE57A0A-AD92-4C19-8980-5BBF78644FE8}" name="类型" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{A27D38B8-8092-4BC0-8EB2-981BAEDA87A8}" name="耗能" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{49B37ACA-9590-4FD6-8FE3-E824CE260B98}" name="描述" dataDxfId="3" dataCellStyle="超链接"/>
-    <tableColumn id="8" xr3:uid="{78A2C399-FFA2-4D35-821D-ABE12EFE4FEA}" name="升级耗能" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{14497251-C1B5-403D-84DA-39FB1F4AC1D8}" name="升级描述" dataDxfId="1" dataCellStyle="超链接"/>
+    <tableColumn id="1" xr3:uid="{86153326-CBA8-4F8F-9EC2-14387C45F2DC}" name="名称" dataDxfId="8" dataCellStyle="超链接"/>
+    <tableColumn id="2" xr3:uid="{60F76BEB-A430-4260-A841-287FB2B859A0}" name="英文名称" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{35E6E336-EECD-41BB-B1D5-6D2067724FC0}" name="颜色" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{A1C9A528-07EE-49BC-ABD8-84993EA4CC60}" name="稀有度" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{EFE57A0A-AD92-4C19-8980-5BBF78644FE8}" name="类型" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{A27D38B8-8092-4BC0-8EB2-981BAEDA87A8}" name="耗能" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{49B37ACA-9590-4FD6-8FE3-E824CE260B98}" name="描述" dataDxfId="2" dataCellStyle="超链接"/>
+    <tableColumn id="8" xr3:uid="{78A2C399-FFA2-4D35-821D-ABE12EFE4FEA}" name="升级耗能" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{14497251-C1B5-403D-84DA-39FB1F4AC1D8}" name="升级描述" dataDxfId="0" dataCellStyle="超链接"/>
     <tableColumn id="10" xr3:uid="{25E1709C-5169-40CC-BE6E-7290D063265A}" name="ok？"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6255,13 +6264,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD8BFBA-4ECB-4D9C-9CFF-711EB681BC89}">
   <dimension ref="A1:D79"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="50.109375" customWidth="1"/>
+    <col min="2" max="2" width="50.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>319</v>
       </c>
@@ -6273,7 +6282,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>320</v>
       </c>
@@ -6282,7 +6291,7 @@
         <v>"card.heavy_blade": create_heavy_blade,</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>321</v>
       </c>
@@ -6291,7 +6300,7 @@
         <v>"card.anger": create_anger,</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>322</v>
       </c>
@@ -6300,7 +6309,7 @@
         <v>"card.double_strike": create_double_strike,</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>323</v>
       </c>
@@ -6309,7 +6318,7 @@
         <v>"card.sword_boomerang": create_sword_boomerang,</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>324</v>
       </c>
@@ -6318,7 +6327,7 @@
         <v>"card.thunderclap": create_thunderclap,</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>325</v>
       </c>
@@ -6327,7 +6336,7 @@
         <v>"card.cleave": create_cleave,</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>326</v>
       </c>
@@ -6336,7 +6345,7 @@
         <v>"card.iron_wave": create_iron_wave,</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>327</v>
       </c>
@@ -6345,7 +6354,7 @@
         <v>"card.wild_strike": create_wild_strike,</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>328</v>
       </c>
@@ -6354,7 +6363,7 @@
         <v>"card.pommel_strike": create_pommel_strike,</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>329</v>
       </c>
@@ -6363,7 +6372,7 @@
         <v>"card.perfected_strike": create_perfected_strike,</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>331</v>
       </c>
@@ -6372,7 +6381,7 @@
         <v>"card.headbutt": create_headbutt,</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>332</v>
       </c>
@@ -6381,7 +6390,7 @@
         <v>"card.body_slam": create_body_slam,</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>333</v>
       </c>
@@ -6390,7 +6399,7 @@
         <v>"card.clash": create_clash,</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>335</v>
       </c>
@@ -6399,7 +6408,7 @@
         <v>"card.havoc": create_havoc,</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>336</v>
       </c>
@@ -6408,7 +6417,7 @@
         <v>"card.shrug_it_off": create_shrug_it_off,</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>337</v>
       </c>
@@ -6417,7 +6426,7 @@
         <v>"card.true_grit": create_true_grit,</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>338</v>
       </c>
@@ -6426,7 +6435,7 @@
         <v>"card.warcry": create_warcry,</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>330</v>
       </c>
@@ -6435,7 +6444,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>330</v>
       </c>
@@ -6444,7 +6453,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>334</v>
       </c>
@@ -6453,7 +6462,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>339</v>
       </c>
@@ -6462,7 +6471,7 @@
         <v>"card.uppercut": create_uppercut,</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>341</v>
       </c>
@@ -6471,7 +6480,7 @@
         <v>"card.pummel": create_pummel,</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>342</v>
       </c>
@@ -6480,7 +6489,7 @@
         <v>"card.carnage": create_carnage,</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>343</v>
       </c>
@@ -6489,7 +6498,7 @@
         <v>"card.reckless_charge": create_reckless_charge,</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>350</v>
       </c>
@@ -6498,7 +6507,7 @@
         <v>"card.bludgeon": create_bludgeon,</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>344</v>
       </c>
@@ -6507,7 +6516,7 @@
         <v>"card.blood_for_blood": create_blood_for_blood,</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>345</v>
       </c>
@@ -6516,7 +6525,7 @@
         <v>"card.dropkick": create_dropkick,</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>346</v>
       </c>
@@ -6525,7 +6534,7 @@
         <v>"card.hemokinesis": create_hemokinesis,</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>347</v>
       </c>
@@ -6534,7 +6543,7 @@
         <v>"card.rampage": create_rampage,</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>348</v>
       </c>
@@ -6543,7 +6552,7 @@
         <v>"card.searing_blow": create_searing_blow,</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>349</v>
       </c>
@@ -6552,7 +6561,7 @@
         <v>"card.sever_soul": create_sever_soul,</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>351</v>
       </c>
@@ -6561,7 +6570,7 @@
         <v>"card.immolate_history": create_immolate_history,</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>352</v>
       </c>
@@ -6570,7 +6579,7 @@
         <v>"card.death_reaper": create_death_reaper,</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>353</v>
       </c>
@@ -6579,7 +6588,7 @@
         <v>"card.immolate": create_immolate,</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>354</v>
       </c>
@@ -6588,7 +6597,7 @@
         <v>"card.fiend_fire": create_fiend_fire,</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>355</v>
       </c>
@@ -6597,25 +6606,25 @@
         <v>"card.feed": create_feed,</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="B38" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="B39" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="B40" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>356</v>
       </c>
@@ -6628,7 +6637,7 @@
         <v>"card.shockwave",</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>357</v>
       </c>
@@ -6641,7 +6650,7 @@
         <v>"card.intimidate",</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>358</v>
       </c>
@@ -6654,7 +6663,7 @@
         <v>"card.battle_trance",</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>359</v>
       </c>
@@ -6667,7 +6676,7 @@
         <v>"card.bloodletting",</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>360</v>
       </c>
@@ -6680,7 +6689,7 @@
         <v>"card.burning_pact",</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>361</v>
       </c>
@@ -6693,7 +6702,7 @@
         <v>"card.disarm",</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>362</v>
       </c>
@@ -6706,7 +6715,7 @@
         <v>"card.dual_wield",</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>363</v>
       </c>
@@ -6719,7 +6728,7 @@
         <v>"card.entrench",</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>364</v>
       </c>
@@ -6732,7 +6741,7 @@
         <v>"card.flame_barrier",</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>365</v>
       </c>
@@ -6745,7 +6754,7 @@
         <v>"card.ghostly_armor",</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>366</v>
       </c>
@@ -6758,7 +6767,7 @@
         <v>"card.infernal_blade",</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>367</v>
       </c>
@@ -6771,7 +6780,7 @@
         <v>"card.power_through",</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>368</v>
       </c>
@@ -6784,7 +6793,7 @@
         <v>"card.rage",</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>369</v>
       </c>
@@ -6797,7 +6806,7 @@
         <v>"card.second_wind",</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>370</v>
       </c>
@@ -6810,7 +6819,7 @@
         <v>"card.seeing_red",</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>371</v>
       </c>
@@ -6823,7 +6832,7 @@
         <v>"card.sentinel",</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>372</v>
       </c>
@@ -6836,7 +6845,7 @@
         <v>"card.spot_weakness",</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>334</v>
       </c>
@@ -6849,7 +6858,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>373</v>
       </c>
@@ -6862,7 +6871,7 @@
         <v>"card.combust",</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>374</v>
       </c>
@@ -6875,7 +6884,7 @@
         <v>"card.dark_embrace",</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>375</v>
       </c>
@@ -6888,7 +6897,7 @@
         <v>"card.feel_no_pain",</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>376</v>
       </c>
@@ -6901,7 +6910,7 @@
         <v>"card.fire_breathing",</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>377</v>
       </c>
@@ -6914,7 +6923,7 @@
         <v>"card.fire_breathing_history",</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>378</v>
       </c>
@@ -6927,7 +6936,7 @@
         <v>"card.inflame",</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>379</v>
       </c>
@@ -6940,7 +6949,7 @@
         <v>"card.metallicize",</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>380</v>
       </c>
@@ -6953,7 +6962,7 @@
         <v>"card.rupture",</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>381</v>
       </c>
@@ -6966,7 +6975,7 @@
         <v>"card.evolve",</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>382</v>
       </c>
@@ -6979,7 +6988,7 @@
         <v>"card.barricade",</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>383</v>
       </c>
@@ -6992,7 +7001,7 @@
         <v>"card.berserk",</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>384</v>
       </c>
@@ -7005,7 +7014,7 @@
         <v>"card.brutality",</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>385</v>
       </c>
@@ -7018,7 +7027,7 @@
         <v>"card.corruption",</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>386</v>
       </c>
@@ -7031,7 +7040,7 @@
         <v>"card.juggernaut",</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>387</v>
       </c>
@@ -7044,7 +7053,7 @@
         <v>"card.impervious",</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>388</v>
       </c>
@@ -7057,7 +7066,7 @@
         <v>"card.double_tap",</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>389</v>
       </c>
@@ -7070,7 +7079,7 @@
         <v>"card.burst",</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>390</v>
       </c>
@@ -7083,7 +7092,7 @@
         <v>"card.limit_break",</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>391</v>
       </c>
@@ -7096,7 +7105,7 @@
         <v>"card.offering",</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>392</v>
       </c>
@@ -7109,7 +7118,7 @@
         <v>"card.amplify",</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>393</v>
       </c>
@@ -7132,18 +7141,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF66D3D-5735-4513-99A1-DFDBFEA9E050}">
   <dimension ref="A1:J106"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="5" max="7" width="9.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.9140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7175,7 +7184,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="42">
       <c r="A2" s="13" t="s">
         <v>395</v>
       </c>
@@ -7205,7 +7214,7 @@
       </c>
       <c r="J2" s="14"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="13"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -7221,7 +7230,7 @@
       </c>
       <c r="J3" s="14"/>
     </row>
-    <row r="4" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="25">
       <c r="A4" s="13" t="s">
         <v>398</v>
       </c>
@@ -7251,7 +7260,7 @@
       </c>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="13"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -7267,7 +7276,7 @@
       </c>
       <c r="J5" s="14"/>
     </row>
-    <row r="6" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="25">
       <c r="A6" s="13" t="s">
         <v>402</v>
       </c>
@@ -7297,7 +7306,7 @@
       </c>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="25">
       <c r="A7" s="13"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -7313,7 +7322,7 @@
       </c>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="42">
       <c r="A8" s="13" t="s">
         <v>407</v>
       </c>
@@ -7343,7 +7352,7 @@
       </c>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="13"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -7359,7 +7368,7 @@
       </c>
       <c r="J9" s="14"/>
     </row>
-    <row r="10" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="28">
       <c r="A10" s="13" t="s">
         <v>409</v>
       </c>
@@ -7389,7 +7398,7 @@
       </c>
       <c r="J10" s="14"/>
     </row>
-    <row r="11" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="28">
       <c r="A11" s="13" t="s">
         <v>411</v>
       </c>
@@ -7421,7 +7430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="50">
       <c r="A12" s="13"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -7437,7 +7446,7 @@
       </c>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="50">
       <c r="A13" s="13" t="s">
         <v>416</v>
       </c>
@@ -7467,7 +7476,7 @@
       </c>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="37.5">
       <c r="A14" s="13"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -7483,7 +7492,7 @@
       </c>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="13"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -7499,7 +7508,7 @@
       </c>
       <c r="J15" s="14"/>
     </row>
-    <row r="16" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="56">
       <c r="A16" s="13" t="s">
         <v>420</v>
       </c>
@@ -7529,7 +7538,7 @@
       </c>
       <c r="J16" s="14"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="13"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -7545,7 +7554,7 @@
       </c>
       <c r="J17" s="14"/>
     </row>
-    <row r="18" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="28">
       <c r="A18" s="13" t="s">
         <v>422</v>
       </c>
@@ -7577,7 +7586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="13"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -7591,7 +7600,7 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="50">
       <c r="A20" s="13" t="s">
         <v>425</v>
       </c>
@@ -7621,7 +7630,7 @@
       </c>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="13"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -7637,7 +7646,7 @@
       </c>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="50">
       <c r="A22" s="13" t="s">
         <v>428</v>
       </c>
@@ -7667,7 +7676,7 @@
       </c>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="37.5">
       <c r="A23" s="13"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -7683,7 +7692,7 @@
       </c>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="13"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -7697,7 +7706,7 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="25">
       <c r="A25" s="13" t="s">
         <v>431</v>
       </c>
@@ -7729,7 +7738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="37.5">
       <c r="A26" s="13"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -7745,7 +7754,7 @@
       </c>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="13"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -7761,7 +7770,7 @@
       </c>
       <c r="J27" s="14"/>
     </row>
-    <row r="28" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="62.5">
       <c r="A28" s="13" t="s">
         <v>434</v>
       </c>
@@ -7791,7 +7800,7 @@
       </c>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="25">
       <c r="A29" s="13" t="s">
         <v>438</v>
       </c>
@@ -7821,7 +7830,7 @@
       </c>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="28">
       <c r="A30" s="13" t="s">
         <v>442</v>
       </c>
@@ -7851,7 +7860,7 @@
       </c>
       <c r="J30" s="14"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="13"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -7867,7 +7876,7 @@
       </c>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="25">
       <c r="A32" s="13" t="s">
         <v>444</v>
       </c>
@@ -7899,7 +7908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="13"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -7915,7 +7924,7 @@
       </c>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="50">
       <c r="A34" s="13" t="s">
         <v>447</v>
       </c>
@@ -7945,7 +7954,7 @@
       </c>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="50">
       <c r="A35" s="13"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -7961,7 +7970,7 @@
       </c>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="25">
       <c r="A36" s="13" t="s">
         <v>453</v>
       </c>
@@ -7991,7 +8000,7 @@
       </c>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" s="13"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -8007,7 +8016,7 @@
       </c>
       <c r="J37" s="14"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" s="13"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -8021,7 +8030,7 @@
       <c r="I38" s="8"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="28">
       <c r="A39" s="13" t="s">
         <v>456</v>
       </c>
@@ -8051,7 +8060,7 @@
       </c>
       <c r="J39" s="14"/>
     </row>
-    <row r="40" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="25">
       <c r="A40" s="13" t="s">
         <v>458</v>
       </c>
@@ -8083,7 +8092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="42">
       <c r="A41" s="13"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -8099,7 +8108,7 @@
       </c>
       <c r="J41" s="14"/>
     </row>
-    <row r="42" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="50">
       <c r="A42" s="13" t="s">
         <v>461</v>
       </c>
@@ -8129,7 +8138,7 @@
       </c>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10">
       <c r="A43" s="13" t="s">
         <v>465</v>
       </c>
@@ -8159,7 +8168,7 @@
       </c>
       <c r="J43" s="14"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10">
       <c r="A44" s="13"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -8175,7 +8184,7 @@
       </c>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10">
       <c r="A45" s="13"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -8191,7 +8200,7 @@
       </c>
       <c r="J45" s="14"/>
     </row>
-    <row r="46" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="25">
       <c r="A46" s="13" t="s">
         <v>467</v>
       </c>
@@ -8223,7 +8232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="28">
       <c r="A47" s="13"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -8239,7 +8248,7 @@
       </c>
       <c r="J47" s="14"/>
     </row>
-    <row r="48" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="37.5">
       <c r="A48" s="13" t="s">
         <v>468</v>
       </c>
@@ -8269,7 +8278,7 @@
       </c>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10">
       <c r="A49" s="13"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -8285,7 +8294,7 @@
       </c>
       <c r="J49" s="14"/>
     </row>
-    <row r="50" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="62.5">
       <c r="A50" s="13" t="s">
         <v>472</v>
       </c>
@@ -8315,7 +8324,7 @@
       </c>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10">
       <c r="A51" s="13"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -8331,7 +8340,7 @@
       </c>
       <c r="J51" s="14"/>
     </row>
-    <row r="52" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="62.5">
       <c r="A52" s="13" t="s">
         <v>475</v>
       </c>
@@ -8361,7 +8370,7 @@
       </c>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="25">
       <c r="A53" s="13" t="s">
         <v>478</v>
       </c>
@@ -8391,7 +8400,7 @@
       </c>
       <c r="J53" s="4"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10">
       <c r="A54" s="13"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -8407,7 +8416,7 @@
       </c>
       <c r="J54" s="14"/>
     </row>
-    <row r="55" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="50">
       <c r="A55" s="13" t="s">
         <v>480</v>
       </c>
@@ -8437,7 +8446,7 @@
       </c>
       <c r="J55" s="4"/>
     </row>
-    <row r="56" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="50">
       <c r="A56" s="13" t="s">
         <v>483</v>
       </c>
@@ -8467,7 +8476,7 @@
       </c>
       <c r="J56" s="4"/>
     </row>
-    <row r="57" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="37.5">
       <c r="A57" s="13"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -8483,7 +8492,7 @@
       </c>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10">
       <c r="A58" s="13"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -8499,7 +8508,7 @@
       </c>
       <c r="J58" s="14"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10">
       <c r="A59" s="13" t="s">
         <v>487</v>
       </c>
@@ -8529,7 +8538,7 @@
       </c>
       <c r="J59" s="14"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10">
       <c r="A60" s="13"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -8545,7 +8554,7 @@
       </c>
       <c r="J60" s="4"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10">
       <c r="A61" s="13"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -8561,7 +8570,7 @@
       </c>
       <c r="J61" s="14"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10">
       <c r="A62" s="13" t="s">
         <v>491</v>
       </c>
@@ -8593,7 +8602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="37.5">
       <c r="A63" s="13"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -8609,7 +8618,7 @@
       </c>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="62.5">
       <c r="A64" s="13" t="s">
         <v>494</v>
       </c>
@@ -8639,7 +8648,7 @@
       </c>
       <c r="J64" s="4"/>
     </row>
-    <row r="65" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="28">
       <c r="A65" s="13" t="s">
         <v>498</v>
       </c>
@@ -8669,7 +8678,7 @@
       </c>
       <c r="J65" s="14"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10">
       <c r="A66" s="13"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -8685,7 +8694,7 @@
       </c>
       <c r="J66" s="14"/>
     </row>
-    <row r="67" spans="1:10" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="75">
       <c r="A67" s="13" t="s">
         <v>500</v>
       </c>
@@ -8715,7 +8724,7 @@
       </c>
       <c r="J67" s="4"/>
     </row>
-    <row r="68" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="28">
       <c r="A68" s="13" t="s">
         <v>504</v>
       </c>
@@ -8745,7 +8754,7 @@
       </c>
       <c r="J68" s="14"/>
     </row>
-    <row r="69" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="62.5">
       <c r="A69" s="13"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -8761,7 +8770,7 @@
       </c>
       <c r="J69" s="4"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10">
       <c r="A70" s="13"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -8777,7 +8786,7 @@
       </c>
       <c r="J70" s="14"/>
     </row>
-    <row r="71" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="42">
       <c r="A71" s="13" t="s">
         <v>507</v>
       </c>
@@ -8807,7 +8816,7 @@
       </c>
       <c r="J71" s="14"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10">
       <c r="A72" s="13"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -8823,7 +8832,7 @@
       </c>
       <c r="J72" s="14"/>
     </row>
-    <row r="73" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="25">
       <c r="A73" s="13" t="s">
         <v>509</v>
       </c>
@@ -8853,7 +8862,7 @@
       </c>
       <c r="J73" s="4"/>
     </row>
-    <row r="74" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="70">
       <c r="A74" s="13"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -8869,7 +8878,7 @@
       </c>
       <c r="J74" s="14"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10">
       <c r="A75" s="13"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -8885,7 +8894,7 @@
       </c>
       <c r="J75" s="14"/>
     </row>
-    <row r="76" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="62.5">
       <c r="A76" s="13" t="s">
         <v>511</v>
       </c>
@@ -8915,7 +8924,7 @@
       </c>
       <c r="J76" s="4"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10">
       <c r="A77" s="13" t="s">
         <v>515</v>
       </c>
@@ -8945,7 +8954,7 @@
       </c>
       <c r="J77" s="14"/>
     </row>
-    <row r="78" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="28">
       <c r="A78" s="13"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -8961,7 +8970,7 @@
       </c>
       <c r="J78" s="14"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10">
       <c r="A79" s="13"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -8977,7 +8986,7 @@
       </c>
       <c r="J79" s="14"/>
     </row>
-    <row r="80" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="50">
       <c r="A80" s="13" t="s">
         <v>517</v>
       </c>
@@ -9007,7 +9016,7 @@
       </c>
       <c r="J80" s="4"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10">
       <c r="A81" s="13"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -9021,7 +9030,7 @@
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
     </row>
-    <row r="82" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="50">
       <c r="A82" s="13" t="s">
         <v>520</v>
       </c>
@@ -9051,7 +9060,7 @@
       </c>
       <c r="J82" s="4"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10">
       <c r="A83" s="13"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -9065,7 +9074,7 @@
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
     </row>
-    <row r="84" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="25">
       <c r="A84" s="13" t="s">
         <v>523</v>
       </c>
@@ -9097,7 +9106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10">
       <c r="A85" s="13"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -9113,7 +9122,7 @@
       </c>
       <c r="J85" s="14"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10">
       <c r="A86" s="13" t="s">
         <v>527</v>
       </c>
@@ -9145,7 +9154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10">
       <c r="A87" s="13" t="s">
         <v>529</v>
       </c>
@@ -9175,7 +9184,7 @@
       </c>
       <c r="J87" s="14"/>
     </row>
-    <row r="88" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="25">
       <c r="A88" s="13"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -9191,7 +9200,7 @@
       </c>
       <c r="J88" s="4"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10">
       <c r="A89" s="13"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -9207,7 +9216,7 @@
       </c>
       <c r="J89" s="14"/>
     </row>
-    <row r="90" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="25">
       <c r="A90" s="13" t="s">
         <v>531</v>
       </c>
@@ -9239,7 +9248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="50">
       <c r="A91" s="13" t="s">
         <v>533</v>
       </c>
@@ -9269,7 +9278,7 @@
       </c>
       <c r="J91" s="4"/>
     </row>
-    <row r="92" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="62.5">
       <c r="A92" s="13" t="s">
         <v>537</v>
       </c>
@@ -9299,7 +9308,7 @@
       </c>
       <c r="J92" s="4"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10">
       <c r="A93" s="13"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -9313,7 +9322,7 @@
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
     </row>
-    <row r="94" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10">
       <c r="A94" s="13" t="s">
         <v>540</v>
       </c>
@@ -9343,7 +9352,7 @@
       </c>
       <c r="J94" s="14"/>
     </row>
-    <row r="95" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="25">
       <c r="A95" s="13"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -9359,7 +9368,7 @@
       </c>
       <c r="J95" s="4"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10">
       <c r="A96" s="13"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -9375,7 +9384,7 @@
       </c>
       <c r="J96" s="14"/>
     </row>
-    <row r="97" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="50">
       <c r="A97" s="13" t="s">
         <v>543</v>
       </c>
@@ -9405,7 +9414,7 @@
       </c>
       <c r="J97" s="14"/>
     </row>
-    <row r="98" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="37.5">
       <c r="A98" s="13"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -9421,7 +9430,7 @@
       </c>
       <c r="J98" s="4"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10">
       <c r="A99" s="13"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -9437,7 +9446,7 @@
       </c>
       <c r="J99" s="14"/>
     </row>
-    <row r="100" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="28">
       <c r="A100" s="13" t="s">
         <v>547</v>
       </c>
@@ -9467,7 +9476,7 @@
       </c>
       <c r="J100" s="14"/>
     </row>
-    <row r="101" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="50">
       <c r="A101" s="13" t="s">
         <v>549</v>
       </c>
@@ -9497,7 +9506,7 @@
       </c>
       <c r="J101" s="4"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10">
       <c r="A102" s="13"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -9513,7 +9522,7 @@
       </c>
       <c r="J102" s="14"/>
     </row>
-    <row r="103" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="28">
       <c r="A103" s="13" t="s">
         <v>553</v>
       </c>
@@ -9543,7 +9552,7 @@
       </c>
       <c r="J103" s="4"/>
     </row>
-    <row r="104" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="37.5">
       <c r="A104" s="13"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -9557,7 +9566,7 @@
       <c r="I104" s="4"/>
       <c r="J104" s="4"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10">
       <c r="A105" s="13"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -9571,7 +9580,7 @@
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
     </row>
-    <row r="106" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="28">
       <c r="A106" s="13" t="s">
         <v>556</v>
       </c>
@@ -9773,7 +9782,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53A55E73-7352-4A59-9A14-0CC045D3CCAF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9783,19 +9792,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.4140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.75" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="44.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.4140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="9" max="16384" width="8.9140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9824,7 +9833,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1">
       <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
@@ -9853,7 +9862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="25" hidden="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -9867,7 +9876,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1">
       <c r="A4" s="13" t="s">
         <v>15</v>
       </c>
@@ -9896,7 +9905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="28" hidden="1">
       <c r="A5" s="13"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -9910,7 +9919,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="28" hidden="1">
       <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
@@ -9939,7 +9948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1">
       <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
@@ -9968,7 +9977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1">
       <c r="A8" s="13"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -9982,7 +9991,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1">
       <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
@@ -10011,7 +10020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1">
       <c r="A10" s="13"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -10025,7 +10034,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1">
       <c r="A11" s="13" t="s">
         <v>29</v>
       </c>
@@ -10054,7 +10063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="25" hidden="1">
       <c r="A12" s="13"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -10068,7 +10077,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="37.5" hidden="1">
       <c r="A13" s="13" t="s">
         <v>35</v>
       </c>
@@ -10097,7 +10106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1">
       <c r="A14" s="13"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -10111,7 +10120,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1">
       <c r="A15" s="13" t="s">
         <v>40</v>
       </c>
@@ -10140,7 +10149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1">
       <c r="A16" s="13"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -10154,7 +10163,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1">
       <c r="A17" s="13" t="s">
         <v>45</v>
       </c>
@@ -10183,7 +10192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="28" hidden="1">
       <c r="A18" s="13" t="s">
         <v>49</v>
       </c>
@@ -10212,7 +10221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1">
       <c r="A19" s="13" t="s">
         <v>51</v>
       </c>
@@ -10241,7 +10250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="13"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -10255,7 +10264,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1">
       <c r="A21" s="13" t="s">
         <v>54</v>
       </c>
@@ -10284,7 +10293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="25" hidden="1">
       <c r="A22" s="13"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -10296,7 +10305,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1">
       <c r="A23" s="13" t="s">
         <v>57</v>
       </c>
@@ -10325,7 +10334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1">
       <c r="A24" s="13"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -10339,7 +10348,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="25" hidden="1">
       <c r="A25" s="13" t="s">
         <v>61</v>
       </c>
@@ -10368,7 +10377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1">
       <c r="A26" s="13"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -10382,7 +10391,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="25" hidden="1">
       <c r="A27" s="13" t="s">
         <v>65</v>
       </c>
@@ -10411,7 +10420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1">
       <c r="A28" s="13" t="s">
         <v>69</v>
       </c>
@@ -10440,7 +10449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1">
       <c r="A29" s="13"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -10454,7 +10463,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="37.5" hidden="1">
       <c r="A30" s="13" t="s">
         <v>72</v>
       </c>
@@ -10483,7 +10492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1">
       <c r="A31" s="13" t="s">
         <v>76</v>
       </c>
@@ -10512,7 +10521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="28" hidden="1">
       <c r="A32" s="13"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -10526,7 +10535,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="28" hidden="1">
       <c r="A33" s="13" t="s">
         <v>79</v>
       </c>
@@ -10555,7 +10564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="28" hidden="1">
       <c r="A34" s="13" t="s">
         <v>81</v>
       </c>
@@ -10584,7 +10593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="28" hidden="1">
       <c r="A35" s="13" t="s">
         <v>83</v>
       </c>
@@ -10613,7 +10622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1">
       <c r="A36" s="13" t="s">
         <v>85</v>
       </c>
@@ -10642,7 +10651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1">
       <c r="A37" s="13"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -10656,7 +10665,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="25">
       <c r="A38" s="13" t="s">
         <v>87</v>
       </c>
@@ -10685,7 +10694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1">
       <c r="A39" s="13" t="s">
         <v>91</v>
       </c>
@@ -10714,7 +10723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="28" hidden="1">
       <c r="A40" s="13"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -10728,7 +10737,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="25" hidden="1">
       <c r="A41" s="13" t="s">
         <v>94</v>
       </c>
@@ -10757,7 +10766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1">
       <c r="A42" s="13" t="s">
         <v>98</v>
       </c>
@@ -10786,7 +10795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="28">
       <c r="A43" s="13" t="s">
         <v>100</v>
       </c>
@@ -10815,7 +10824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1">
       <c r="A44" s="13"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -10829,7 +10838,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="28" hidden="1">
       <c r="A45" s="13" t="s">
         <v>102</v>
       </c>
@@ -10858,7 +10867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1">
       <c r="A46" s="13" t="s">
         <v>104</v>
       </c>
@@ -10887,7 +10896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="28" hidden="1">
       <c r="A47" s="13"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -10901,7 +10910,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1">
       <c r="A48" s="13"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -10915,7 +10924,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="26" hidden="1">
       <c r="A49" s="13" t="s">
         <v>106</v>
       </c>
@@ -10944,7 +10953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1">
       <c r="A50" s="13" t="s">
         <v>108</v>
       </c>
@@ -10973,7 +10982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="25" hidden="1">
       <c r="A51" s="13"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -10987,7 +10996,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1">
       <c r="A52" s="13"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -11001,7 +11010,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="38.5" hidden="1">
       <c r="A53" s="13" t="s">
         <v>112</v>
       </c>
@@ -11030,7 +11039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1">
       <c r="A54" s="13" t="s">
         <v>114</v>
       </c>
@@ -11059,7 +11068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="37.5" hidden="1">
       <c r="A55" s="13"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -11073,7 +11082,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1">
       <c r="A56" s="13" t="s">
         <v>118</v>
       </c>
@@ -11102,7 +11111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="28" hidden="1">
       <c r="A57" s="13"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -11116,7 +11125,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1">
       <c r="A58" s="13" t="s">
         <v>120</v>
       </c>
@@ -11145,7 +11154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1">
       <c r="A59" s="13"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -11159,7 +11168,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="28" hidden="1">
       <c r="A60" s="13" t="s">
         <v>122</v>
       </c>
@@ -11188,7 +11197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1">
       <c r="A61" s="13" t="s">
         <v>124</v>
       </c>
@@ -11217,7 +11226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="25" hidden="1">
       <c r="A62" s="13"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -11231,7 +11240,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1">
       <c r="A63" s="13" t="s">
         <v>128</v>
       </c>
@@ -11260,7 +11269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="28" hidden="1">
       <c r="A64" s="13"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -11274,7 +11283,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1">
       <c r="A65" s="13" t="s">
         <v>130</v>
       </c>
@@ -11303,7 +11312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1">
       <c r="A66" s="13"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -11317,7 +11326,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="25" hidden="1">
       <c r="A67" s="13" t="s">
         <v>134</v>
       </c>
@@ -11346,7 +11355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="28" hidden="1">
       <c r="A68" s="13"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -11360,7 +11369,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" s="13" t="s">
         <v>138</v>
       </c>
@@ -11389,7 +11398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1">
       <c r="A70" s="13"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -11403,7 +11412,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="25" hidden="1">
       <c r="A71" s="13" t="s">
         <v>140</v>
       </c>
@@ -11432,7 +11441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="25" hidden="1">
       <c r="A72" s="13"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -11446,7 +11455,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1">
       <c r="A73" s="13"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -11460,7 +11469,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1">
       <c r="A74" s="13" t="s">
         <v>144</v>
       </c>
@@ -11489,7 +11498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1">
       <c r="A75" s="13" t="s">
         <v>146</v>
       </c>
@@ -11518,7 +11527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1">
       <c r="A76" s="13"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -11532,7 +11541,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1">
       <c r="A77" s="13" t="s">
         <v>148</v>
       </c>
@@ -11561,7 +11570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1">
       <c r="A78" s="13"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -11575,7 +11584,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="42" hidden="1">
       <c r="A79" s="13" t="s">
         <v>151</v>
       </c>
@@ -11604,7 +11613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" s="13" t="s">
         <v>153</v>
       </c>
@@ -11633,7 +11642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1">
       <c r="A81" s="13"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -11645,7 +11654,7 @@
       <c r="G81" s="4"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="28" hidden="1">
       <c r="A82" s="13" t="s">
         <v>155</v>
       </c>
@@ -11674,7 +11683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9">
       <c r="A83" s="13" t="s">
         <v>157</v>
       </c>
@@ -11703,7 +11712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1">
       <c r="A84" s="13"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -11717,7 +11726,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1">
       <c r="A85" s="13"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -11731,7 +11740,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1">
       <c r="A86" s="13"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -11745,7 +11754,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1">
       <c r="A87" s="13" t="s">
         <v>161</v>
       </c>
@@ -11774,7 +11783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="28" hidden="1">
       <c r="A88" s="13"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -11788,7 +11797,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1">
       <c r="A89" s="13" t="s">
         <v>163</v>
       </c>
@@ -11817,7 +11826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1">
       <c r="A90" s="13"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -11831,7 +11840,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="28" hidden="1">
       <c r="A91" s="13" t="s">
         <v>166</v>
       </c>
@@ -11860,7 +11869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1">
       <c r="A92" s="13"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -11874,7 +11883,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1">
       <c r="A93" s="13" t="s">
         <v>168</v>
       </c>
@@ -11903,7 +11912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1">
       <c r="A94" s="13"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -11917,7 +11926,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="42" hidden="1">
       <c r="A95" s="13" t="s">
         <v>172</v>
       </c>
@@ -11946,7 +11955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1">
       <c r="A96" s="13" t="s">
         <v>174</v>
       </c>
@@ -11975,7 +11984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="25" hidden="1">
       <c r="A97" s="13"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -11989,7 +11998,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1">
       <c r="A98" s="13" t="s">
         <v>178</v>
       </c>
@@ -12018,7 +12027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="28" hidden="1">
       <c r="A99" s="13"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -12032,7 +12041,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1">
       <c r="A100" s="13"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -12046,7 +12055,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1">
       <c r="A101" s="13" t="s">
         <v>182</v>
       </c>
@@ -12075,7 +12084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="28" hidden="1">
       <c r="A102" s="13"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -12089,7 +12098,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="28" hidden="1">
       <c r="A103" s="13" t="s">
         <v>184</v>
       </c>
@@ -12118,7 +12127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1">
       <c r="A104" s="13" t="s">
         <v>186</v>
       </c>
@@ -12147,7 +12156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1">
       <c r="A105" s="13"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -12161,7 +12170,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="26" hidden="1">
       <c r="A106" s="13" t="s">
         <v>189</v>
       </c>
@@ -12190,7 +12199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1">
       <c r="A107" s="13" t="s">
         <v>191</v>
       </c>
@@ -12219,7 +12228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1">
       <c r="A108" s="13"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -12233,7 +12242,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1">
       <c r="A109" s="13" t="s">
         <v>193</v>
       </c>
@@ -12262,7 +12271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" ht="28" hidden="1">
       <c r="A110" s="13"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -12276,7 +12285,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="28" hidden="1">
       <c r="A111" s="13" t="s">
         <v>195</v>
       </c>
@@ -12305,7 +12314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1">
       <c r="A112" s="13"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -12319,7 +12328,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1">
       <c r="A113" s="13" t="s">
         <v>197</v>
       </c>
@@ -12348,7 +12357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1">
       <c r="A114" s="13"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -12362,7 +12371,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="26" hidden="1">
       <c r="A115" s="13" t="s">
         <v>199</v>
       </c>
@@ -12391,7 +12400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1">
       <c r="A116" s="13"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -12405,7 +12414,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="28" hidden="1">
       <c r="A117" s="13" t="s">
         <v>201</v>
       </c>
@@ -12434,7 +12443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="28" hidden="1">
       <c r="A118" s="13" t="s">
         <v>203</v>
       </c>
@@ -12463,7 +12472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="28" hidden="1">
       <c r="A119" s="13" t="s">
         <v>205</v>
       </c>
@@ -12492,7 +12501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="28" hidden="1">
       <c r="A120" s="13" t="s">
         <v>209</v>
       </c>
@@ -12521,7 +12530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1">
       <c r="A121" s="13" t="s">
         <v>211</v>
       </c>
@@ -12550,7 +12559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1">
       <c r="A122" s="13"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -12564,7 +12573,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1">
       <c r="A123" s="13" t="s">
         <v>213</v>
       </c>
@@ -12593,7 +12602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1">
       <c r="A124" s="13" t="s">
         <v>217</v>
       </c>
@@ -12622,7 +12631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1">
       <c r="A125" s="13"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -12636,7 +12645,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1">
       <c r="A126" s="13"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -12650,7 +12659,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1">
       <c r="A127" s="13" t="s">
         <v>220</v>
       </c>
@@ -12679,7 +12688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="25" hidden="1">
       <c r="A128" s="13"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -12693,7 +12702,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1">
       <c r="A129" s="13"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -12707,7 +12716,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="25" hidden="1">
       <c r="A130" s="13" t="s">
         <v>223</v>
       </c>
@@ -12736,7 +12745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1">
       <c r="A131" s="13" t="s">
         <v>227</v>
       </c>
@@ -12765,7 +12774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="28.2" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" ht="28.5" hidden="1" thickBot="1">
       <c r="A132" s="10"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
@@ -13004,13 +13013,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E36262C3-D2A1-452A-BE28-BB8976CDADC0}">
   <dimension ref="A1:J134"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
-    <col min="8" max="9" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.4140625" customWidth="1"/>
+    <col min="8" max="9" width="10.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -13042,7 +13051,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="79.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="62.5">
       <c r="A2" s="13" t="s">
         <v>580</v>
       </c>
@@ -13070,8 +13079,11 @@
       <c r="I2" s="18" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="13" t="s">
         <v>585</v>
       </c>
@@ -13103,7 +13115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="25">
       <c r="A4" s="13"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -13118,7 +13130,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="55.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="56">
       <c r="A5" s="13" t="s">
         <v>588</v>
       </c>
@@ -13138,7 +13150,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="H5" s="17">
         <v>1</v>
@@ -13146,8 +13158,11 @@
       <c r="I5" s="7" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="55.2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="56">
       <c r="A6" s="13"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -13157,15 +13172,15 @@
       <c r="G6" s="6"/>
       <c r="H6" s="17"/>
       <c r="I6" s="7" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="37.5">
       <c r="A7" s="13" t="s">
+        <v>846</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>590</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>591</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>582</v>
@@ -13180,16 +13195,19 @@
         <v>1</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H7" s="17">
         <v>1</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="37.5">
       <c r="A8" s="13"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -13197,19 +13215,19 @@
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
       <c r="G8" s="17" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H8" s="17"/>
       <c r="I8" s="18" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="42">
       <c r="A9" s="13" t="s">
+        <v>594</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>595</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>596</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>582</v>
@@ -13224,21 +13242,24 @@
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H9" s="17">
         <v>1</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>797</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>597</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>598</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>582</v>
@@ -13253,16 +13274,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H10" s="17">
         <v>0</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>599</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="13"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -13277,7 +13301,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="13"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -13292,12 +13316,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="28">
       <c r="A13" s="13" t="s">
+        <v>600</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>582</v>
@@ -13324,7 +13348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="13"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -13339,12 +13363,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="25">
       <c r="A15" s="13" t="s">
+        <v>602</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>603</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>604</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>582</v>
@@ -13359,7 +13383,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H15" s="17">
         <v>0</v>
@@ -13367,8 +13391,11 @@
       <c r="I15" s="18" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="13"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -13383,7 +13410,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="13"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -13398,12 +13425,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="25">
       <c r="A18" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>606</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>607</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>582</v>
@@ -13430,7 +13457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="82.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="70">
       <c r="A19" s="13"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -13438,19 +13465,19 @@
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="6" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="7" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="42">
       <c r="A20" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>608</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>609</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>582</v>
@@ -13465,24 +13492,24 @@
         <v>1</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="H20" s="17">
         <v>1</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="28">
       <c r="A21" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>610</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>611</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>582</v>
@@ -13505,8 +13532,11 @@
       <c r="I21" s="7" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="55.2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="56">
       <c r="A22" s="13"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -13514,19 +13544,19 @@
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="6" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="7" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="56">
       <c r="A23" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="B23" s="17" t="s">
         <v>612</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>613</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>582</v>
@@ -13541,21 +13571,24 @@
         <v>2</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="H23" s="17">
         <v>2</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>804</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="37.5">
       <c r="A24" s="13" t="s">
+        <v>613</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>614</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>615</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>582</v>
@@ -13570,16 +13603,19 @@
         <v>3</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H24" s="17">
         <v>2</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.25">
+        <v>615</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="62.5">
       <c r="A25" s="13"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -13587,19 +13623,19 @@
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
       <c r="G25" s="17" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H25" s="17"/>
       <c r="I25" s="18" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="75">
+      <c r="A26" s="13" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="79.2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+      <c r="B26" s="17" t="s">
         <v>618</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>619</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>582</v>
@@ -13614,21 +13650,24 @@
         <v>1</v>
       </c>
       <c r="G26" s="17" t="s">
+        <v>619</v>
+      </c>
+      <c r="H26" s="17">
+        <v>1</v>
+      </c>
+      <c r="I26" s="18" t="s">
         <v>620</v>
       </c>
-      <c r="H26" s="17">
-        <v>1</v>
-      </c>
-      <c r="I26" s="18" t="s">
+      <c r="J26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="25">
+      <c r="A27" s="13" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+      <c r="B27" s="17" t="s">
         <v>622</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>623</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>582</v>
@@ -13643,16 +13682,19 @@
         <v>0</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H27" s="17">
         <v>0</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="37.5">
       <c r="A28" s="13"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -13660,14 +13702,14 @@
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="18" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="13"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -13680,12 +13722,12 @@
       <c r="H29" s="17"/>
       <c r="I29" s="18"/>
     </row>
-    <row r="30" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="62.5">
       <c r="A30" s="13" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>627</v>
+        <v>837</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>582</v>
@@ -13700,21 +13742,24 @@
         <v>1</v>
       </c>
       <c r="G30" s="17" t="s">
+        <v>626</v>
+      </c>
+      <c r="H30" s="17">
+        <v>1</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="56">
+      <c r="A31" s="13" t="s">
         <v>628</v>
       </c>
-      <c r="H30" s="17">
-        <v>1</v>
-      </c>
-      <c r="I30" s="18" t="s">
+      <c r="B31" s="17" t="s">
         <v>629</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>630</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>631</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>582</v>
@@ -13729,16 +13774,19 @@
         <v>1</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="H31" s="17">
         <v>1</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>806</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="13"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -13753,12 +13801,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="25">
       <c r="A33" s="13" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>582</v>
@@ -13781,8 +13829,11 @@
       <c r="I33" s="18" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="92.4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="87.5">
       <c r="A34" s="13"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -13790,19 +13841,19 @@
       <c r="E34" s="17"/>
       <c r="F34" s="17"/>
       <c r="G34" s="17" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="H34" s="17"/>
       <c r="I34" s="18" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="28">
+      <c r="A35" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="B35" s="17" t="s">
         <v>635</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>636</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>637</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>582</v>
@@ -13829,7 +13880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="42">
       <c r="A36" s="13"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -13837,19 +13888,19 @@
       <c r="E36" s="17"/>
       <c r="F36" s="17"/>
       <c r="G36" s="6" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="7" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="25">
       <c r="A37" s="13" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>582</v>
@@ -13864,16 +13915,19 @@
         <v>0</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H37" s="17">
         <v>0</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="25">
       <c r="A38" s="13"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -13881,19 +13935,19 @@
       <c r="E38" s="17"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H38" s="17"/>
       <c r="I38" s="18" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="28">
       <c r="A39" s="13" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>582</v>
@@ -13908,16 +13962,19 @@
         <v>2</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="H39" s="17">
         <v>2</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="105.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>810</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="100">
       <c r="A40" s="13"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -13925,19 +13982,19 @@
       <c r="E40" s="17"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H40" s="17"/>
       <c r="I40" s="18" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="51.5">
+      <c r="A41" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="B41" s="17" t="s">
         <v>644</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
-        <v>645</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>646</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>582</v>
@@ -13952,16 +14009,19 @@
         <v>2</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="H41" s="17">
         <v>2</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>812</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="13"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -13976,12 +14036,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="50">
       <c r="A43" s="13" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>582</v>
@@ -13996,24 +14056,24 @@
         <v>1</v>
       </c>
       <c r="G43" s="17" t="s">
+        <v>647</v>
+      </c>
+      <c r="H43" s="17">
+        <v>1</v>
+      </c>
+      <c r="I43" s="18" t="s">
+        <v>648</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="25">
+      <c r="A44" s="13" t="s">
         <v>649</v>
       </c>
-      <c r="H43" s="17">
-        <v>1</v>
-      </c>
-      <c r="I43" s="18" t="s">
+      <c r="B44" s="17" t="s">
         <v>650</v>
-      </c>
-      <c r="J43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
-        <v>651</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>652</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>582</v>
@@ -14040,7 +14100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="25">
       <c r="A45" s="13"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -14048,14 +14108,14 @@
       <c r="E45" s="17"/>
       <c r="F45" s="17"/>
       <c r="G45" s="17" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H45" s="17"/>
       <c r="I45" s="18" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="25">
       <c r="A46" s="13"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -14063,19 +14123,19 @@
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
       <c r="G46" s="17" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H46" s="17"/>
       <c r="I46" s="18" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="28">
+      <c r="A47" s="13" t="s">
+        <v>653</v>
+      </c>
+      <c r="B47" s="17" t="s">
         <v>654</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A47" s="13" t="s">
-        <v>655</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>656</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>582</v>
@@ -14098,8 +14158,11 @@
       <c r="I47" s="7" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="25">
       <c r="A48" s="13"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -14107,19 +14170,19 @@
       <c r="E48" s="17"/>
       <c r="F48" s="17"/>
       <c r="G48" s="17" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="H48" s="17"/>
       <c r="I48" s="18" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="28">
       <c r="A49" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>582</v>
@@ -14134,21 +14197,21 @@
         <v>1</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="H49" s="17">
         <v>1</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="28">
       <c r="A50" s="13" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B50" s="17" t="s">
         <v>82</v>
@@ -14178,12 +14241,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="28">
       <c r="A51" s="13" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>582</v>
@@ -14210,12 +14273,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="37.5">
       <c r="A52" s="13" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>582</v>
@@ -14230,16 +14293,19 @@
         <v>1</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H52" s="17">
         <v>1</v>
       </c>
       <c r="I52" s="18" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>664</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="13"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -14254,12 +14320,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="28">
       <c r="A54" s="13" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>582</v>
@@ -14286,7 +14352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="41.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="42">
       <c r="A55" s="13"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -14294,19 +14360,19 @@
       <c r="E55" s="17"/>
       <c r="F55" s="17"/>
       <c r="G55" s="6" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="H55" s="17"/>
       <c r="I55" s="7" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="50">
       <c r="A56" s="13" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>582</v>
@@ -14321,16 +14387,19 @@
         <v>1</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="H56" s="17">
         <v>0</v>
       </c>
       <c r="I56" s="18" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>669</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="37.5">
       <c r="A57" s="13"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -14345,7 +14414,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10">
       <c r="A58" s="13"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -14360,12 +14429,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="50">
       <c r="A59" s="13" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>582</v>
@@ -14380,16 +14449,19 @@
         <v>-1</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H59" s="17">
         <v>-1</v>
       </c>
       <c r="I59" s="18" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>673</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" s="13"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -14404,12 +14476,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="25">
       <c r="A61" s="13" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>582</v>
@@ -14432,8 +14504,11 @@
       <c r="I61" s="18" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" ht="92.4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="87.5">
       <c r="A62" s="13"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -14441,14 +14516,14 @@
       <c r="E62" s="17"/>
       <c r="F62" s="17"/>
       <c r="G62" s="17" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H62" s="17"/>
       <c r="I62" s="18" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="13"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -14463,12 +14538,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="82.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="84">
       <c r="A64" s="13" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>582</v>
@@ -14483,21 +14558,24 @@
         <v>2</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="H64" s="17">
         <v>1</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>817</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="13" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>582</v>
@@ -14520,8 +14598,11 @@
       <c r="I65" s="18" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" ht="69" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="70">
       <c r="A66" s="13"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -14529,19 +14610,19 @@
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="6" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="H66" s="17"/>
       <c r="I66" s="7" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="75">
       <c r="A67" s="13" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C67" s="17" t="s">
         <v>582</v>
@@ -14556,16 +14637,19 @@
         <v>3</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H67" s="17">
         <v>3</v>
       </c>
       <c r="I67" s="18" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>683</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="25">
       <c r="A68" s="13"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -14573,19 +14657,19 @@
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H68" s="17"/>
       <c r="I68" s="18" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="37.5">
+      <c r="A69" s="13" t="s">
+        <v>686</v>
+      </c>
+      <c r="B69" s="17" t="s">
         <v>687</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
-        <v>688</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>689</v>
       </c>
       <c r="C69" s="17" t="s">
         <v>582</v>
@@ -14600,21 +14684,24 @@
         <v>1</v>
       </c>
       <c r="G69" s="17" t="s">
+        <v>688</v>
+      </c>
+      <c r="H69" s="17">
+        <v>1</v>
+      </c>
+      <c r="I69" s="18" t="s">
+        <v>689</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="87.5">
+      <c r="A70" s="13" t="s">
         <v>690</v>
       </c>
-      <c r="H69" s="17">
-        <v>1</v>
-      </c>
-      <c r="I69" s="18" t="s">
+      <c r="B70" s="17" t="s">
         <v>691</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="92.4" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
-        <v>692</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>693</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>582</v>
@@ -14629,21 +14716,24 @@
         <v>1</v>
       </c>
       <c r="G70" s="17" t="s">
+        <v>692</v>
+      </c>
+      <c r="H70" s="17">
+        <v>1</v>
+      </c>
+      <c r="I70" s="18" t="s">
+        <v>693</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="62.5">
+      <c r="A71" s="13" t="s">
         <v>694</v>
       </c>
-      <c r="H70" s="17">
-        <v>1</v>
-      </c>
-      <c r="I70" s="18" t="s">
+      <c r="B71" s="17" t="s">
         <v>695</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="66" x14ac:dyDescent="0.25">
-      <c r="A71" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>697</v>
       </c>
       <c r="C71" s="17" t="s">
         <v>582</v>
@@ -14658,21 +14748,24 @@
         <v>1</v>
       </c>
       <c r="G71" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="H71" s="17">
+        <v>1</v>
+      </c>
+      <c r="I71" s="18" t="s">
+        <v>697</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="25">
+      <c r="A72" s="13" t="s">
         <v>698</v>
       </c>
-      <c r="H71" s="17">
-        <v>1</v>
-      </c>
-      <c r="I71" s="18" t="s">
+      <c r="B72" s="17" t="s">
         <v>699</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="13" t="s">
-        <v>700</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>701</v>
       </c>
       <c r="C72" s="17" t="s">
         <v>582</v>
@@ -14693,13 +14786,13 @@
         <v>1</v>
       </c>
       <c r="I72" s="18" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="37.5">
       <c r="A73" s="13"/>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -14707,19 +14800,19 @@
       <c r="E73" s="17"/>
       <c r="F73" s="17"/>
       <c r="G73" s="17" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H73" s="17"/>
       <c r="I73" s="18" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="28">
       <c r="A74" s="13" t="s">
-        <v>703</v>
+        <v>839</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>704</v>
+        <v>838</v>
       </c>
       <c r="C74" s="17" t="s">
         <v>582</v>
@@ -14734,21 +14827,24 @@
         <v>1</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="H74" s="17">
         <v>1</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>821</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="25">
       <c r="A75" s="13" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C75" s="17" t="s">
         <v>582</v>
@@ -14763,16 +14859,19 @@
         <v>1</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="H75" s="17">
         <v>1</v>
       </c>
       <c r="I75" s="18" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="92.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="75">
       <c r="A76" s="13"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -14780,19 +14879,19 @@
       <c r="E76" s="17"/>
       <c r="F76" s="17"/>
       <c r="G76" s="17" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="H76" s="17"/>
       <c r="I76" s="18" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="50">
       <c r="A77" s="13" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C77" s="17" t="s">
         <v>582</v>
@@ -14807,16 +14906,19 @@
         <v>0</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H77" s="17">
         <v>0</v>
       </c>
       <c r="I77" s="18" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>708</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="37.5">
       <c r="A78" s="13"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -14824,19 +14926,19 @@
       <c r="E78" s="17"/>
       <c r="F78" s="17"/>
       <c r="G78" s="17" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="H78" s="17"/>
       <c r="I78" s="18" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="25">
       <c r="A79" s="13" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C79" s="17" t="s">
         <v>582</v>
@@ -14859,8 +14961,11 @@
       <c r="I79" s="18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" ht="82.8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="70">
       <c r="A80" s="13"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -14868,19 +14973,19 @@
       <c r="E80" s="17"/>
       <c r="F80" s="17"/>
       <c r="G80" s="6" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="H80" s="17"/>
       <c r="I80" s="7" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="84">
       <c r="A81" s="13" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>718</v>
+        <v>840</v>
       </c>
       <c r="C81" s="17" t="s">
         <v>582</v>
@@ -14895,7 +15000,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>830</v>
+        <v>841</v>
       </c>
       <c r="H81" s="17">
         <v>1</v>
@@ -14903,8 +15008,11 @@
       <c r="I81" s="7" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="82.8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="70">
       <c r="A82" s="13"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -14914,15 +15022,15 @@
       <c r="G82" s="6"/>
       <c r="H82" s="17"/>
       <c r="I82" s="7" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="25">
       <c r="A83" s="13" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="C83" s="17" t="s">
         <v>582</v>
@@ -14937,16 +15045,19 @@
         <v>2</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="H83" s="17">
         <v>2</v>
       </c>
       <c r="I83" s="18" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>717</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="28">
       <c r="A84" s="13"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -14958,15 +15069,15 @@
       </c>
       <c r="H84" s="17"/>
       <c r="I84" s="7" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.25">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="51.5">
       <c r="A85" s="13" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C85" s="17" t="s">
         <v>582</v>
@@ -14981,16 +15092,19 @@
         <v>-1</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="H85" s="17">
         <v>-1</v>
       </c>
       <c r="I85" s="18" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="13"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -15005,12 +15119,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="25">
       <c r="A87" s="13" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C87" s="17" t="s">
         <v>582</v>
@@ -15033,8 +15147,11 @@
       <c r="I87" s="18" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="62.5">
       <c r="A88" s="13"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -15042,19 +15159,19 @@
       <c r="E88" s="17"/>
       <c r="F88" s="17"/>
       <c r="G88" s="17" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="H88" s="17"/>
       <c r="I88" s="18" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="105.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="100">
       <c r="A89" s="13" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="C89" s="17" t="s">
         <v>582</v>
@@ -15069,16 +15186,19 @@
         <v>3</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="H89" s="17">
         <v>2</v>
       </c>
       <c r="I89" s="18" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" s="13"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -15093,12 +15213,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="25">
       <c r="A91" s="13" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C91" s="17" t="s">
         <v>582</v>
@@ -15125,7 +15245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="28">
       <c r="A92" s="13"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -15140,12 +15260,12 @@
         <v>242</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="84">
       <c r="A93" s="13" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>734</v>
+        <v>842</v>
       </c>
       <c r="C93" s="17" t="s">
         <v>582</v>
@@ -15160,21 +15280,24 @@
         <v>1</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="H93" s="17">
         <v>1</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>827</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" s="13" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="C94" s="17" t="s">
         <v>582</v>
@@ -15189,19 +15312,19 @@
         <v>1</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="H94" s="17">
         <v>1</v>
       </c>
       <c r="I94" s="18" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="J94">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="25">
       <c r="A95" s="13"/>
       <c r="B95" s="17"/>
       <c r="C95" s="17"/>
@@ -15209,19 +15332,19 @@
       <c r="E95" s="17"/>
       <c r="F95" s="17"/>
       <c r="G95" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H95" s="17"/>
       <c r="I95" s="18" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.25">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="62.5">
       <c r="A96" s="13" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="C96" s="17" t="s">
         <v>582</v>
@@ -15236,21 +15359,24 @@
         <v>1</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="H96" s="17">
         <v>0</v>
       </c>
       <c r="I96" s="18" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>735</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="37.5">
       <c r="A97" s="13" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C97" s="17" t="s">
         <v>582</v>
@@ -15265,19 +15391,19 @@
         <v>1</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="H97" s="17">
         <v>1</v>
       </c>
       <c r="I97" s="18" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="J97">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10">
       <c r="A98" s="13"/>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -15292,12 +15418,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="25">
       <c r="A99" s="13" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="C99" s="17" t="s">
         <v>582</v>
@@ -15324,7 +15450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="28">
       <c r="A100" s="13"/>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -15332,19 +15458,19 @@
       <c r="E100" s="17"/>
       <c r="F100" s="17"/>
       <c r="G100" s="6" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="H100" s="17"/>
       <c r="I100" s="7" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101" s="13" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="C101" s="17" t="s">
         <v>582</v>
@@ -15371,7 +15497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="25">
       <c r="A102" s="13"/>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -15383,15 +15509,15 @@
       </c>
       <c r="H102" s="17"/>
       <c r="I102" s="18" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="25">
       <c r="A103" s="13" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="C103" s="17" t="s">
         <v>582</v>
@@ -15414,8 +15540,11 @@
       <c r="I103" s="18" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="37.5">
       <c r="A104" s="13"/>
       <c r="B104" s="17"/>
       <c r="C104" s="17"/>
@@ -15423,19 +15552,19 @@
       <c r="E104" s="17"/>
       <c r="F104" s="17"/>
       <c r="G104" s="17" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="H104" s="17"/>
       <c r="I104" s="18" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="25">
       <c r="A105" s="13" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="C105" s="17" t="s">
         <v>582</v>
@@ -15462,7 +15591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10">
       <c r="A106" s="13"/>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
@@ -15477,12 +15606,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="28">
       <c r="A107" s="13" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="C107" s="17" t="s">
         <v>582</v>
@@ -15505,8 +15634,11 @@
       <c r="I107" s="7" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="62.5">
       <c r="A108" s="13"/>
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
@@ -15514,19 +15646,19 @@
       <c r="E108" s="17"/>
       <c r="F108" s="17"/>
       <c r="G108" s="17" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="H108" s="17"/>
       <c r="I108" s="18" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="25">
       <c r="A109" s="13" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="C109" s="17" t="s">
         <v>582</v>
@@ -15541,21 +15673,24 @@
         <v>2</v>
       </c>
       <c r="G109" s="17" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="H109" s="17">
         <v>2</v>
       </c>
       <c r="I109" s="18" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="62.5">
       <c r="A110" s="13" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C110" s="17" t="s">
         <v>582</v>
@@ -15570,16 +15705,19 @@
         <v>1</v>
       </c>
       <c r="G110" s="17" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="H110" s="17">
         <v>0</v>
       </c>
       <c r="I110" s="18" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="50">
       <c r="A111" s="13"/>
       <c r="B111" s="17"/>
       <c r="C111" s="17"/>
@@ -15587,19 +15725,19 @@
       <c r="E111" s="17"/>
       <c r="F111" s="17"/>
       <c r="G111" s="17" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="H111" s="17"/>
       <c r="I111" s="18" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="25">
       <c r="A112" s="13" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="C112" s="17" t="s">
         <v>582</v>
@@ -15614,21 +15752,24 @@
         <v>-1</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="H112" s="17">
         <v>-1</v>
       </c>
       <c r="I112" s="18" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>764</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="25">
       <c r="A113" s="13" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C113" s="17" t="s">
         <v>582</v>
@@ -15655,12 +15796,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="25">
       <c r="A114" s="13" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="C114" s="17" t="s">
         <v>582</v>
@@ -15675,16 +15816,19 @@
         <v>1</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H114" s="17">
         <v>1</v>
       </c>
       <c r="I114" s="18" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="82.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="70">
       <c r="A115" s="13"/>
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
@@ -15692,16 +15836,16 @@
       <c r="E115" s="17"/>
       <c r="F115" s="17"/>
       <c r="G115" s="6" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="H115" s="17"/>
       <c r="I115" s="7" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="28">
       <c r="A116" s="13" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="B116" s="17" t="s">
         <v>204</v>
@@ -15731,12 +15875,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="25">
       <c r="A117" s="13" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="C117" s="17" t="s">
         <v>582</v>
@@ -15763,7 +15907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="28">
       <c r="A118" s="13"/>
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
@@ -15778,12 +15922,12 @@
         <v>242</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="28">
       <c r="A119" s="13" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="C119" s="17" t="s">
         <v>582</v>
@@ -15810,7 +15954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="25">
       <c r="A120" s="13"/>
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
@@ -15818,19 +15962,19 @@
       <c r="E120" s="17"/>
       <c r="F120" s="17"/>
       <c r="G120" s="17" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H120" s="17"/>
       <c r="I120" s="18" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="28">
       <c r="A121" s="13" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="C121" s="17" t="s">
         <v>582</v>
@@ -15853,8 +15997,11 @@
       <c r="I121" s="7" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="62.5">
       <c r="A122" s="13"/>
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
@@ -15862,19 +16009,19 @@
       <c r="E122" s="17"/>
       <c r="F122" s="17"/>
       <c r="G122" s="17" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="H122" s="17"/>
       <c r="I122" s="18" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="28">
       <c r="A123" s="13" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="C123" s="17" t="s">
         <v>582</v>
@@ -15889,16 +16036,19 @@
         <v>1</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="H123" s="17">
         <v>0</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>832</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
       <c r="A124" s="13"/>
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
@@ -15913,12 +16063,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="79.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ht="62.5">
       <c r="A125" s="13" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="C125" s="17" t="s">
         <v>582</v>
@@ -15933,21 +16083,24 @@
         <v>1</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="H125" s="17">
         <v>0</v>
       </c>
       <c r="I125" s="18" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>782</v>
+      </c>
+      <c r="J125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="25">
       <c r="A126" s="13" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="C126" s="17" t="s">
         <v>582</v>
@@ -15974,7 +16127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="62.5">
       <c r="A127" s="13"/>
       <c r="B127" s="17"/>
       <c r="C127" s="17"/>
@@ -15982,19 +16135,19 @@
       <c r="E127" s="17"/>
       <c r="F127" s="17"/>
       <c r="G127" s="17" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="H127" s="17"/>
       <c r="I127" s="18" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="25">
       <c r="A128" s="13" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="C128" s="17" t="s">
         <v>582</v>
@@ -16017,8 +16170,11 @@
       <c r="I128" s="18" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="129" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="37.5">
       <c r="A129" s="13"/>
       <c r="B129" s="17"/>
       <c r="C129" s="17"/>
@@ -16026,19 +16182,19 @@
       <c r="E129" s="17"/>
       <c r="F129" s="17"/>
       <c r="G129" s="17" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="H129" s="17"/>
       <c r="I129" s="18" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="37.5">
       <c r="A130" s="13" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="C130" s="17" t="s">
         <v>582</v>
@@ -16053,16 +16209,19 @@
         <v>1</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="H130" s="17">
         <v>0</v>
       </c>
       <c r="I130" s="18" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>791</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
       <c r="A131" s="13"/>
       <c r="B131" s="17"/>
       <c r="C131" s="17"/>
@@ -16077,12 +16236,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="69" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="70">
       <c r="A132" s="13" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>799</v>
+        <v>844</v>
       </c>
       <c r="C132" s="17" t="s">
         <v>582</v>
@@ -16097,21 +16256,24 @@
         <v>1</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="H132" s="17">
         <v>1</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="27.6" hidden="1" x14ac:dyDescent="0.25">
+        <v>833</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="28">
       <c r="A133" s="13" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="C133" s="17" t="s">
         <v>582</v>
@@ -16126,16 +16288,19 @@
         <v>3</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="H133" s="17">
         <v>3</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="55.8" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>835</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="56.5" thickBot="1">
       <c r="A134" s="10"/>
       <c r="B134" s="19"/>
       <c r="C134" s="19"/>
@@ -16143,11 +16308,11 @@
       <c r="E134" s="19"/>
       <c r="F134" s="19"/>
       <c r="G134" s="10" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="H134" s="19"/>
       <c r="I134" s="11" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
     </row>
   </sheetData>
@@ -16333,8 +16498,9 @@
     <hyperlink ref="I134" r:id="rId178" tooltip="敏捷" display="https://sts.huijiwiki.com/wiki/%E6%95%8F%E6%8D%B7" xr:uid="{A4DDD3EA-74B6-4837-BEA0-DEF91ED47D8C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId179"/>
   <tableParts count="1">
-    <tablePart r:id="rId179"/>
+    <tablePart r:id="rId180"/>
   </tableParts>
 </worksheet>
 </file>